--- a/results/job_matches_2026-07-14.xlsx
+++ b/results/job_matches_2026-07-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Engineering and Infrastructure)</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aurora Innovation</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark</t>
+          <t>AWS, Glue, EMR, Azure, Databricks, Google Cloud Platform, GCP, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b8b74c1db36b82</t>
+          <t>https://www.indeed.com/viewjob?jk=3e278e0dc4824974</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Full Stack (Java, AWS, React)</t>
+          <t>Senior Software Engineer (Data Engineering and Infrastructure)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Aurora Innovation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,42 +591,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Scala, Kafka, MySQL</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0f99e44e51085df</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b8b74c1db36b82</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer I (Data Eng infra)</t>
+          <t>Software Developer, Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aurora Innovation</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=490f497f5639497d</t>
+          <t>https://www.indeed.com/viewjob?jk=c01d88d0c47a7625</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Senior Software Engineer – Full Stack (Java, AWS, React)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Astronautics Corporation of America</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oak Creek, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d06ee741990db6b</t>
+          <t>https://www.indeed.com/viewjob?jk=d0f99e44e51085df</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Management Professional - Data Engineering - Entities</t>
+          <t>Software Engineer I (Data Eng infra)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Aurora Innovation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d437f6ae16eb4d</t>
+          <t>https://www.indeed.com/viewjob?jk=490f497f5639497d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Quality AI Intern (61_2026.3)</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Affinity Solutions</t>
+          <t>Astronautics Corporation of America</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oak Creek, WI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc7c811d1c4b67c</t>
+          <t>https://www.indeed.com/viewjob?jk=9d06ee741990db6b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AWS Severless Software Engineer III</t>
+          <t>Senior Data Management Professional - Data Engineering - Entities</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NBME</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce2dc4576aaa8a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=44d437f6ae16eb4d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Platform Engineer</t>
+          <t>Data Quality AI Intern (61_2026.3)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Affinity Solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Vertex AI, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40b7d898d0faad8</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc7c811d1c4b67c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Reliability Engineer, Battery Module</t>
+          <t>AWS Severless Software Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>NBME</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sparks, NV, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af907c177dd5fdb</t>
+          <t>https://www.indeed.com/viewjob?jk=ce2dc4576aaa8a2e</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Native Builder_EU</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea4fc6a360496ad</t>
+          <t>https://www.indeed.com/viewjob?jk=59be0306e4985a52</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer-Specialist</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2df1f2e18d690c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=12264a4762b0f153</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer-Specialist</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d896c15ac717e14c</t>
+          <t>https://www.indeed.com/viewjob?jk=4741b2aaf2ec4639</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer-Specialist</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4fe4e7c9a86b11</t>
+          <t>https://www.indeed.com/viewjob?jk=c8379cf1d692d007</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AWS Data Engineering Advisor</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ENGIE</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, S3, ECS, IAM, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088581dbc2434494</t>
+          <t>https://www.indeed.com/viewjob?jk=9696f4f0c31fbf12</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6310ba46fd00a82c</t>
+          <t>https://www.indeed.com/viewjob?jk=23fcdad233ea5e6d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>C2FO</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Spark, Scala, Kafka, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a710f918b88f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=12bdc06f31387ddb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - AI/ML</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa005e3343082c96</t>
+          <t>https://www.indeed.com/viewjob?jk=7f457f2be81b9770</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI) Senior Data Scientist</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9ea8d31a8815a9</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c8bee941837486</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Engineering Architect</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e831741c10ec9a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=6bce80595c811362</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SQL Developer</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>We Are Recruiting</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Foley, AL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a0bb69f0f00f0c</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0cf43be3ae79d3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Safelite</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Talend</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab9b545c0f88523</t>
+          <t>https://www.indeed.com/viewjob?jk=ade89b18f313e675</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, IAM, RDS, Databricks, CI/CD</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,172 +1336,172 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439c58ad35a8bb78</t>
+          <t>https://www.indeed.com/viewjob?jk=cfddcbf296252d6b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41b78df5b95306be</t>
+          <t>https://www.indeed.com/viewjob?jk=0aae1d49cd9474ec</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c2fa1d45c9055b</t>
+          <t>https://www.indeed.com/viewjob?jk=e2866e598e580305</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Clifton, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Oracle</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009aa09bd21a9217</t>
+          <t>https://www.indeed.com/viewjob?jk=c2ffd4ec0a1a5c3a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Big Data)</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d8e19f0fb16bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=534c078f01ee2602</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ef94552c14d9bd</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d39a911901dc6d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer II (US)</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2633a0f0dff514a6</t>
+          <t>https://www.indeed.com/viewjob?jk=a72c1fe63174bbb8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Princ Engr-Ntwk Engring</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e6dbfd3d963c65c</t>
+          <t>https://www.indeed.com/viewjob?jk=4bdbc801745a49ec</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Analytics Solutions Associate Senior - DART</t>
+          <t>Sr. Machine Learning Platform Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, ETL, ELT, Tableau, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Vertex AI, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1af5fc2a067c379</t>
+          <t>https://www.indeed.com/viewjob?jk=c40b7d898d0faad8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Financial Data &amp; Analytics Engineer</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Research Foundation for The State University of New York at Stony Brook</t>
+          <t>Entertainment Partners</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Stony Brook, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c72e69c8d1b5df</t>
+          <t>https://www.indeed.com/viewjob?jk=e42eebf957e43408</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AI Native Builder_EU</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=898a5660007f1525</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea4fc6a360496ad</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Technical Specialist</t>
+          <t>Forward Deployed Engineer-Specialist</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e03219acd75f33</t>
+          <t>https://www.indeed.com/viewjob?jk=2df1f2e18d690c4a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Technical Specialist(Python Developer)</t>
+          <t>Forward Deployed Engineer-Specialist</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d26e04dc07674449</t>
+          <t>https://www.indeed.com/viewjob?jk=d896c15ac717e14c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>Forward Deployed Engineer-Specialist</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dcac0248b7373d4</t>
+          <t>https://www.indeed.com/viewjob?jk=db4fe4e7c9a86b11</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer, Cat Digital</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Snowflake, Power BI, CI/CD, Azure DevOps, Airflow, Apache Airflow</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba56e26d2f7d66e</t>
+          <t>https://www.indeed.com/viewjob?jk=6310ba46fd00a82c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer I-Pathology Molecular and Cell Based Medicine</t>
+          <t>Senior Data Engineer I</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>C2FO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Redshift, Spark, Scala, Kafka, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f1090f617db00fd</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a710f918b88f2b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior System Software Engineer for Cloud – GeForce NOW</t>
+          <t>Senior Data Scientist - AI/ML</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d6d30e78e6f4c6e</t>
+          <t>https://www.indeed.com/viewjob?jk=aa005e3343082c96</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend / Cloud Services</t>
+          <t>Artificial Intelligence (AI) Senior Data Scientist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a96d284c8c6745</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9ea8d31a8815a9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineering Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd6388cdeebf986</t>
+          <t>https://www.indeed.com/viewjob?jk=e831741c10ec9a8d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Technical Specialist - Senior</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, IAM, RDS, Databricks, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,172 +2001,172 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfb170c35e948ca</t>
+          <t>https://www.indeed.com/viewjob?jk=439c58ad35a8bb78</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Java Specialist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51d97fe985e82f06</t>
+          <t>https://www.indeed.com/viewjob?jk=41b78df5b95306be</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d7f6a3d55e28770</t>
+          <t>https://www.indeed.com/viewjob?jk=26c2fa1d45c9055b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FirstDay Foundation</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Clifton, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d797cade2cc30f67</t>
+          <t>https://www.indeed.com/viewjob?jk=009aa09bd21a9217</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer (Big Data)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NYSTEC</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43f810dbefdcbc9</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d8e19f0fb16bc7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f681ba8c58e14f</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ec36958a4f20d5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Big Data)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>Safelite</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Hive, Spark, Scala, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,137 +2211,137 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f9d9276b923717</t>
+          <t>https://www.indeed.com/viewjob?jk=eab9b545c0f88523</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Lambda, API Gateway, RDS, Spark, PySpark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05cf4bb1193bec3f</t>
+          <t>https://www.indeed.com/viewjob?jk=d0cafea3b627d6c7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3836b0fc7c4571</t>
+          <t>https://www.indeed.com/viewjob?jk=2633a0f0dff514a6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57668a6af42a8310</t>
+          <t>https://www.indeed.com/viewjob?jk=84ef94552c14d9bd</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - GenAI/Agentic AI - Remote</t>
+          <t>Princ Engr-Ntwk Engring</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34b1a1a8543d5bde</t>
+          <t>https://www.indeed.com/viewjob?jk=4e6dbfd3d963c65c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineering Architect</t>
+          <t>Senior Financial Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>The Research Foundation for The State University of New York at Stony Brook</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Stony Brook, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a16e3ffc1c278fc</t>
+          <t>https://www.indeed.com/viewjob?jk=05c72e69c8d1b5df</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=487e755470e0a906</t>
+          <t>https://www.indeed.com/viewjob?jk=898a5660007f1525</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AI) - Frisco, TX</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Invovia</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8e491698172a68a</t>
+          <t>https://www.indeed.com/viewjob?jk=9dcac0248b7373d4</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AI)</t>
+          <t>Technical Specialist</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Invovia</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9389c7fce7ffb417</t>
+          <t>https://www.indeed.com/viewjob?jk=91e03219acd75f33</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Technical Specialist(Python Developer)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc63eb13d50f0ab</t>
+          <t>https://www.indeed.com/viewjob?jk=d26e04dc07674449</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Data Engineer I-Pathology Molecular and Cell Based Medicine</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3004d47870448a1</t>
+          <t>https://www.indeed.com/viewjob?jk=1f1090f617db00fd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Analytics Data Engineer, Cat Digital</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, S3, Azure, Scala, Snowflake, Power BI, CI/CD, Azure DevOps, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=845986ee9c384d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba56e26d2f7d66e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Senior System Software Engineer for Cloud – GeForce NOW</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, DynamoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9bc641ca30ce01</t>
+          <t>https://www.indeed.com/viewjob?jk=9d6d30e78e6f4c6e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Managing Engineer - Fusion GRC Platform</t>
+          <t>Senior Software Engineer - Backend / Cloud Services</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,67 +2666,67 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8c6087cd256e74</t>
+          <t>https://www.indeed.com/viewjob?jk=18a96d284c8c6745</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Data &amp; Integration</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cccab38c68c6dc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd6388cdeebf986</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Marketing Technology Strategist</t>
+          <t>Technical Specialist - Senior</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Phase2</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08cde2c4527579db</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfb170c35e948ca</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. IT Data Engineer</t>
+          <t>Senior Java Specialist</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0debfb86cec6f81</t>
+          <t>https://www.indeed.com/viewjob?jk=51d97fe985e82f06</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist - GenAI/Agentic AI - Remote</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,49 +2806,49 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e522d64598216a</t>
+          <t>https://www.indeed.com/viewjob?jk=34b1a1a8543d5bde</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer - Oracle data integrator and BI</t>
+          <t>Senior Software Engineer (Big Data)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Smart Apply Test Company</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Databricks, Hadoop, Hive, Spark, Scala, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b40de561865171b</t>
+          <t>https://www.indeed.com/viewjob?jk=17f9d9276b923717</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2858,85 +2858,85 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>AWS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5962ad63a23cfa81</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3836b0fc7c4571</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083794db905029d1</t>
+          <t>https://www.indeed.com/viewjob?jk=6d7f6a3d55e28770</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>FirstDay Foundation</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6911722171aa1c</t>
+          <t>https://www.indeed.com/viewjob?jk=d797cade2cc30f67</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Security Architect(AI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Paylocity</t>
+          <t>NYSTEC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b6040d8fca19b2e</t>
+          <t>https://www.indeed.com/viewjob?jk=e43f810dbefdcbc9</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,102 +3016,102 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd021ef938d1ce24</t>
+          <t>https://www.indeed.com/viewjob?jk=91f681ba8c58e14f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Hunter)</t>
+          <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1f7af295967ab5</t>
+          <t>https://www.indeed.com/viewjob?jk=05cf4bb1193bec3f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Security Architect(AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Paylocity</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
+          <t>AWS, Glue, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ffe1515831234d9</t>
+          <t>https://www.indeed.com/viewjob?jk=57668a6af42a8310</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Product Engineer - Fusion GRC Platform</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef44df6379fa49ce</t>
+          <t>https://www.indeed.com/viewjob?jk=8102d30c9db848fa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Architect of Data Architecture</t>
+          <t>Data Engineering Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Empower</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,137 +3156,137 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a69b442d48a997e</t>
+          <t>https://www.indeed.com/viewjob?jk=8a16e3ffc1c278fc</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d4be214d89c9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=487e755470e0a906</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd7b858f4e17691</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc63eb13d50f0ab</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PI Security LLC</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed01df22f7b5ad6f</t>
+          <t>https://www.indeed.com/viewjob?jk=c3004d47870448a1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Forward Deployed Engineer (AI) - Frisco, TX</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Afficiency</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MLflow, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be5a298b53e539ed</t>
+          <t>https://www.indeed.com/viewjob?jk=f8e491698172a68a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Forward Deployed Engineer (AI)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a2f1102b97c2bd1</t>
+          <t>https://www.indeed.com/viewjob?jk=9389c7fce7ffb417</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - SRE</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,67 +3366,67 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f2cb5787bcd07a</t>
+          <t>https://www.indeed.com/viewjob?jk=845986ee9c384d0c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90454ed63602f69</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9bc641ca30ce01</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Managing Engineer - Fusion GRC Platform</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2df343ab9d22ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8c6087cd256e74</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks</t>
+          <t>Sr. Data Engineer - Cloud, AWS and Snowflake</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SugarAI</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
+          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51c067e768a2b9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=b4be1c8e67e2a1f2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer Seniors III (Databricks)</t>
+          <t>Sr. Software Engineer- Data &amp; Integration</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Data Modeling, ETL, ELT</t>
+          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89625a5f68a2c750</t>
+          <t>https://www.indeed.com/viewjob?jk=cccab38c68c6dc6f</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Sr. IT Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c629002dbb52205d</t>
+          <t>https://www.indeed.com/viewjob?jk=d0debfb86cec6f81</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Safelite</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,102 +3576,102 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89f11f71a1c806a8</t>
+          <t>https://www.indeed.com/viewjob?jk=18e522d64598216a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer IV (Snowflake/Databricks) - REMOTE</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Velera</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd204a1167efc6a3</t>
+          <t>https://www.indeed.com/viewjob?jk=5962ad63a23cfa81</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aab6a4a6b438005</t>
+          <t>https://www.indeed.com/viewjob?jk=083794db905029d1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Marketing Technology Strategist</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>Phase2</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,102 +3681,102 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073c59c0c666dd26</t>
+          <t>https://www.indeed.com/viewjob?jk=08cde2c4527579db</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Oracle)</t>
+          <t>Data Engineer - Oracle data integrator and BI</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7673be72cf2a7f02</t>
+          <t>https://www.indeed.com/viewjob?jk=4b40de561865171b</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise, Data &amp; AI</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Zoox</t>
+          <t>Entertainment Partners</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, S3, RDS, Azure, NoSQL, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303390f40d7bb17a</t>
+          <t>https://www.indeed.com/viewjob?jk=597ab0eb363227ed</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Integration Operations Engineerr</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Dental Care Alliance</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Snowflake, Informatica PowerCenter, ETL, ELT</t>
+          <t>RDS, Azure, Scala, SQL Server, NoSQL, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=748fc639b3268939</t>
+          <t>https://www.indeed.com/viewjob?jk=8f835ab35442d7c1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Security Architect(AI)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>Paylocity</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,89 +3821,89 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d697f334d121ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=7b6040d8fca19b2e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior AI &amp; Cloud Engineer</t>
+          <t>Solutions Architect - Financial Services (Hunter)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3b212b4def3f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1f7af295967ab5</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Security Architect(AI)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Paylocity</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81752facbba9d16c</t>
+          <t>https://www.indeed.com/viewjob?jk=0ffe1515831234d9</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I- Data &amp; Insights Engineering</t>
+          <t>Product Engineer - Fusion GRC Platform</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Aledade, Inc.</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3912,11 +3912,11 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c358b482d33d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=ef44df6379fa49ce</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr. Data Engineering Architect</t>
+          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,102 +3961,102 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6af42e024fb5358</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6911722171aa1c</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Cloud Architect @ Dallas, TX</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Logistic Solutions Inc</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ffb721ba3a7f68</t>
+          <t>https://www.indeed.com/viewjob?jk=14d4be214d89c9f3</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2545dd224fcef4a</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd7b858f4e17691</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. Cloud Security Engineer (Remote)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,67 +4066,67 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47913b36a9ddd604</t>
+          <t>https://www.indeed.com/viewjob?jk=5a2f1102b97c2bd1</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Engineer - &amp; Modeler Informatica</t>
+          <t>Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aebf504e442ce2f2</t>
+          <t>https://www.indeed.com/viewjob?jk=91f2cb5787bcd07a</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Scala, Data Modeling, ETL, ELT, Power BI, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445e8b11f533b240</t>
+          <t>https://www.indeed.com/viewjob?jk=c90454ed63602f69</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Level 2 – Technical Support Engineer</t>
+          <t>Architect of Data Architecture</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Empower</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT, REST API integration</t>
+          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f92c2bb95c010dd6</t>
+          <t>https://www.indeed.com/viewjob?jk=2a69b442d48a997e</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Bi Developer</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Afficiency</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MLflow, Terraform, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,42 +4206,917 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b85dd5750a229b32</t>
+          <t>https://www.indeed.com/viewjob?jk=be5a298b53e539ed</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>PI Security LLC</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed01df22f7b5ad6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Specialist - Data Engineering</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>LTM Limited</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c629002dbb52205d</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Data Engineer IV (Snowflake/Databricks) - REMOTE</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Velera</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd204a1167efc6a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Smart Apply Test Company</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d697f334d121ec3</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81752facbba9d16c</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Pano AI</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2df343ab9d22ccf</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Databricks</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>SugarAI</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51c067e768a2b9f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Data Engineer Seniors III (Databricks)</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>FIS</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89625a5f68a2c750</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Business Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Safelite</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89f11f71a1c806a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Pano AI</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4aab6a4a6b438005</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Health Data Analytics Institute</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Dedham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=073c59c0c666dd26</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Oracle)</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Bitscopic</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7673be72cf2a7f02</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer – Enterprise, Data &amp; AI</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Zoox</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, Terraform, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=303390f40d7bb17a</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Senior Data Integration Operations Engineerr</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Northeastern University</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Snowflake, Informatica PowerCenter, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=748fc639b3268939</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Senior AI &amp; Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e3b212b4def3f9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineering Architect</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b6af42e024fb5358</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Cloud Architect @ Dallas, TX</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Logistic Solutions Inc</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1ffb721ba3a7f68</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Consumer Cellular</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2545dd224fcef4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Sr. Cloud Security Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Inspira Financial</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Oak Brook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47913b36a9ddd604</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Chandler, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, GCP, Scala, Data Modeling, ETL, ELT, Power BI, Git</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=445e8b11f533b240</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff9ef03bf06139c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer I- Data &amp; Insights Engineering</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Aledade, Inc.</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15c358b482d33d6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
           <t>Full Stack Mid-level Java Software Engineer</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>WSFS Bank</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>Wilmington, DE, US USA</t>
         </is>
       </c>
-      <c r="D109" t="n">
+      <c r="D131" t="n">
         <v>10.4</v>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="E131" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Kubernetes, Datadog, Python</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=78f65e99062ef281</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Data Engineer - &amp; Modeler Informatica</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aebf504e442ce2f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Bi Developer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Cloud and Things</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Albany, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b85dd5750a229b32</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Level 2 – Technical Support Engineer</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT, REST API integration</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f92c2bb95c010dd6</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-14.xlsx
+++ b/results/job_matches_2026-07-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G134"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,52 +573,52 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Engineering and Infrastructure)</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aurora Innovation</t>
+          <t>Winfo Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b8b74c1db36b82</t>
+          <t>https://www.indeed.com/viewjob?jk=0c1691b4d7b52de9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Developer, Business Intelligence Analyst</t>
+          <t>Senior Software Engineer (Data Engineering and Infrastructure)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Aurora Innovation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01d88d0c47a7625</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b8b74c1db36b82</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Full Stack (Java, AWS, React)</t>
+          <t>Software Developer, Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Scala, Kafka, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0f99e44e51085df</t>
+          <t>https://www.indeed.com/viewjob?jk=c01d88d0c47a7625</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer I (Data Eng infra)</t>
+          <t>Senior Data Engineer, AWS Data Platform</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aurora Innovation</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=490f497f5639497d</t>
+          <t>https://www.indeed.com/viewjob?jk=cfb146f53215cc2b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Software Engineer I (Data Eng infra)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Astronautics Corporation of America</t>
+          <t>Aurora Innovation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Oak Creek, WI, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,64 +731,64 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d06ee741990db6b</t>
+          <t>https://www.indeed.com/viewjob?jk=490f497f5639497d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Management Professional - Data Engineering - Entities</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Astronautics Corporation of America</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oak Creek, WI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d437f6ae16eb4d</t>
+          <t>https://www.indeed.com/viewjob?jk=9d06ee741990db6b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Quality AI Intern (61_2026.3)</t>
+          <t>Senior Data Management Professional - Data Engineering - Entities</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Affinity Solutions</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc7c811d1c4b67c</t>
+          <t>https://www.indeed.com/viewjob?jk=44d437f6ae16eb4d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS Severless Software Engineer III</t>
+          <t>Data Quality AI Intern (61_2026.3)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NBME</t>
+          <t>Affinity Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,52 +836,52 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce2dc4576aaa8a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc7c811d1c4b67c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Severless Software Engineer III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>NBME</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2afd6091c64d55df</t>
+          <t>https://www.indeed.com/viewjob?jk=ce2dc4576aaa8a2e</t>
         </is>
       </c>
     </row>
@@ -2043,17 +2043,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Clifton, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c2fa1d45c9055b</t>
+          <t>https://www.indeed.com/viewjob?jk=009aa09bd21a9217</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Clifton, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009aa09bd21a9217</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ec36958a4f20d5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Big Data)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Safelite</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d8e19f0fb16bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=eab9b545c0f88523</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Hadoop, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ec36958a4f20d5</t>
+          <t>https://www.indeed.com/viewjob?jk=2633a0f0dff514a6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Safelite</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Talend</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab9b545c0f88523</t>
+          <t>https://www.indeed.com/viewjob?jk=84ef94552c14d9bd</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Princ Engr-Ntwk Engring</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, RDS, Spark, PySpark, Scala, Kafka, SQL Server</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0cafea3b627d6c7</t>
+          <t>https://www.indeed.com/viewjob?jk=4e6dbfd3d963c65c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer II (US)</t>
+          <t>Senior Financial Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>The Research Foundation for The State University of New York at Stony Brook</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Stony Brook, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2633a0f0dff514a6</t>
+          <t>https://www.indeed.com/viewjob?jk=05c72e69c8d1b5df</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ef94552c14d9bd</t>
+          <t>https://www.indeed.com/viewjob?jk=898a5660007f1525</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Princ Engr-Ntwk Engring</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e6dbfd3d963c65c</t>
+          <t>https://www.indeed.com/viewjob?jk=9dcac0248b7373d4</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Financial Data &amp; Analytics Engineer</t>
+          <t>Technical Specialist</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>The Research Foundation for The State University of New York at Stony Brook</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Stony Brook, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c72e69c8d1b5df</t>
+          <t>https://www.indeed.com/viewjob?jk=91e03219acd75f33</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Technical Specialist(Python Developer)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=898a5660007f1525</t>
+          <t>https://www.indeed.com/viewjob?jk=d26e04dc07674449</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>Data Engineer I-Pathology Molecular and Cell Based Medicine</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dcac0248b7373d4</t>
+          <t>https://www.indeed.com/viewjob?jk=1f1090f617db00fd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Technical Specialist</t>
+          <t>Analytics Data Engineer, Cat Digital</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, S3, Azure, Scala, Snowflake, Power BI, CI/CD, Azure DevOps, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e03219acd75f33</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba56e26d2f7d66e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Technical Specialist(Python Developer)</t>
+          <t>Senior System Software Engineer for Cloud – GeForce NOW</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, DynamoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,19 +2526,19 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d26e04dc07674449</t>
+          <t>https://www.indeed.com/viewjob?jk=9d6d30e78e6f4c6e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer I-Pathology Molecular and Cell Based Medicine</t>
+          <t>Senior Software Engineer - Backend / Cloud Services</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f1090f617db00fd</t>
+          <t>https://www.indeed.com/viewjob?jk=18a96d284c8c6745</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer, Cat Digital</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Snowflake, Power BI, CI/CD, Azure DevOps, Airflow, Apache Airflow</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba56e26d2f7d66e</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd6388cdeebf986</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior System Software Engineer for Cloud – GeForce NOW</t>
+          <t>Technical Specialist - Senior</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d6d30e78e6f4c6e</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfb170c35e948ca</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend / Cloud Services</t>
+          <t>Senior Java Specialist</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,67 +2666,67 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a96d284c8c6745</t>
+          <t>https://www.indeed.com/viewjob?jk=51d97fe985e82f06</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist - GenAI/Agentic AI - Remote</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd6388cdeebf986</t>
+          <t>https://www.indeed.com/viewjob?jk=34b1a1a8543d5bde</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Technical Specialist - Senior</t>
+          <t>Senior Software Engineer (Big Data)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Smart Apply Test Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Databricks, Hadoop, Hive, Spark, Scala, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfb170c35e948ca</t>
+          <t>https://www.indeed.com/viewjob?jk=17f9d9276b923717</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Java Specialist</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51d97fe985e82f06</t>
+          <t>https://www.indeed.com/viewjob?jk=33124af211245233</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - GenAI/Agentic AI - Remote</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, Power BI</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34b1a1a8543d5bde</t>
+          <t>https://www.indeed.com/viewjob?jk=6d7f6a3d55e28770</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Big Data)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>FirstDay Foundation</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Hive, Spark, Scala, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f9d9276b923717</t>
+          <t>https://www.indeed.com/viewjob?jk=d797cade2cc30f67</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>NYSTEC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3836b0fc7c4571</t>
+          <t>https://www.indeed.com/viewjob?jk=e43f810dbefdcbc9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d7f6a3d55e28770</t>
+          <t>https://www.indeed.com/viewjob?jk=91f681ba8c58e14f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FirstDay Foundation</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d797cade2cc30f67</t>
+          <t>https://www.indeed.com/viewjob?jk=05cf4bb1193bec3f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NYSTEC</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43f810dbefdcbc9</t>
+          <t>https://www.indeed.com/viewjob?jk=8102d30c9db848fa</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineering Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f681ba8c58e14f</t>
+          <t>https://www.indeed.com/viewjob?jk=8a16e3ffc1c278fc</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05cf4bb1193bec3f</t>
+          <t>https://www.indeed.com/viewjob?jk=487e755470e0a906</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57668a6af42a8310</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc63eb13d50f0ab</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8102d30c9db848fa</t>
+          <t>https://www.indeed.com/viewjob?jk=c3004d47870448a1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineering Architect</t>
+          <t>Forward Deployed Engineer (AI) - Frisco, TX</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a16e3ffc1c278fc</t>
+          <t>https://www.indeed.com/viewjob?jk=f8e491698172a68a</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Forward Deployed Engineer (AI)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=487e755470e0a906</t>
+          <t>https://www.indeed.com/viewjob?jk=9389c7fce7ffb417</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc63eb13d50f0ab</t>
+          <t>https://www.indeed.com/viewjob?jk=845986ee9c384d0c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,42 +3251,42 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3004d47870448a1</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9bc641ca30ce01</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AI) - Frisco, TX</t>
+          <t>Sr. Data Engineer - Cloud, AWS and Snowflake</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Invovia</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8e491698172a68a</t>
+          <t>https://www.indeed.com/viewjob?jk=b4be1c8e67e2a1f2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AI)</t>
+          <t>Sr. Software Engineer- Data &amp; Integration</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Invovia</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9389c7fce7ffb417</t>
+          <t>https://www.indeed.com/viewjob?jk=cccab38c68c6dc6f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Sr. IT Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=845986ee9c384d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=d0debfb86cec6f81</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9bc641ca30ce01</t>
+          <t>https://www.indeed.com/viewjob?jk=18e522d64598216a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Managing Engineer - Fusion GRC Platform</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Kubernetes, Git</t>
+          <t>AWS, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8c6087cd256e74</t>
+          <t>https://www.indeed.com/viewjob?jk=3979f77f1eb1efbc</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Cloud, AWS and Snowflake</t>
+          <t>Marketing Technology Strategist</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Phase2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4be1c8e67e2a1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=08cde2c4527579db</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Data &amp; Integration</t>
+          <t>Data Engineer - Oracle data integrator and BI</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cccab38c68c6dc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=4b40de561865171b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. IT Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Entertainment Partners</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, S3, RDS, Azure, NoSQL, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0debfb86cec6f81</t>
+          <t>https://www.indeed.com/viewjob?jk=597ab0eb363227ed</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Dental Care Alliance</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, NoSQL, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e522d64598216a</t>
+          <t>https://www.indeed.com/viewjob?jk=8f835ab35442d7c1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Security Architect(AI)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Paylocity</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5962ad63a23cfa81</t>
+          <t>https://www.indeed.com/viewjob?jk=7b6040d8fca19b2e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Solutions Architect - Financial Services (Hunter)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083794db905029d1</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1f7af295967ab5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Marketing Technology Strategist</t>
+          <t>Senior Security Architect(AI)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Phase2</t>
+          <t>Paylocity</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08cde2c4527579db</t>
+          <t>https://www.indeed.com/viewjob?jk=0ffe1515831234d9</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer - Oracle data integrator and BI</t>
+          <t>Product Engineer - Fusion GRC Platform</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b40de561865171b</t>
+          <t>https://www.indeed.com/viewjob?jk=ef44df6379fa49ce</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Entertainment Partners</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, NoSQL, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597ab0eb363227ed</t>
+          <t>https://www.indeed.com/viewjob?jk=14d4be214d89c9f3</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Dental Care Alliance</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, NoSQL, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f835ab35442d7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd7b858f4e17691</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Security Architect(AI)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Paylocity</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b6040d8fca19b2e</t>
+          <t>https://www.indeed.com/viewjob?jk=5a2f1102b97c2bd1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Hunter)</t>
+          <t>Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1f7af295967ab5</t>
+          <t>https://www.indeed.com/viewjob?jk=91f2cb5787bcd07a</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Security Architect(AI)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Paylocity</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ffe1515831234d9</t>
+          <t>https://www.indeed.com/viewjob?jk=c90454ed63602f69</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Product Engineer - Fusion GRC Platform</t>
+          <t>Architect of Data Architecture</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Empower</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef44df6379fa49ce</t>
+          <t>https://www.indeed.com/viewjob?jk=2a69b442d48a997e</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Afficiency</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MLflow, Terraform, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6911722171aa1c</t>
+          <t>https://www.indeed.com/viewjob?jk=be5a298b53e539ed</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>PI Security LLC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,77 +3986,77 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d4be214d89c9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=ed01df22f7b5ad6f</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd7b858f4e17691</t>
+          <t>https://www.indeed.com/viewjob?jk=c629002dbb52205d</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Engineer IV (Snowflake/Databricks) - REMOTE</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Velera</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a2f1102b97c2bd1</t>
+          <t>https://www.indeed.com/viewjob?jk=fd204a1167efc6a3</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - SRE</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Smart Apply Test Company</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,67 +4101,67 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f2cb5787bcd07a</t>
+          <t>https://www.indeed.com/viewjob?jk=2d697f334d121ec3</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90454ed63602f69</t>
+          <t>https://www.indeed.com/viewjob?jk=c2df343ab9d22ccf</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Architect of Data Architecture</t>
+          <t>Senior Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Empower</t>
+          <t>SugarAI</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a69b442d48a997e</t>
+          <t>https://www.indeed.com/viewjob?jk=51c067e768a2b9f2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Data Engineer Seniors III (Databricks)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Afficiency</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MLflow, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be5a298b53e539ed</t>
+          <t>https://www.indeed.com/viewjob?jk=89625a5f68a2c750</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PI Security LLC</t>
+          <t>Safelite</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed01df22f7b5ad6f</t>
+          <t>https://www.indeed.com/viewjob?jk=89f11f71a1c806a8</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c629002dbb52205d</t>
+          <t>https://www.indeed.com/viewjob?jk=4aab6a4a6b438005</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer IV (Snowflake/Databricks) - REMOTE</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Velera</t>
+          <t>Health Data Analytics Institute</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dedham, MA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd204a1167efc6a3</t>
+          <t>https://www.indeed.com/viewjob?jk=073c59c0c666dd26</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer (Oracle)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d697f334d121ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=7673be72cf2a7f02</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer – Enterprise, Data &amp; AI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Zoox</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81752facbba9d16c</t>
+          <t>https://www.indeed.com/viewjob?jk=303390f40d7bb17a</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Integration Operations Engineerr</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>Northeastern University</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Snowflake, Informatica PowerCenter, ETL, ELT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2df343ab9d22ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=748fc639b3268939</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks</t>
+          <t>Sr. Data Engineering Architect</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SugarAI</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51c067e768a2b9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=b6af42e024fb5358</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer Seniors III (Databricks)</t>
+          <t>Cloud Architect @ Dallas, TX</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Logistic Solutions Inc</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89625a5f68a2c750</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ffb721ba3a7f68</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Safelite</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89f11f71a1c806a8</t>
+          <t>https://www.indeed.com/viewjob?jk=e2545dd224fcef4a</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Sr. Cloud Security Engineer (Remote)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>IAM, RDS, Azure, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aab6a4a6b438005</t>
+          <t>https://www.indeed.com/viewjob?jk=47913b36a9ddd604</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+          <t>RDS, Azure, Databricks, GCP, Scala, Data Modeling, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073c59c0c666dd26</t>
+          <t>https://www.indeed.com/viewjob?jk=445e8b11f533b240</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Oracle)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7673be72cf2a7f02</t>
+          <t>https://www.indeed.com/viewjob?jk=ff9ef03bf06139c6</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise, Data &amp; AI</t>
+          <t>Senior Software Engineer I- Data &amp; Insights Engineering</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Zoox</t>
+          <t>Aledade, Inc.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, Terraform, Kubernetes, Airflow</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303390f40d7bb17a</t>
+          <t>https://www.indeed.com/viewjob?jk=15c358b482d33d6d</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Data Integration Operations Engineerr</t>
+          <t>Data Engineer - &amp; Modeler Informatica</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Snowflake, Informatica PowerCenter, ETL, ELT</t>
+          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=748fc639b3268939</t>
+          <t>https://www.indeed.com/viewjob?jk=aebf504e442ce2f2</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior AI &amp; Cloud Engineer</t>
+          <t>Bi Developer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3b212b4def3f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=b85dd5750a229b32</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Sr. Data Engineering Architect</t>
+          <t>Level 2 – Technical Support Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4765,356 +4765,6 @@
         </is>
       </c>
       <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b6af42e024fb5358</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Cloud Architect @ Dallas, TX</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Logistic Solutions Inc</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ffb721ba3a7f68</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Consumer Cellular</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Scottsdale, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2545dd224fcef4a</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Sr. Cloud Security Engineer (Remote)</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Inspira Financial</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Oak Brook, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=47913b36a9ddd604</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Chandler, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Scala, Data Modeling, ETL, ELT, Power BI, Git</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=445e8b11f533b240</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Dearborn, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff9ef03bf06139c6</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer I- Data &amp; Insights Engineering</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Aledade, Inc.</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15c358b482d33d6d</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Full Stack Mid-level Java Software Engineer</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>WSFS Bank</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Kubernetes, Datadog, Python</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=78f65e99062ef281</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Data Engineer - &amp; Modeler Informatica</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aebf504e442ce2f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Bi Developer</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Cloud and Things</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Albany, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b85dd5750a229b32</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Level 2 – Technical Support Engineer</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT, REST API integration</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f92c2bb95c010dd6</t>
         </is>

--- a/results/job_matches_2026-07-14.xlsx
+++ b/results/job_matches_2026-07-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,47 +748,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Senior Data Management Professional - Data Engineering - Entities</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Astronautics Corporation of America</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Oak Creek, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d06ee741990db6b</t>
+          <t>https://www.indeed.com/viewjob?jk=44d437f6ae16eb4d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Management Professional - Data Engineering - Entities</t>
+          <t>Data Quality AI Intern (61_2026.3)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Affinity Solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d437f6ae16eb4d</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc7c811d1c4b67c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Quality AI Intern (61_2026.3)</t>
+          <t>AWS Severless Software Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Affinity Solutions</t>
+          <t>NBME</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc7c811d1c4b67c</t>
+          <t>https://www.indeed.com/viewjob?jk=ce2dc4576aaa8a2e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AWS Severless Software Engineer III</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NBME</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce2dc4576aaa8a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=59be0306e4985a52</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59be0306e4985a52</t>
+          <t>https://www.indeed.com/viewjob?jk=12264a4762b0f153</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12264a4762b0f153</t>
+          <t>https://www.indeed.com/viewjob?jk=4741b2aaf2ec4639</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4741b2aaf2ec4639</t>
+          <t>https://www.indeed.com/viewjob?jk=c8379cf1d692d007</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8379cf1d692d007</t>
+          <t>https://www.indeed.com/viewjob?jk=9696f4f0c31fbf12</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9696f4f0c31fbf12</t>
+          <t>https://www.indeed.com/viewjob?jk=23fcdad233ea5e6d</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23fcdad233ea5e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=12bdc06f31387ddb</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12bdc06f31387ddb</t>
+          <t>https://www.indeed.com/viewjob?jk=7f457f2be81b9770</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f457f2be81b9770</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c8bee941837486</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c8bee941837486</t>
+          <t>https://www.indeed.com/viewjob?jk=6bce80595c811362</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bce80595c811362</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0cf43be3ae79d3</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0cf43be3ae79d3</t>
+          <t>https://www.indeed.com/viewjob?jk=ade89b18f313e675</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade89b18f313e675</t>
+          <t>https://www.indeed.com/viewjob?jk=cfddcbf296252d6b</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfddcbf296252d6b</t>
+          <t>https://www.indeed.com/viewjob?jk=0aae1d49cd9474ec</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0aae1d49cd9474ec</t>
+          <t>https://www.indeed.com/viewjob?jk=e2866e598e580305</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2866e598e580305</t>
+          <t>https://www.indeed.com/viewjob?jk=c2ffd4ec0a1a5c3a</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ffd4ec0a1a5c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=534c078f01ee2602</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=534c078f01ee2602</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d39a911901dc6d</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d39a911901dc6d</t>
+          <t>https://www.indeed.com/viewjob?jk=a72c1fe63174bbb8</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a72c1fe63174bbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=4bdbc801745a49ec</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Junior Software Engineer- Cloud Cost Optimization</t>
+          <t>Sr. Machine Learning Platform Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Vertex AI, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bdbc801745a49ec</t>
+          <t>https://www.indeed.com/viewjob?jk=c40b7d898d0faad8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Platform Engineer</t>
+          <t>AI Native Builder_EU</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Vertex AI, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40b7d898d0faad8</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea4fc6a360496ad</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Forward Deployed Engineer-Specialist</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Entertainment Partners</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,24 +1641,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42eebf957e43408</t>
+          <t>https://www.indeed.com/viewjob?jk=2df1f2e18d690c4a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Native Builder_EU</t>
+          <t>Forward Deployed Engineer-Specialist</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea4fc6a360496ad</t>
+          <t>https://www.indeed.com/viewjob?jk=d896c15ac717e14c</t>
         </is>
       </c>
     </row>
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2df1f2e18d690c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=db4fe4e7c9a86b11</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer-Specialist</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Entertainment Partners</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,42 +1746,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d896c15ac717e14c</t>
+          <t>https://www.indeed.com/viewjob?jk=e42eebf957e43408</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer-Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4fe4e7c9a86b11</t>
+          <t>https://www.indeed.com/viewjob?jk=6310ba46fd00a82c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer I</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>C2FO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Redshift, Spark, Scala, Kafka, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6310ba46fd00a82c</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a710f918b88f2b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I</t>
+          <t>Application Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>C2FO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Spark, Scala, Kafka, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, ECS, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a710f918b88f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=53d521f5fad271b9</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Princ Engr-Ntwk Engring</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ef94552c14d9bd</t>
+          <t>https://www.indeed.com/viewjob?jk=4e6dbfd3d963c65c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Princ Engr-Ntwk Engring</t>
+          <t>Senior Financial Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>The Research Foundation for The State University of New York at Stony Brook</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Stony Brook, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e6dbfd3d963c65c</t>
+          <t>https://www.indeed.com/viewjob?jk=05c72e69c8d1b5df</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Financial Data &amp; Analytics Engineer</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Research Foundation for The State University of New York at Stony Brook</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Stony Brook, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c72e69c8d1b5df</t>
+          <t>https://www.indeed.com/viewjob?jk=84ef94552c14d9bd</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>Technical Specialist</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,19 +2351,19 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dcac0248b7373d4</t>
+          <t>https://www.indeed.com/viewjob?jk=91e03219acd75f33</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Technical Specialist</t>
+          <t>Technical Specialist(Python Developer)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e03219acd75f33</t>
+          <t>https://www.indeed.com/viewjob?jk=d26e04dc07674449</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Technical Specialist(Python Developer)</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d26e04dc07674449</t>
+          <t>https://www.indeed.com/viewjob?jk=9dcac0248b7373d4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer I-Pathology Molecular and Cell Based Medicine</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f1090f617db00fd</t>
+          <t>https://www.indeed.com/viewjob?jk=82d983a063892214</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer, Cat Digital</t>
+          <t>Data Engineer I-Pathology Molecular and Cell Based Medicine</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Snowflake, Power BI, CI/CD, Azure DevOps, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba56e26d2f7d66e</t>
+          <t>https://www.indeed.com/viewjob?jk=1f1090f617db00fd</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior System Software Engineer for Cloud – GeForce NOW</t>
+          <t>Analytics Data Engineer, Cat Digital</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, Azure, Scala, Snowflake, Power BI, CI/CD, Azure DevOps, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d6d30e78e6f4c6e</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba56e26d2f7d66e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend / Cloud Services</t>
+          <t>Senior System Software Engineer for Cloud – GeForce NOW</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, DynamoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a96d284c8c6745</t>
+          <t>https://www.indeed.com/viewjob?jk=9d6d30e78e6f4c6e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Specialist - Senior</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,29 +2586,29 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd6388cdeebf986</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfb170c35e948ca</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Technical Specialist - Senior</t>
+          <t>Senior Java Specialist</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfb170c35e948ca</t>
+          <t>https://www.indeed.com/viewjob?jk=51d97fe985e82f06</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Java Specialist</t>
+          <t>Senior Software Engineer - Backend / Cloud Services</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51d97fe985e82f06</t>
+          <t>https://www.indeed.com/viewjob?jk=18a96d284c8c6745</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Big Data)</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Hive, Spark, Scala, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f9d9276b923717</t>
+          <t>https://www.indeed.com/viewjob?jk=33124af211245233</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33124af211245233</t>
+          <t>https://www.indeed.com/viewjob?jk=6d7f6a3d55e28770</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>FirstDay Foundation</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d7f6a3d55e28770</t>
+          <t>https://www.indeed.com/viewjob?jk=d797cade2cc30f67</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FirstDay Foundation</t>
+          <t>NYSTEC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d797cade2cc30f67</t>
+          <t>https://www.indeed.com/viewjob?jk=e43f810dbefdcbc9</t>
         </is>
       </c>
     </row>
@@ -2853,12 +2853,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NYSTEC</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43f810dbefdcbc9</t>
+          <t>https://www.indeed.com/viewjob?jk=91f681ba8c58e14f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f681ba8c58e14f</t>
+          <t>https://www.indeed.com/viewjob?jk=05cf4bb1193bec3f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05cf4bb1193bec3f</t>
+          <t>https://www.indeed.com/viewjob?jk=8102d30c9db848fa</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Data Engineering Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8102d30c9db848fa</t>
+          <t>https://www.indeed.com/viewjob?jk=8a16e3ffc1c278fc</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineering Architect</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a16e3ffc1c278fc</t>
+          <t>https://www.indeed.com/viewjob?jk=487e755470e0a906</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Forward Deployed Engineer (AI) - Frisco, TX</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=487e755470e0a906</t>
+          <t>https://www.indeed.com/viewjob?jk=f8e491698172a68a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Forward Deployed Engineer (AI)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc63eb13d50f0ab</t>
+          <t>https://www.indeed.com/viewjob?jk=9389c7fce7ffb417</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3004d47870448a1</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc63eb13d50f0ab</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AI) - Frisco, TX</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Invovia</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8e491698172a68a</t>
+          <t>https://www.indeed.com/viewjob?jk=845986ee9c384d0c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AI)</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Invovia</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9389c7fce7ffb417</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9bc641ca30ce01</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Sr. Data Engineer - Cloud, AWS and Snowflake</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=845986ee9c384d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=b4be1c8e67e2a1f2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Sr. Software Engineer- Data &amp; Integration</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9bc641ca30ce01</t>
+          <t>https://www.indeed.com/viewjob?jk=cccab38c68c6dc6f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Cloud, AWS and Snowflake</t>
+          <t>Sr. IT Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4be1c8e67e2a1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=d0debfb86cec6f81</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Data &amp; Integration</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cccab38c68c6dc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=18e522d64598216a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. IT Data Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0debfb86cec6f81</t>
+          <t>https://www.indeed.com/viewjob?jk=3979f77f1eb1efbc</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Marketing Technology Strategist</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Phase2</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e522d64598216a</t>
+          <t>https://www.indeed.com/viewjob?jk=08cde2c4527579db</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Engineer - Oracle data integrator and BI</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3979f77f1eb1efbc</t>
+          <t>https://www.indeed.com/viewjob?jk=4b40de561865171b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Marketing Technology Strategist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Phase2</t>
+          <t>Entertainment Partners</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, NoSQL, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08cde2c4527579db</t>
+          <t>https://www.indeed.com/viewjob?jk=597ab0eb363227ed</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer - Oracle data integrator and BI</t>
+          <t>Data Engineer- Hybrid</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b40de561865171b</t>
+          <t>https://www.indeed.com/viewjob?jk=936d9e38993af00c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Entertainment Partners</t>
+          <t>Dental Care Alliance</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, NoSQL, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Scala, SQL Server, NoSQL, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597ab0eb363227ed</t>
+          <t>https://www.indeed.com/viewjob?jk=8f835ab35442d7c1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Security Architect(AI)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Dental Care Alliance</t>
+          <t>Paylocity</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, NoSQL, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f835ab35442d7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=7b6040d8fca19b2e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Security Architect(AI)</t>
+          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Paylocity</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b6040d8fca19b2e</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6911722171aa1c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Hunter)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1f7af295967ab5</t>
+          <t>https://www.indeed.com/viewjob?jk=14d4be214d89c9f3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Security Architect(AI)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Paylocity</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ffe1515831234d9</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd7b858f4e17691</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Product Engineer - Fusion GRC Platform</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Afficiency</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MLflow, Terraform, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef44df6379fa49ce</t>
+          <t>https://www.indeed.com/viewjob?jk=be5a298b53e539ed</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Architect of Data Architecture</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Empower</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d4be214d89c9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=2a69b442d48a997e</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Developer Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>giggs</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Studio City, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,17 +3776,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd7b858f4e17691</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac26f490d494d59</t>
         </is>
       </c>
     </row>
@@ -3863,17 +3863,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Product Engineer - Fusion GRC Platform</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90454ed63602f69</t>
+          <t>https://www.indeed.com/viewjob?jk=ef44df6379fa49ce</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Architect of Data Architecture</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Empower</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a69b442d48a997e</t>
+          <t>https://www.indeed.com/viewjob?jk=c90454ed63602f69</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Afficiency</t>
+          <t>PI Security LLC</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MLflow, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be5a298b53e539ed</t>
+          <t>https://www.indeed.com/viewjob?jk=ed01df22f7b5ad6f</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PI Security LLC</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed01df22f7b5ad6f</t>
+          <t>https://www.indeed.com/viewjob?jk=c629002dbb52205d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Data Engineer IV (Snowflake/Databricks) - REMOTE</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Velera</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c629002dbb52205d</t>
+          <t>https://www.indeed.com/viewjob?jk=fd204a1167efc6a3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer IV (Snowflake/Databricks) - REMOTE</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Velera</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd204a1167efc6a3</t>
+          <t>https://www.indeed.com/viewjob?jk=c2df343ab9d22ccf</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>SugarAI</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d697f334d121ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=51c067e768a2b9f2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineer Seniors III (Databricks)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2df343ab9d22ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=89625a5f68a2c750</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SugarAI</t>
+          <t>Safelite</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51c067e768a2b9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=89f11f71a1c806a8</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Engineer Seniors III (Databricks)</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89625a5f68a2c750</t>
+          <t>https://www.indeed.com/viewjob?jk=4aab6a4a6b438005</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Safelite</t>
+          <t>Health Data Analytics Institute</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dedham, MA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,19 +4241,19 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89f11f71a1c806a8</t>
+          <t>https://www.indeed.com/viewjob?jk=073c59c0c666dd26</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Engineer (Oracle)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aab6a4a6b438005</t>
+          <t>https://www.indeed.com/viewjob?jk=7673be72cf2a7f02</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer – Enterprise, Data &amp; AI</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>Zoox</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+          <t>RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073c59c0c666dd26</t>
+          <t>https://www.indeed.com/viewjob?jk=303390f40d7bb17a</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Oracle)</t>
+          <t>Senior Data Integration Operations Engineerr</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Northeastern University</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Snowflake, Informatica PowerCenter, ETL, ELT</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7673be72cf2a7f02</t>
+          <t>https://www.indeed.com/viewjob?jk=748fc639b3268939</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise, Data &amp; AI</t>
+          <t>Sr. Data Engineering Architect</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Zoox</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303390f40d7bb17a</t>
+          <t>https://www.indeed.com/viewjob?jk=b6af42e024fb5358</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Integration Operations Engineerr</t>
+          <t>Cloud Architect @ Dallas, TX</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Logistic Solutions Inc</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Snowflake, Informatica PowerCenter, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=748fc639b3268939</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ffb721ba3a7f68</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Data Engineering Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
+          <t>RDS, Azure, Databricks, GCP, Scala, Data Modeling, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6af42e024fb5358</t>
+          <t>https://www.indeed.com/viewjob?jk=445e8b11f533b240</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Cloud Architect @ Dallas, TX</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Logistic Solutions Inc</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ffb721ba3a7f68</t>
+          <t>https://www.indeed.com/viewjob?jk=ff9ef03bf06139c6</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Engineer I- Data &amp; Insights Engineering</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>Aledade, Inc.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2545dd224fcef4a</t>
+          <t>https://www.indeed.com/viewjob?jk=15c358b482d33d6d</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sr. Cloud Security Engineer (Remote)</t>
+          <t>Level 2 – Technical Support Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47913b36a9ddd604</t>
+          <t>https://www.indeed.com/viewjob?jk=f92c2bb95c010dd6</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer - &amp; Modeler Informatica</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Scala, Data Modeling, ETL, ELT, Power BI, Git</t>
+          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445e8b11f533b240</t>
+          <t>https://www.indeed.com/viewjob?jk=aebf504e442ce2f2</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Bi Developer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,147 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff9ef03bf06139c6</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer I- Data &amp; Insights Engineering</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Aledade, Inc.</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15c358b482d33d6d</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Data Engineer - &amp; Modeler Informatica</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aebf504e442ce2f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Bi Developer</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Cloud and Things</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Albany, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=b85dd5750a229b32</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Level 2 – Technical Support Engineer</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT, REST API integration</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f92c2bb95c010dd6</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-14.xlsx
+++ b/results/job_matches_2026-07-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Native Builder_EU</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Entertainment Partners</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,42 +1606,42 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea4fc6a360496ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e42eebf957e43408</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer-Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2df1f2e18d690c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=6310ba46fd00a82c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer-Specialist</t>
+          <t>Senior Data Engineer I</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>C2FO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, Redshift, Spark, Scala, Kafka, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d896c15ac717e14c</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a710f918b88f2b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer-Specialist</t>
+          <t>Application Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,59 +1721,59 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4fe4e7c9a86b11</t>
+          <t>https://www.indeed.com/viewjob?jk=53d521f5fad271b9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Senior Data Scientist - AI/ML</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Entertainment Partners</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42eebf957e43408</t>
+          <t>https://www.indeed.com/viewjob?jk=aa005e3343082c96</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Artificial Intelligence (AI) Senior Data Scientist</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6310ba46fd00a82c</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9ea8d31a8815a9</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I</t>
+          <t>Engineering Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>C2FO</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Spark, Scala, Kafka, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a710f918b88f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=e831741c10ec9a8d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Application Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, IAM, RDS, Databricks, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,102 +1861,102 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d521f5fad271b9</t>
+          <t>https://www.indeed.com/viewjob?jk=439c58ad35a8bb78</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - AI/ML</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa005e3343082c96</t>
+          <t>https://www.indeed.com/viewjob?jk=41b78df5b95306be</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI) Senior Data Scientist</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Clifton, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9ea8d31a8815a9</t>
+          <t>https://www.indeed.com/viewjob?jk=009aa09bd21a9217</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Engineering Architect</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e831741c10ec9a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ec36958a4f20d5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Safelite</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, IAM, RDS, Databricks, CI/CD</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439c58ad35a8bb78</t>
+          <t>https://www.indeed.com/viewjob?jk=eab9b545c0f88523</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41b78df5b95306be</t>
+          <t>https://www.indeed.com/viewjob?jk=2633a0f0dff514a6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Princ Engr-Ntwk Engring</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Clifton, NJ, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009aa09bd21a9217</t>
+          <t>https://www.indeed.com/viewjob?jk=4e6dbfd3d963c65c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Financial Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>The Research Foundation for The State University of New York at Stony Brook</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Stony Brook, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Hadoop, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ec36958a4f20d5</t>
+          <t>https://www.indeed.com/viewjob?jk=05c72e69c8d1b5df</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Safelite</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Talend</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab9b545c0f88523</t>
+          <t>https://www.indeed.com/viewjob?jk=84ef94552c14d9bd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer II (US)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2633a0f0dff514a6</t>
+          <t>https://www.indeed.com/viewjob?jk=898a5660007f1525</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Princ Engr-Ntwk Engring</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e6dbfd3d963c65c</t>
+          <t>https://www.indeed.com/viewjob?jk=9dcac0248b7373d4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Financial Data &amp; Analytics Engineer</t>
+          <t>Technical Specialist</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The Research Foundation for The State University of New York at Stony Brook</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Stony Brook, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c72e69c8d1b5df</t>
+          <t>https://www.indeed.com/viewjob?jk=91e03219acd75f33</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Technical Specialist(Python Developer)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,14 +2281,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ef94552c14d9bd</t>
+          <t>https://www.indeed.com/viewjob?jk=d26e04dc07674449</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2298,15 +2298,15 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=898a5660007f1525</t>
+          <t>https://www.indeed.com/viewjob?jk=82d983a063892214</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Technical Specialist</t>
+          <t>Data Engineer I-Pathology Molecular and Cell Based Medicine</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e03219acd75f33</t>
+          <t>https://www.indeed.com/viewjob?jk=1f1090f617db00fd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Technical Specialist(Python Developer)</t>
+          <t>Analytics Data Engineer, Cat Digital</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, S3, Azure, Scala, Snowflake, Power BI, CI/CD, Azure DevOps, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d26e04dc07674449</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba56e26d2f7d66e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>Senior System Software Engineer for Cloud – GeForce NOW</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, DynamoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dcac0248b7373d4</t>
+          <t>https://www.indeed.com/viewjob?jk=9d6d30e78e6f4c6e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Specialist - Senior</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82d983a063892214</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfb170c35e948ca</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer I-Pathology Molecular and Cell Based Medicine</t>
+          <t>Senior Java Specialist</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f1090f617db00fd</t>
+          <t>https://www.indeed.com/viewjob?jk=51d97fe985e82f06</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer, Cat Digital</t>
+          <t>Senior Software Engineer - Backend / Cloud Services</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Snowflake, Power BI, CI/CD, Azure DevOps, Airflow, Apache Airflow</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba56e26d2f7d66e</t>
+          <t>https://www.indeed.com/viewjob?jk=18a96d284c8c6745</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior System Software Engineer for Cloud – GeForce NOW</t>
+          <t>Spark Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d6d30e78e6f4c6e</t>
+          <t>https://www.indeed.com/viewjob?jk=e7beab78b75a48b8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Technical Specialist - Senior</t>
+          <t>Senior Data Scientist - GenAI/Agentic AI - Remote</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfb170c35e948ca</t>
+          <t>https://www.indeed.com/viewjob?jk=34b1a1a8543d5bde</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Java Specialist</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51d97fe985e82f06</t>
+          <t>https://www.indeed.com/viewjob?jk=33124af211245233</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend / Cloud Services</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a96d284c8c6745</t>
+          <t>https://www.indeed.com/viewjob?jk=6d7f6a3d55e28770</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - GenAI/Agentic AI - Remote</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>FirstDay Foundation</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34b1a1a8543d5bde</t>
+          <t>https://www.indeed.com/viewjob?jk=d797cade2cc30f67</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>NYSTEC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33124af211245233</t>
+          <t>https://www.indeed.com/viewjob?jk=e43f810dbefdcbc9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d7f6a3d55e28770</t>
+          <t>https://www.indeed.com/viewjob?jk=91f681ba8c58e14f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FirstDay Foundation</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d797cade2cc30f67</t>
+          <t>https://www.indeed.com/viewjob?jk=05cf4bb1193bec3f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer, Quality Engineering, Energy</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NYSTEC</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Brookshire, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43f810dbefdcbc9</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e988ed0beac81e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f681ba8c58e14f</t>
+          <t>https://www.indeed.com/viewjob?jk=8102d30c9db848fa</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>Data Engineering Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05cf4bb1193bec3f</t>
+          <t>https://www.indeed.com/viewjob?jk=8a16e3ffc1c278fc</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8102d30c9db848fa</t>
+          <t>https://www.indeed.com/viewjob?jk=487e755470e0a906</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineering Architect</t>
+          <t>Forward Deployed Engineer (AI) - Frisco, TX</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a16e3ffc1c278fc</t>
+          <t>https://www.indeed.com/viewjob?jk=f8e491698172a68a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Forward Deployed Engineer (AI)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=487e755470e0a906</t>
+          <t>https://www.indeed.com/viewjob?jk=9389c7fce7ffb417</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AI) - Frisco, TX</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Invovia</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8e491698172a68a</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc63eb13d50f0ab</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AI)</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Invovia</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9389c7fce7ffb417</t>
+          <t>https://www.indeed.com/viewjob?jk=845986ee9c384d0c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc63eb13d50f0ab</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9bc641ca30ce01</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Sr. Data Engineer - Cloud, AWS and Snowflake</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=845986ee9c384d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=b4be1c8e67e2a1f2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Sr. Software Engineer- Data &amp; Integration</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9bc641ca30ce01</t>
+          <t>https://www.indeed.com/viewjob?jk=cccab38c68c6dc6f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Cloud, AWS and Snowflake</t>
+          <t>Sr. IT Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4be1c8e67e2a1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=d0debfb86cec6f81</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Data &amp; Integration</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cccab38c68c6dc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=18e522d64598216a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. IT Data Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0debfb86cec6f81</t>
+          <t>https://www.indeed.com/viewjob?jk=3979f77f1eb1efbc</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Marketing Technology Strategist</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Phase2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e522d64598216a</t>
+          <t>https://www.indeed.com/viewjob?jk=08cde2c4527579db</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Engineer - Oracle data integrator and BI</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3979f77f1eb1efbc</t>
+          <t>https://www.indeed.com/viewjob?jk=4b40de561865171b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Marketing Technology Strategist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Phase2</t>
+          <t>Entertainment Partners</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, NoSQL, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08cde2c4527579db</t>
+          <t>https://www.indeed.com/viewjob?jk=597ab0eb363227ed</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer - Oracle data integrator and BI</t>
+          <t>Data Engineer- Hybrid</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b40de561865171b</t>
+          <t>https://www.indeed.com/viewjob?jk=936d9e38993af00c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Entertainment Partners</t>
+          <t>Dental Care Alliance</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, NoSQL, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Scala, SQL Server, NoSQL, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597ab0eb363227ed</t>
+          <t>https://www.indeed.com/viewjob?jk=8f835ab35442d7c1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer- Hybrid</t>
+          <t>Senior Security Architect(AI)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>Paylocity</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936d9e38993af00c</t>
+          <t>https://www.indeed.com/viewjob?jk=7b6040d8fca19b2e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Dental Care Alliance</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, NoSQL, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f835ab35442d7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6911722171aa1c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Security Architect(AI)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Paylocity</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b6040d8fca19b2e</t>
+          <t>https://www.indeed.com/viewjob?jk=14d4be214d89c9f3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6911722171aa1c</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd7b858f4e17691</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Afficiency</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MLflow, Terraform, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d4be214d89c9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=be5a298b53e539ed</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Developer Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>giggs</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Studio City, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd7b858f4e17691</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac26f490d494d59</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Afficiency</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MLflow, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be5a298b53e539ed</t>
+          <t>https://www.indeed.com/viewjob?jk=5a2f1102b97c2bd1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Architect of Data Architecture</t>
+          <t>Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Empower</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a69b442d48a997e</t>
+          <t>https://www.indeed.com/viewjob?jk=91f2cb5787bcd07a</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Developer Engineer</t>
+          <t>Product Engineer - Fusion GRC Platform</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>giggs</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Studio City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac26f490d494d59</t>
+          <t>https://www.indeed.com/viewjob?jk=ef44df6379fa49ce</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a2f1102b97c2bd1</t>
+          <t>https://www.indeed.com/viewjob?jk=c90454ed63602f69</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - SRE</t>
+          <t>Architect of Data Architecture</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Empower</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f2cb5787bcd07a</t>
+          <t>https://www.indeed.com/viewjob?jk=2a69b442d48a997e</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Product Engineer - Fusion GRC Platform</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>PI Security LLC</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, IAM, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,67 +3891,67 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef44df6379fa49ce</t>
+          <t>https://www.indeed.com/viewjob?jk=ed01df22f7b5ad6f</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90454ed63602f69</t>
+          <t>https://www.indeed.com/viewjob?jk=c629002dbb52205d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Data Engineer IV (Snowflake/Databricks) - REMOTE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PI Security LLC</t>
+          <t>Velera</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed01df22f7b5ad6f</t>
+          <t>https://www.indeed.com/viewjob?jk=fd204a1167efc6a3</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c629002dbb52205d</t>
+          <t>https://www.indeed.com/viewjob?jk=c2df343ab9d22ccf</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer IV (Snowflake/Databricks) - REMOTE</t>
+          <t>Senior Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Velera</t>
+          <t>SugarAI</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd204a1167efc6a3</t>
+          <t>https://www.indeed.com/viewjob?jk=51c067e768a2b9f2</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineer Seniors III (Databricks)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2df343ab9d22ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=89625a5f68a2c750</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SugarAI</t>
+          <t>Safelite</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51c067e768a2b9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=89f11f71a1c806a8</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Engineer Seniors III (Databricks)</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89625a5f68a2c750</t>
+          <t>https://www.indeed.com/viewjob?jk=4aab6a4a6b438005</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Safelite</t>
+          <t>Health Data Analytics Institute</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dedham, MA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,19 +4171,19 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89f11f71a1c806a8</t>
+          <t>https://www.indeed.com/viewjob?jk=073c59c0c666dd26</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Engineer (Oracle)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aab6a4a6b438005</t>
+          <t>https://www.indeed.com/viewjob?jk=7673be72cf2a7f02</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer – Enterprise, Data &amp; AI</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>Zoox</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+          <t>RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073c59c0c666dd26</t>
+          <t>https://www.indeed.com/viewjob?jk=303390f40d7bb17a</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Oracle)</t>
+          <t>Senior Data Integration Operations Engineerr</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Northeastern University</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Snowflake, Informatica PowerCenter, ETL, ELT</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7673be72cf2a7f02</t>
+          <t>https://www.indeed.com/viewjob?jk=748fc639b3268939</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise, Data &amp; AI</t>
+          <t>Sr. Data Engineering Architect</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Zoox</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303390f40d7bb17a</t>
+          <t>https://www.indeed.com/viewjob?jk=b6af42e024fb5358</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Integration Operations Engineerr</t>
+          <t>Cloud Architect @ Dallas, TX</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Logistic Solutions Inc</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Snowflake, Informatica PowerCenter, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=748fc639b3268939</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ffb721ba3a7f68</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr. Data Engineering Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
+          <t>RDS, Azure, Databricks, GCP, Scala, Data Modeling, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6af42e024fb5358</t>
+          <t>https://www.indeed.com/viewjob?jk=445e8b11f533b240</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Cloud Architect @ Dallas, TX</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Logistic Solutions Inc</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ffb721ba3a7f68</t>
+          <t>https://www.indeed.com/viewjob?jk=ff9ef03bf06139c6</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer I- Data &amp; Insights Engineering</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Aledade, Inc.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Scala, Data Modeling, ETL, ELT, Power BI, Git</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445e8b11f533b240</t>
+          <t>https://www.indeed.com/viewjob?jk=15c358b482d33d6d</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Level 2 – Technical Support Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff9ef03bf06139c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f92c2bb95c010dd6</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I- Data &amp; Insights Engineering</t>
+          <t>Data Engineer - &amp; Modeler Informatica</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Aledade, Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c358b482d33d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=aebf504e442ce2f2</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Level 2 – Technical Support Engineer</t>
+          <t>Bi Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT, REST API integration</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4555,76 +4555,6 @@
         </is>
       </c>
       <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f92c2bb95c010dd6</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Data Engineer - &amp; Modeler Informatica</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aebf504e442ce2f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Bi Developer</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Cloud and Things</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Albany, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b85dd5750a229b32</t>
         </is>

--- a/results/job_matches_2026-07-14.xlsx
+++ b/results/job_matches_2026-07-14.xlsx
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Clifton, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009aa09bd21a9217</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ec36958a4f20d5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Safelite</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Hadoop, Spark</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ec36958a4f20d5</t>
+          <t>https://www.indeed.com/viewjob?jk=eab9b545c0f88523</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Safelite</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Talend</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab9b545c0f88523</t>
+          <t>https://www.indeed.com/viewjob?jk=2633a0f0dff514a6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer II (US)</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Buckeye Express</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Northwood, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2633a0f0dff514a6</t>
+          <t>https://www.indeed.com/viewjob?jk=1a019537c9558853</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ef94552c14d9bd</t>
+          <t>https://www.indeed.com/viewjob?jk=898a5660007f1525</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=898a5660007f1525</t>
+          <t>https://www.indeed.com/viewjob?jk=9dcac0248b7373d4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dcac0248b7373d4</t>
+          <t>https://www.indeed.com/viewjob?jk=84ef94552c14d9bd</t>
         </is>
       </c>
     </row>
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7beab78b75a48b8</t>
+          <t>https://www.indeed.com/viewjob?jk=2cb65007f4e4e07a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - GenAI/Agentic AI - Remote</t>
+          <t>Spark Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34b1a1a8543d5bde</t>
+          <t>https://www.indeed.com/viewjob?jk=e7beab78b75a48b8</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Data Scientist - GenAI/Agentic AI - Remote</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33124af211245233</t>
+          <t>https://www.indeed.com/viewjob?jk=34b1a1a8543d5bde</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d7f6a3d55e28770</t>
+          <t>https://www.indeed.com/viewjob?jk=33124af211245233</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FirstDay Foundation</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d797cade2cc30f67</t>
+          <t>https://www.indeed.com/viewjob?jk=6d7f6a3d55e28770</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NYSTEC</t>
+          <t>FirstDay Foundation</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43f810dbefdcbc9</t>
+          <t>https://www.indeed.com/viewjob?jk=d797cade2cc30f67</t>
         </is>
       </c>
     </row>
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>NYSTEC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f681ba8c58e14f</t>
+          <t>https://www.indeed.com/viewjob?jk=e43f810dbefdcbc9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05cf4bb1193bec3f</t>
+          <t>https://www.indeed.com/viewjob?jk=91f681ba8c58e14f</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2953,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AI) - Frisco, TX</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Invovia</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8e491698172a68a</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc63eb13d50f0ab</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AI)</t>
+          <t>Forward Deployed Engineer (AI) - Frisco, TX</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9389c7fce7ffb417</t>
+          <t>https://www.indeed.com/viewjob?jk=f8e491698172a68a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Forward Deployed Engineer (AI)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc63eb13d50f0ab</t>
+          <t>https://www.indeed.com/viewjob?jk=9389c7fce7ffb417</t>
         </is>
       </c>
     </row>
@@ -3618,17 +3618,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Software Developer Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Afficiency</t>
+          <t>giggs</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Studio City, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MLflow, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be5a298b53e539ed</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac26f490d494d59</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Developer Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>giggs</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Studio City, CA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac26f490d494d59</t>
+          <t>https://www.indeed.com/viewjob?jk=5a2f1102b97c2bd1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a2f1102b97c2bd1</t>
+          <t>https://www.indeed.com/viewjob?jk=91f2cb5787bcd07a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - SRE</t>
+          <t>Product Engineer - Fusion GRC Platform</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f2cb5787bcd07a</t>
+          <t>https://www.indeed.com/viewjob?jk=ef44df6379fa49ce</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Product Engineer - Fusion GRC Platform</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef44df6379fa49ce</t>
+          <t>https://www.indeed.com/viewjob?jk=c90454ed63602f69</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Architect of Data Architecture</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Empower</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90454ed63602f69</t>
+          <t>https://www.indeed.com/viewjob?jk=2a69b442d48a997e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Architect of Data Architecture</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Empower</t>
+          <t>Afficiency</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MLflow, Terraform, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a69b442d48a997e</t>
+          <t>https://www.indeed.com/viewjob?jk=be5a298b53e539ed</t>
         </is>
       </c>
     </row>
@@ -4423,17 +4423,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I- Data &amp; Insights Engineering</t>
+          <t>Data Engineer - &amp; Modeler Informatica</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Aledade, Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,29 +4441,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c358b482d33d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=aebf504e442ce2f2</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Level 2 – Technical Support Engineer</t>
+          <t>Senior Software Engineer I- Data &amp; Insights Engineering</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Aledade, Inc.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT, REST API integration</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f92c2bb95c010dd6</t>
+          <t>https://www.indeed.com/viewjob?jk=15c358b482d33d6d</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Engineer - &amp; Modeler Informatica</t>
+          <t>Level 2 – Technical Support Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,17 +4511,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aebf504e442ce2f2</t>
+          <t>https://www.indeed.com/viewjob?jk=f92c2bb95c010dd6</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-14.xlsx
+++ b/results/job_matches_2026-07-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Engineering and Infrastructure)</t>
+          <t>Software Developer, Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aurora Innovation</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b8b74c1db36b82</t>
+          <t>https://www.indeed.com/viewjob?jk=c01d88d0c47a7625</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Developer, Business Intelligence Analyst</t>
+          <t>Senior Data Engineer, AWS Data Platform</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01d88d0c47a7625</t>
+          <t>https://www.indeed.com/viewjob?jk=cfb146f53215cc2b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AWS Data Platform</t>
+          <t>Azure Data Architect (remote US)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>News Corp</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfb146f53215cc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=d584a94be46cf8b0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer I (Data Eng infra)</t>
+          <t>Senior Data Management Professional - Data Engineering - Entities</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aurora Innovation</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,19 +741,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=490f497f5639497d</t>
+          <t>https://www.indeed.com/viewjob?jk=44d437f6ae16eb4d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Management Professional - Data Engineering - Entities</t>
+          <t>Data Quality AI Intern (61_2026.3)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Affinity Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d437f6ae16eb4d</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc7c811d1c4b67c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Quality AI Intern (61_2026.3)</t>
+          <t>AWS Severless Software Engineer III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Affinity Solutions</t>
+          <t>NBME</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc7c811d1c4b67c</t>
+          <t>https://www.indeed.com/viewjob?jk=ce2dc4576aaa8a2e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS Severless Software Engineer III</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NBME</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce2dc4576aaa8a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=59be0306e4985a52</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59be0306e4985a52</t>
+          <t>https://www.indeed.com/viewjob?jk=12264a4762b0f153</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12264a4762b0f153</t>
+          <t>https://www.indeed.com/viewjob?jk=4741b2aaf2ec4639</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4741b2aaf2ec4639</t>
+          <t>https://www.indeed.com/viewjob?jk=c8379cf1d692d007</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8379cf1d692d007</t>
+          <t>https://www.indeed.com/viewjob?jk=9696f4f0c31fbf12</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9696f4f0c31fbf12</t>
+          <t>https://www.indeed.com/viewjob?jk=23fcdad233ea5e6d</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23fcdad233ea5e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=12bdc06f31387ddb</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12bdc06f31387ddb</t>
+          <t>https://www.indeed.com/viewjob?jk=7f457f2be81b9770</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f457f2be81b9770</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c8bee941837486</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c8bee941837486</t>
+          <t>https://www.indeed.com/viewjob?jk=6bce80595c811362</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bce80595c811362</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0cf43be3ae79d3</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0cf43be3ae79d3</t>
+          <t>https://www.indeed.com/viewjob?jk=ade89b18f313e675</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade89b18f313e675</t>
+          <t>https://www.indeed.com/viewjob?jk=cfddcbf296252d6b</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfddcbf296252d6b</t>
+          <t>https://www.indeed.com/viewjob?jk=0aae1d49cd9474ec</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0aae1d49cd9474ec</t>
+          <t>https://www.indeed.com/viewjob?jk=e2866e598e580305</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2866e598e580305</t>
+          <t>https://www.indeed.com/viewjob?jk=c2ffd4ec0a1a5c3a</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ffd4ec0a1a5c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=534c078f01ee2602</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=534c078f01ee2602</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d39a911901dc6d</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d39a911901dc6d</t>
+          <t>https://www.indeed.com/viewjob?jk=a72c1fe63174bbb8</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a72c1fe63174bbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=4bdbc801745a49ec</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Junior Software Engineer- Cloud Cost Optimization</t>
+          <t>Sr. Machine Learning Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Vertex AI, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bdbc801745a49ec</t>
+          <t>https://www.indeed.com/viewjob?jk=c40b7d898d0faad8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Platform Engineer</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Entertainment Partners</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,69 +1571,69 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Vertex AI, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40b7d898d0faad8</t>
+          <t>https://www.indeed.com/viewjob?jk=e42eebf957e43408</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Entertainment Partners</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42eebf957e43408</t>
+          <t>https://www.indeed.com/viewjob?jk=6310ba46fd00a82c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer I</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>C2FO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Redshift, Spark, Scala, Kafka, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6310ba46fd00a82c</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a710f918b88f2b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I</t>
+          <t>Application Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>C2FO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Spark, Scala, Kafka, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, ECS, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a710f918b88f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=53d521f5fad271b9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Application Engineer</t>
+          <t>Senior Data Scientist - AI/ML</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d521f5fad271b9</t>
+          <t>https://www.indeed.com/viewjob?jk=aa005e3343082c96</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - AI/ML</t>
+          <t>Artificial Intelligence (AI) Senior Data Scientist</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa005e3343082c96</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9ea8d31a8815a9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI) Senior Data Scientist</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, IAM, RDS, Databricks, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9ea8d31a8815a9</t>
+          <t>https://www.indeed.com/viewjob?jk=439c58ad35a8bb78</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Engineering Architect</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e831741c10ec9a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ec36958a4f20d5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Safelite</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, IAM, RDS, Databricks, CI/CD</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439c58ad35a8bb78</t>
+          <t>https://www.indeed.com/viewjob?jk=eab9b545c0f88523</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Buckeye Express</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Northwood, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41b78df5b95306be</t>
+          <t>https://www.indeed.com/viewjob?jk=1a019537c9558853</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Hadoop, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ec36958a4f20d5</t>
+          <t>https://www.indeed.com/viewjob?jk=2633a0f0dff514a6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Princ Engr-Ntwk Engring</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Safelite</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab9b545c0f88523</t>
+          <t>https://www.indeed.com/viewjob?jk=4e6dbfd3d963c65c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer II (US)</t>
+          <t>Senior Financial Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>The Research Foundation for The State University of New York at Stony Brook</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Stony Brook, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2633a0f0dff514a6</t>
+          <t>https://www.indeed.com/viewjob?jk=05c72e69c8d1b5df</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Buckeye Express</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northwood, OH, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a019537c9558853</t>
+          <t>https://www.indeed.com/viewjob?jk=898a5660007f1525</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Princ Engr-Ntwk Engring</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e6dbfd3d963c65c</t>
+          <t>https://www.indeed.com/viewjob?jk=84ef94552c14d9bd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Financial Data &amp; Analytics Engineer</t>
+          <t>Technical Specialist</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The Research Foundation for The State University of New York at Stony Brook</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Stony Brook, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c72e69c8d1b5df</t>
+          <t>https://www.indeed.com/viewjob?jk=91e03219acd75f33</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Technical Specialist(Python Developer)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=898a5660007f1525</t>
+          <t>https://www.indeed.com/viewjob?jk=d26e04dc07674449</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dcac0248b7373d4</t>
+          <t>https://www.indeed.com/viewjob?jk=82d983a063892214</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Data Engineer I-Pathology Molecular and Cell Based Medicine</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ef94552c14d9bd</t>
+          <t>https://www.indeed.com/viewjob?jk=1f1090f617db00fd</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Technical Specialist</t>
+          <t>Analytics Data Engineer, Cat Digital</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, S3, Azure, Scala, Snowflake, Power BI, CI/CD, Azure DevOps, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e03219acd75f33</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba56e26d2f7d66e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Technical Specialist(Python Developer)</t>
+          <t>Specialist, Retirement Investment Analytics</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d26e04dc07674449</t>
+          <t>https://www.indeed.com/viewjob?jk=ea8b523875ba47e1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Specialist - Senior</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82d983a063892214</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfb170c35e948ca</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer I-Pathology Molecular and Cell Based Medicine</t>
+          <t>Senior Java Specialist</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,102 +2351,102 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f1090f617db00fd</t>
+          <t>https://www.indeed.com/viewjob?jk=51d97fe985e82f06</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer, Cat Digital</t>
+          <t>Spark Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Snowflake, Power BI, CI/CD, Azure DevOps, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba56e26d2f7d66e</t>
+          <t>https://www.indeed.com/viewjob?jk=2cb65007f4e4e07a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior System Software Engineer for Cloud – GeForce NOW</t>
+          <t>Spark Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d6d30e78e6f4c6e</t>
+          <t>https://www.indeed.com/viewjob?jk=e7beab78b75a48b8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Technical Specialist - Senior</t>
+          <t>Senior Data Scientist - GenAI/Agentic AI - Remote</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfb170c35e948ca</t>
+          <t>https://www.indeed.com/viewjob?jk=34b1a1a8543d5bde</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Java Specialist</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51d97fe985e82f06</t>
+          <t>https://www.indeed.com/viewjob?jk=33124af211245233</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend / Cloud Services</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a96d284c8c6745</t>
+          <t>https://www.indeed.com/viewjob?jk=6d7f6a3d55e28770</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Spark Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>FirstDay Foundation</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cb65007f4e4e07a</t>
+          <t>https://www.indeed.com/viewjob?jk=d797cade2cc30f67</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Spark Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NYSTEC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7beab78b75a48b8</t>
+          <t>https://www.indeed.com/viewjob?jk=e43f810dbefdcbc9</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - GenAI/Agentic AI - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, Power BI</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34b1a1a8543d5bde</t>
+          <t>https://www.indeed.com/viewjob?jk=91f681ba8c58e14f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Sr. Software Engineer, Quality Engineering, Energy</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Brookshire, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33124af211245233</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e988ed0beac81e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d7f6a3d55e28770</t>
+          <t>https://www.indeed.com/viewjob?jk=8102d30c9db848fa</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineering Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FirstDay Foundation</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d797cade2cc30f67</t>
+          <t>https://www.indeed.com/viewjob?jk=8a16e3ffc1c278fc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NYSTEC</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43f810dbefdcbc9</t>
+          <t>https://www.indeed.com/viewjob?jk=487e755470e0a906</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f681ba8c58e14f</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc63eb13d50f0ab</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Quality Engineering, Energy</t>
+          <t>Forward Deployed Engineer (AI) - Frisco, TX</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brookshire, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e988ed0beac81e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8e491698172a68a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Forward Deployed Engineer (AI)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8102d30c9db848fa</t>
+          <t>https://www.indeed.com/viewjob?jk=9389c7fce7ffb417</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineering Architect</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a16e3ffc1c278fc</t>
+          <t>https://www.indeed.com/viewjob?jk=845986ee9c384d0c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=487e755470e0a906</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9bc641ca30ce01</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr. Data Engineer - Cloud, AWS and Snowflake</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc63eb13d50f0ab</t>
+          <t>https://www.indeed.com/viewjob?jk=b4be1c8e67e2a1f2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AI) - Frisco, TX</t>
+          <t>Sr. Software Engineer- Data &amp; Integration</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Invovia</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8e491698172a68a</t>
+          <t>https://www.indeed.com/viewjob?jk=cccab38c68c6dc6f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AI)</t>
+          <t>Sr. IT Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Invovia</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9389c7fce7ffb417</t>
+          <t>https://www.indeed.com/viewjob?jk=d0debfb86cec6f81</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=845986ee9c384d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=18e522d64598216a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9bc641ca30ce01</t>
+          <t>https://www.indeed.com/viewjob?jk=3979f77f1eb1efbc</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Cloud, AWS and Snowflake</t>
+          <t>Marketing Technology Strategist</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Phase2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4be1c8e67e2a1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=08cde2c4527579db</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Data &amp; Integration</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Entertainment Partners</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, NoSQL, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cccab38c68c6dc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=597ab0eb363227ed</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. IT Data Engineer</t>
+          <t>Data Engineer- Hybrid</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0debfb86cec6f81</t>
+          <t>https://www.indeed.com/viewjob?jk=936d9e38993af00c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Dental Care Alliance</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, NoSQL, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e522d64598216a</t>
+          <t>https://www.indeed.com/viewjob?jk=8f835ab35442d7c1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Security Architect(AI)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Paylocity</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3979f77f1eb1efbc</t>
+          <t>https://www.indeed.com/viewjob?jk=7b6040d8fca19b2e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Marketing Technology Strategist</t>
+          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Phase2</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08cde2c4527579db</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6911722171aa1c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer - Oracle data integrator and BI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b40de561865171b</t>
+          <t>https://www.indeed.com/viewjob?jk=14d4be214d89c9f3</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Entertainment Partners</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, NoSQL, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597ab0eb363227ed</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd7b858f4e17691</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer- Hybrid</t>
+          <t>Software Developer Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>giggs</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Studio City, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936d9e38993af00c</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac26f490d494d59</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Dental Care Alliance</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, NoSQL, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,19 +3471,19 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f835ab35442d7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=5a2f1102b97c2bd1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Security Architect(AI)</t>
+          <t>Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Paylocity</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b6040d8fca19b2e</t>
+          <t>https://www.indeed.com/viewjob?jk=91f2cb5787bcd07a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
+          <t>Product Engineer - Fusion GRC Platform</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,14 +3541,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6911722171aa1c</t>
+          <t>https://www.indeed.com/viewjob?jk=ef44df6379fa49ce</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d4be214d89c9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c90454ed63602f69</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Architect of Data Architecture</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Empower</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd7b858f4e17691</t>
+          <t>https://www.indeed.com/viewjob?jk=2a69b442d48a997e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Developer Engineer</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>giggs</t>
+          <t>Afficiency</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Studio City, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,42 +3636,42 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MLflow, Terraform, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac26f490d494d59</t>
+          <t>https://www.indeed.com/viewjob?jk=be5a298b53e539ed</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a2f1102b97c2bd1</t>
+          <t>https://www.indeed.com/viewjob?jk=c629002dbb52205d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - SRE</t>
+          <t>Data Engineer IV (Snowflake/Databricks) - REMOTE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Velera</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f2cb5787bcd07a</t>
+          <t>https://www.indeed.com/viewjob?jk=fd204a1167efc6a3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Product Engineer - Fusion GRC Platform</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,67 +3751,67 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef44df6379fa49ce</t>
+          <t>https://www.indeed.com/viewjob?jk=c2df343ab9d22ccf</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>SugarAI</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90454ed63602f69</t>
+          <t>https://www.indeed.com/viewjob?jk=51c067e768a2b9f2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Architect of Data Architecture</t>
+          <t>Data Engineer Seniors III (Databricks)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Empower</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a69b442d48a997e</t>
+          <t>https://www.indeed.com/viewjob?jk=89625a5f68a2c750</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Afficiency</t>
+          <t>Safelite</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MLflow, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be5a298b53e539ed</t>
+          <t>https://www.indeed.com/viewjob?jk=89f11f71a1c806a8</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PI Security LLC</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed01df22f7b5ad6f</t>
+          <t>https://www.indeed.com/viewjob?jk=4aab6a4a6b438005</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Health Data Analytics Institute</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dedham, MA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c629002dbb52205d</t>
+          <t>https://www.indeed.com/viewjob?jk=073c59c0c666dd26</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer IV (Snowflake/Databricks) - REMOTE</t>
+          <t>Senior Data Engineer (Oracle)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Velera</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd204a1167efc6a3</t>
+          <t>https://www.indeed.com/viewjob?jk=7673be72cf2a7f02</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Engineer – Enterprise, Data &amp; AI</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>Zoox</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2df343ab9d22ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=303390f40d7bb17a</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks</t>
+          <t>[REMOTE] Senior Platform Software Engineer- Oracle Clinical Digital Assistant</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SugarAI</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51c067e768a2b9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=23f3fde4ed90357e</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer Seniors III (Databricks)</t>
+          <t>Sr. Data Engineering Architect</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89625a5f68a2c750</t>
+          <t>https://www.indeed.com/viewjob?jk=b6af42e024fb5358</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Cloud Architect @ Dallas, TX</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Safelite</t>
+          <t>Logistic Solutions Inc</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89f11f71a1c806a8</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ffb721ba3a7f68</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, GCP, Scala, Data Modeling, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aab6a4a6b438005</t>
+          <t>https://www.indeed.com/viewjob?jk=445e8b11f533b240</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer - &amp; Modeler Informatica</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073c59c0c666dd26</t>
+          <t>https://www.indeed.com/viewjob?jk=aebf504e442ce2f2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Oracle)</t>
+          <t>Senior Software Engineer I- Data &amp; Insights Engineering</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Aledade, Inc.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7673be72cf2a7f02</t>
+          <t>https://www.indeed.com/viewjob?jk=15c358b482d33d6d</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise, Data &amp; AI</t>
+          <t>Appian Dev-Reporting &amp; Analytics</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Zoox</t>
+          <t>Department of Finance</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, ETL, Power BI, Tableau, AKS</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303390f40d7bb17a</t>
+          <t>https://www.indeed.com/viewjob?jk=88aacc0c7f29344d</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Data Integration Operations Engineerr</t>
+          <t>Bi Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Snowflake, Informatica PowerCenter, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4275,286 +4275,6 @@
         </is>
       </c>
       <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=748fc639b3268939</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Sr. Data Engineering Architect</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b6af42e024fb5358</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Cloud Architect @ Dallas, TX</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Logistic Solutions Inc</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ffb721ba3a7f68</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Chandler, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Scala, Data Modeling, ETL, ELT, Power BI, Git</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=445e8b11f533b240</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Dearborn, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff9ef03bf06139c6</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Data Engineer - &amp; Modeler Informatica</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aebf504e442ce2f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer I- Data &amp; Insights Engineering</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Aledade, Inc.</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15c358b482d33d6d</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Level 2 – Technical Support Engineer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT, REST API integration</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f92c2bb95c010dd6</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Bi Developer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Cloud and Things</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Albany, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b85dd5750a229b32</t>
         </is>

--- a/results/job_matches_2026-07-14.xlsx
+++ b/results/job_matches_2026-07-14.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -736,24 +736,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d437f6ae16eb4d</t>
+          <t>https://www.indeed.com/viewjob?jk=00a24491194c9938</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Quality AI Intern (61_2026.3)</t>
+          <t>Senior Data Management Professional - Data Engineering - Entities</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Affinity Solutions</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc7c811d1c4b67c</t>
+          <t>https://www.indeed.com/viewjob?jk=44d437f6ae16eb4d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AWS Severless Software Engineer III</t>
+          <t>Data Quality AI Intern (61_2026.3)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NBME</t>
+          <t>Affinity Solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce2dc4576aaa8a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc7c811d1c4b67c</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Entertainment Partners</t>
+          <t>Arbitration Forums Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,102 +1581,102 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42eebf957e43408</t>
+          <t>https://www.indeed.com/viewjob?jk=0c27f2a9eec45412</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Native Developer- Europe</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6310ba46fd00a82c</t>
+          <t>https://www.indeed.com/viewjob?jk=444a0e6bd539f82b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I</t>
+          <t>AI Native Builder-Europe</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>C2FO</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Spark, Scala, Kafka, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a710f918b88f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=ae934e8451ebc14c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Application Engineer</t>
+          <t>AI Native Builder_EU</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d521f5fad271b9</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea4fc6a360496ad</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - AI/ML</t>
+          <t>Forward Deployed Engineer-Specialist</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,19 +1721,19 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa005e3343082c96</t>
+          <t>https://www.indeed.com/viewjob?jk=2df1f2e18d690c4a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI) Senior Data Scientist</t>
+          <t>Forward Deployed Engineer-Specialist</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1742,11 +1742,11 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9ea8d31a8815a9</t>
+          <t>https://www.indeed.com/viewjob?jk=d896c15ac717e14c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Forward Deployed Engineer-Specialist</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, IAM, RDS, Databricks, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439c58ad35a8bb78</t>
+          <t>https://www.indeed.com/viewjob?jk=db4fe4e7c9a86b11</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Entertainment Partners</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Hadoop, Spark</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ec36958a4f20d5</t>
+          <t>https://www.indeed.com/viewjob?jk=e42eebf957e43408</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Safelite</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Talend</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,102 +1861,102 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab9b545c0f88523</t>
+          <t>https://www.indeed.com/viewjob?jk=6310ba46fd00a82c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Senior Data Engineer I</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Buckeye Express</t>
+          <t>C2FO</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Northwood, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Redshift, Spark, Scala, Kafka, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a019537c9558853</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a710f918b88f2b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer II (US)</t>
+          <t>Sr. Data Engineer I</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>iHerb</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, BigQuery, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2633a0f0dff514a6</t>
+          <t>https://www.indeed.com/viewjob?jk=67dc4ab0c6df1a50</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Princ Engr-Ntwk Engring</t>
+          <t>Application Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e6dbfd3d963c65c</t>
+          <t>https://www.indeed.com/viewjob?jk=53d521f5fad271b9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Financial Data &amp; Analytics Engineer</t>
+          <t>Senior Data Scientist - AI/ML</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Research Foundation for The State University of New York at Stony Brook</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Stony Brook, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c72e69c8d1b5df</t>
+          <t>https://www.indeed.com/viewjob?jk=aa005e3343082c96</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Artificial Intelligence (AI) Senior Data Scientist</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=898a5660007f1525</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9ea8d31a8815a9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ef94552c14d9bd</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ec36958a4f20d5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Technical Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Safelite</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e03219acd75f33</t>
+          <t>https://www.indeed.com/viewjob?jk=eab9b545c0f88523</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Technical Specialist(Python Developer)</t>
+          <t>Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d26e04dc07674449</t>
+          <t>https://www.indeed.com/viewjob?jk=2633a0f0dff514a6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Princ Engr-Ntwk Engring</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82d983a063892214</t>
+          <t>https://www.indeed.com/viewjob?jk=4e6dbfd3d963c65c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer I-Pathology Molecular and Cell Based Medicine</t>
+          <t>Senior Financial Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>The Research Foundation for The State University of New York at Stony Brook</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Stony Brook, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f1090f617db00fd</t>
+          <t>https://www.indeed.com/viewjob?jk=05c72e69c8d1b5df</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer, Cat Digital</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Snowflake, Power BI, CI/CD, Azure DevOps, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba56e26d2f7d66e</t>
+          <t>https://www.indeed.com/viewjob?jk=898a5660007f1525</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Specialist, Retirement Investment Analytics</t>
+          <t>Technical Specialist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea8b523875ba47e1</t>
+          <t>https://www.indeed.com/viewjob?jk=91e03219acd75f33</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Technical Specialist - Senior</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfb170c35e948ca</t>
+          <t>https://www.indeed.com/viewjob?jk=84ef94552c14d9bd</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Java Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,137 +2351,137 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51d97fe985e82f06</t>
+          <t>https://www.indeed.com/viewjob?jk=82d983a063892214</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Spark Engineer</t>
+          <t>Data Engineer I-Pathology Molecular and Cell Based Medicine</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cb65007f4e4e07a</t>
+          <t>https://www.indeed.com/viewjob?jk=1f1090f617db00fd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Spark Engineer</t>
+          <t>Analytics Data Engineer, Cat Digital</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, S3, Azure, Scala, Snowflake, Power BI, CI/CD, Azure DevOps, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7beab78b75a48b8</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba56e26d2f7d66e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - GenAI/Agentic AI - Remote</t>
+          <t>Technical Product Management - Cloud Optimization - Remote</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34b1a1a8543d5bde</t>
+          <t>https://www.indeed.com/viewjob?jk=8490d129696b2471</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Specialist, Retirement Investment Analytics</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,199 +2491,199 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33124af211245233</t>
+          <t>https://www.indeed.com/viewjob?jk=ea8b523875ba47e1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d7f6a3d55e28770</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69cd7125f7a833</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FirstDay Foundation</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d797cade2cc30f67</t>
+          <t>https://www.indeed.com/viewjob?jk=c09787e1cb8cb395</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NYSTEC</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43f810dbefdcbc9</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4ad7ea1b58a31e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f681ba8c58e14f</t>
+          <t>https://www.indeed.com/viewjob?jk=1cc726639aa959a6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Quality Engineering, Energy</t>
+          <t>Technical Specialist - Senior</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brookshire, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e988ed0beac81e</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfb170c35e948ca</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Spark Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8102d30c9db848fa</t>
+          <t>https://www.indeed.com/viewjob?jk=2cb65007f4e4e07a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineering Architect</t>
+          <t>Spark Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a16e3ffc1c278fc</t>
+          <t>https://www.indeed.com/viewjob?jk=e7beab78b75a48b8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=487e755470e0a906</t>
+          <t>https://www.indeed.com/viewjob?jk=33124af211245233</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc63eb13d50f0ab</t>
+          <t>https://www.indeed.com/viewjob?jk=6d7f6a3d55e28770</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AI) - Frisco, TX</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Invovia</t>
+          <t>FirstDay Foundation</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8e491698172a68a</t>
+          <t>https://www.indeed.com/viewjob?jk=d797cade2cc30f67</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Invovia</t>
+          <t>NYSTEC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9389c7fce7ffb417</t>
+          <t>https://www.indeed.com/viewjob?jk=e43f810dbefdcbc9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=845986ee9c384d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=91f681ba8c58e14f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Sr. Software Engineer, Quality Engineering, Energy</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Brookshire, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,42 +2936,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9bc641ca30ce01</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e988ed0beac81e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Cloud, AWS and Snowflake</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4be1c8e67e2a1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=8102d30c9db848fa</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Data &amp; Integration</t>
+          <t>Data Engineering Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cccab38c68c6dc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=8a16e3ffc1c278fc</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. IT Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0debfb86cec6f81</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc63eb13d50f0ab</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Forward Deployed Engineer (AI) - Frisco, TX</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e522d64598216a</t>
+          <t>https://www.indeed.com/viewjob?jk=f8e491698172a68a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Forward Deployed Engineer (AI)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3979f77f1eb1efbc</t>
+          <t>https://www.indeed.com/viewjob?jk=9389c7fce7ffb417</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Marketing Technology Strategist</t>
+          <t>Sr. Data Engineer - Cloud, AWS and Snowflake</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Phase2</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08cde2c4527579db</t>
+          <t>https://www.indeed.com/viewjob?jk=b4be1c8e67e2a1f2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr. Software Engineer- Data &amp; Integration</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Entertainment Partners</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, NoSQL, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597ab0eb363227ed</t>
+          <t>https://www.indeed.com/viewjob?jk=cccab38c68c6dc6f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer- Hybrid</t>
+          <t>Sr. IT Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936d9e38993af00c</t>
+          <t>https://www.indeed.com/viewjob?jk=d0debfb86cec6f81</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Dental Care Alliance</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, NoSQL, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f835ab35442d7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=18e522d64598216a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Security Architect(AI)</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Paylocity</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
+          <t>AWS, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b6040d8fca19b2e</t>
+          <t>https://www.indeed.com/viewjob?jk=3979f77f1eb1efbc</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
+          <t>Marketing Technology Strategist</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Phase2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6911722171aa1c</t>
+          <t>https://www.indeed.com/viewjob?jk=08cde2c4527579db</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Entertainment Partners</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, NoSQL, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d4be214d89c9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=597ab0eb363227ed</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer- Hybrid</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd7b858f4e17691</t>
+          <t>https://www.indeed.com/viewjob?jk=936d9e38993af00c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Developer Engineer</t>
+          <t>Senior Security Architect(AI)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>giggs</t>
+          <t>Paylocity</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Studio City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac26f490d494d59</t>
+          <t>https://www.indeed.com/viewjob?jk=7b6040d8fca19b2e</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a2f1102b97c2bd1</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6911722171aa1c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - SRE</t>
+          <t>RPA Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f2cb5787bcd07a</t>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Product Engineer - Fusion GRC Platform</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef44df6379fa49ce</t>
+          <t>https://www.indeed.com/viewjob?jk=5a2f1102b97c2bd1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90454ed63602f69</t>
+          <t>https://www.indeed.com/viewjob?jk=91f2cb5787bcd07a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Architect of Data Architecture</t>
+          <t>Product Engineer - Fusion GRC Platform</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Empower</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a69b442d48a997e</t>
+          <t>https://www.indeed.com/viewjob?jk=ef44df6379fa49ce</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Architect of Data Architecture</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Afficiency</t>
+          <t>Empower</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MLflow, Terraform, Docker</t>
+          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be5a298b53e539ed</t>
+          <t>https://www.indeed.com/viewjob?jk=2a69b442d48a997e</t>
         </is>
       </c>
     </row>
@@ -4108,17 +4108,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Verisure</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Uniontown, OH, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Scala, Data Modeling, ETL, ELT, Power BI, Git</t>
+          <t>AWS, Azure, Scala, SQL Server, REST API integration, Power BI, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445e8b11f533b240</t>
+          <t>https://www.indeed.com/viewjob?jk=c374eb71cdd5829a</t>
         </is>
       </c>
     </row>
@@ -4178,17 +4178,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I- Data &amp; Insights Engineering</t>
+          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Aledade, Inc.</t>
+          <t>Asurion</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,17 +4196,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, AWS CodePipeline, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c358b482d33d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a35189b0c83845</t>
         </is>
       </c>
     </row>
@@ -4248,17 +4248,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Bi Developer</t>
+          <t>Senior Software Engineer I- Data &amp; Insights Engineering</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Aledade, Inc.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI, Tableau</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b85dd5750a229b32</t>
+          <t>https://www.indeed.com/viewjob?jk=15c358b482d33d6d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-14.xlsx
+++ b/results/job_matches_2026-07-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Databricks Solution Architect</t>
+          <t>Cloud Data Engineer II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>BankUnited</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami Lakes, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.9</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture</t>
+          <t>AWS, Glue, Redshift, Athena, Step Functions, RDS, Azure, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95200cc7178deeb2</t>
+          <t>https://www.indeed.com/viewjob?jk=c7dee1b85cc76fb8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer II</t>
+          <t>Cloud Transformation Senior Consultant</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BankUnited</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Miami Lakes, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, Step Functions, RDS, Azure, Hadoop, Spark, PySpark</t>
+          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7dee1b85cc76fb8</t>
+          <t>https://www.indeed.com/viewjob?jk=57362c44cdaea54f</t>
         </is>
       </c>
     </row>
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AWS Data Platform</t>
+          <t>Azure Data Architect (remote US)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>News Corp</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfb146f53215cc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=d584a94be46cf8b0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure Data Architect (remote US)</t>
+          <t>Senior Data Engineer, AWS Data Platform</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>News Corp</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d584a94be46cf8b0</t>
+          <t>https://www.indeed.com/viewjob?jk=cfb146f53215cc2b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Management Professional - Data Engineering - Entities</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,277 +741,277 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a24491194c9938</t>
+          <t>https://www.indeed.com/viewjob?jk=b9be95a71934961d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Management Professional - Data Engineering - Entities</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d437f6ae16eb4d</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf05ce3284e6a20</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Quality AI Intern (61_2026.3)</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Affinity Solutions</t>
+          <t>Itero Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc7c811d1c4b67c</t>
+          <t>https://www.indeed.com/viewjob?jk=e304be37d5897728</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Junior Software Engineer- Cloud Cost Optimization</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Itero Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, Glue, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59be0306e4985a52</t>
+          <t>https://www.indeed.com/viewjob?jk=9724f20b3e8cf9d3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Junior Software Engineer- Cloud Cost Optimization</t>
+          <t>Senior Cloud Database Operations Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Abrigo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12264a4762b0f153</t>
+          <t>https://www.indeed.com/viewjob?jk=d7fae8116d2ca386</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Junior Software Engineer- Cloud Cost Optimization</t>
+          <t>Senior Cloud Database Operations Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Abrigo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4741b2aaf2ec4639</t>
+          <t>https://www.indeed.com/viewjob?jk=3e9a8697ac906001</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Junior Software Engineer- Cloud Cost Optimization</t>
+          <t>Senior Cloud Database Operations Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Abrigo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8379cf1d692d007</t>
+          <t>https://www.indeed.com/viewjob?jk=0dae3ed04ad2bede</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Junior Software Engineer- Cloud Cost Optimization</t>
+          <t>Senior Data Management Professional - Data Engineering - Entities</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9696f4f0c31fbf12</t>
+          <t>https://www.indeed.com/viewjob?jk=00a24491194c9938</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Junior Software Engineer- Cloud Cost Optimization</t>
+          <t>Senior Data Management Professional - Data Engineering - Entities</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,19 +1021,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23fcdad233ea5e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=44d437f6ae16eb4d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Junior Software Engineer- Cloud Cost Optimization</t>
+          <t>Data Quality AI Intern (61_2026.3)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Affinity Solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12bdc06f31387ddb</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc7c811d1c4b67c</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f457f2be81b9770</t>
+          <t>https://www.indeed.com/viewjob?jk=59be0306e4985a52</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c8bee941837486</t>
+          <t>https://www.indeed.com/viewjob?jk=12264a4762b0f153</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bce80595c811362</t>
+          <t>https://www.indeed.com/viewjob?jk=4741b2aaf2ec4639</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0cf43be3ae79d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c8379cf1d692d007</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade89b18f313e675</t>
+          <t>https://www.indeed.com/viewjob?jk=9696f4f0c31fbf12</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfddcbf296252d6b</t>
+          <t>https://www.indeed.com/viewjob?jk=23fcdad233ea5e6d</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0aae1d49cd9474ec</t>
+          <t>https://www.indeed.com/viewjob?jk=12bdc06f31387ddb</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2866e598e580305</t>
+          <t>https://www.indeed.com/viewjob?jk=7f457f2be81b9770</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ffd4ec0a1a5c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c8bee941837486</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=534c078f01ee2602</t>
+          <t>https://www.indeed.com/viewjob?jk=6bce80595c811362</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d39a911901dc6d</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0cf43be3ae79d3</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a72c1fe63174bbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=ade89b18f313e675</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bdbc801745a49ec</t>
+          <t>https://www.indeed.com/viewjob?jk=cfddcbf296252d6b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Platform Engineer</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Vertex AI, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40b7d898d0faad8</t>
+          <t>https://www.indeed.com/viewjob?jk=0aae1d49cd9474ec</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c27f2a9eec45412</t>
+          <t>https://www.indeed.com/viewjob?jk=e2866e598e580305</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Native Developer- Europe</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=444a0e6bd539f82b</t>
+          <t>https://www.indeed.com/viewjob?jk=c2ffd4ec0a1a5c3a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Native Builder-Europe</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae934e8451ebc14c</t>
+          <t>https://www.indeed.com/viewjob?jk=534c078f01ee2602</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Native Builder_EU</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea4fc6a360496ad</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d39a911901dc6d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer-Specialist</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2df1f2e18d690c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=a72c1fe63174bbb8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer-Specialist</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d896c15ac717e14c</t>
+          <t>https://www.indeed.com/viewjob?jk=4bdbc801745a49ec</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer-Specialist</t>
+          <t>Sr. Machine Learning Platform Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Vertex AI, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4fe4e7c9a86b11</t>
+          <t>https://www.indeed.com/viewjob?jk=c40b7d898d0faad8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Entertainment Partners</t>
+          <t>Charter Manufacturing</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Mequon, WI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,172 +1826,172 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42eebf957e43408</t>
+          <t>https://www.indeed.com/viewjob?jk=284985e81accb0a4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Arbitration Forums Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6310ba46fd00a82c</t>
+          <t>https://www.indeed.com/viewjob?jk=0c27f2a9eec45412</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I</t>
+          <t>AI Native Developer- Europe</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>C2FO</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Spark, Scala, Kafka, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a710f918b88f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=444a0e6bd539f82b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer I</t>
+          <t>AI Native Builder-Europe</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>iHerb</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, BigQuery, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67dc4ab0c6df1a50</t>
+          <t>https://www.indeed.com/viewjob?jk=ae934e8451ebc14c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Application Engineer</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Entertainment Partners</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d521f5fad271b9</t>
+          <t>https://www.indeed.com/viewjob?jk=e42eebf957e43408</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - AI/ML</t>
+          <t>AI Native Builder_EU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,19 +2001,19 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa005e3343082c96</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea4fc6a360496ad</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI) Senior Data Scientist</t>
+          <t>Forward Deployed Engineer-Specialist</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2022,11 +2022,11 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9ea8d31a8815a9</t>
+          <t>https://www.indeed.com/viewjob?jk=2df1f2e18d690c4a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Forward Deployed Engineer-Specialist</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Hadoop, Spark</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ec36958a4f20d5</t>
+          <t>https://www.indeed.com/viewjob?jk=d896c15ac717e14c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Forward Deployed Engineer-Specialist</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Safelite</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Talend</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab9b545c0f88523</t>
+          <t>https://www.indeed.com/viewjob?jk=db4fe4e7c9a86b11</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer II (US)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2633a0f0dff514a6</t>
+          <t>https://www.indeed.com/viewjob?jk=6310ba46fd00a82c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Princ Engr-Ntwk Engring</t>
+          <t>Senior Data Engineer I</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>C2FO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Redshift, Spark, Scala, Kafka, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e6dbfd3d963c65c</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a710f918b88f2b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Financial Data &amp; Analytics Engineer</t>
+          <t>Application Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Research Foundation for The State University of New York at Stony Brook</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Stony Brook, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, ECS, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,137 +2211,137 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c72e69c8d1b5df</t>
+          <t>https://www.indeed.com/viewjob?jk=53d521f5fad271b9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr Sales Engineer - US-East</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Perforce Software</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=898a5660007f1525</t>
+          <t>https://www.indeed.com/viewjob?jk=fc6cc2f265b558a0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Technical Specialist</t>
+          <t>Sr Sales Engineer - US-East</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Perforce Software</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e03219acd75f33</t>
+          <t>https://www.indeed.com/viewjob?jk=1e4b3c9272c2a259</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Sr Sales Engineer - US-East</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Perforce Software</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ef94552c14d9bd</t>
+          <t>https://www.indeed.com/viewjob?jk=4036bfdc733445b6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist - AI/ML</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82d983a063892214</t>
+          <t>https://www.indeed.com/viewjob?jk=aa005e3343082c96</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer I-Pathology Molecular and Cell Based Medicine</t>
+          <t>Artificial Intelligence (AI) Senior Data Scientist</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,102 +2386,102 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f1090f617db00fd</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9ea8d31a8815a9</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer, Cat Digital</t>
+          <t>DataHub Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Snowflake, Power BI, CI/CD, Azure DevOps, Airflow, Apache Airflow</t>
+          <t>AWS, S3, IAM, RDS, Azure, Kafka, Kafka Connect, Oracle, MySQL, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba56e26d2f7d66e</t>
+          <t>https://www.indeed.com/viewjob?jk=5423277344900438</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Technical Product Management - Cloud Optimization - Remote</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8490d129696b2471</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ec36958a4f20d5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Specialist, Retirement Investment Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Safelite</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,172 +2491,172 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea8b523875ba47e1</t>
+          <t>https://www.indeed.com/viewjob?jk=eab9b545c0f88523</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe69cd7125f7a833</t>
+          <t>https://www.indeed.com/viewjob?jk=2633a0f0dff514a6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Princ Engr-Ntwk Engring</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c09787e1cb8cb395</t>
+          <t>https://www.indeed.com/viewjob?jk=4e6dbfd3d963c65c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Financial Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>The Research Foundation for The State University of New York at Stony Brook</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Stony Brook, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4ad7ea1b58a31e</t>
+          <t>https://www.indeed.com/viewjob?jk=05c72e69c8d1b5df</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cc726639aa959a6</t>
+          <t>https://www.indeed.com/viewjob?jk=84ef94552c14d9bd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Technical Specialist - Senior</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,242 +2666,242 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfb170c35e948ca</t>
+          <t>https://www.indeed.com/viewjob?jk=898a5660007f1525</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Spark Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cb65007f4e4e07a</t>
+          <t>https://www.indeed.com/viewjob?jk=82d983a063892214</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Spark Engineer</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Escalent</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7beab78b75a48b8</t>
+          <t>https://www.indeed.com/viewjob?jk=45d62ba2dc0bd875</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33124af211245233</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69cd7125f7a833</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d7f6a3d55e28770</t>
+          <t>https://www.indeed.com/viewjob?jk=c09787e1cb8cb395</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FirstDay Foundation</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d797cade2cc30f67</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4ad7ea1b58a31e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NYSTEC</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43f810dbefdcbc9</t>
+          <t>https://www.indeed.com/viewjob?jk=1cc726639aa959a6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Specialist, Retirement Investment Analytics</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f681ba8c58e14f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea8b523875ba47e1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Quality Engineering, Energy</t>
+          <t>Spark Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brookshire, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e988ed0beac81e</t>
+          <t>https://www.indeed.com/viewjob?jk=2cb65007f4e4e07a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Spark Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8102d30c9db848fa</t>
+          <t>https://www.indeed.com/viewjob?jk=e7beab78b75a48b8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineering Architect</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a16e3ffc1c278fc</t>
+          <t>https://www.indeed.com/viewjob?jk=33124af211245233</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc63eb13d50f0ab</t>
+          <t>https://www.indeed.com/viewjob?jk=6d7f6a3d55e28770</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AI) - Frisco, TX</t>
+          <t>Sr. Software Engineer, Quality Engineering, Energy</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Invovia</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Brookshire, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,24 +3076,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8e491698172a68a</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e988ed0beac81e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AI)</t>
+          <t>Forward Deployed Engineer (AI) - Frisco, TX</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9389c7fce7ffb417</t>
+          <t>https://www.indeed.com/viewjob?jk=f8e491698172a68a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Cloud, AWS and Snowflake</t>
+          <t>Forward Deployed Engineer (AI)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,67 +3156,67 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4be1c8e67e2a1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=9389c7fce7ffb417</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Data &amp; Integration</t>
+          <t>Sigma Report Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Tachyon Technologies</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cccab38c68c6dc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8d0798b16bd29a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. IT Data Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0debfb86cec6f81</t>
+          <t>https://www.indeed.com/viewjob?jk=8102d30c9db848fa</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e522d64598216a</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc63eb13d50f0ab</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Sr. Data Engineer - Cloud, AWS and Snowflake</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3979f77f1eb1efbc</t>
+          <t>https://www.indeed.com/viewjob?jk=b4be1c8e67e2a1f2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Marketing Technology Strategist</t>
+          <t>Sr. Software Engineer- Data &amp; Integration</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Phase2</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08cde2c4527579db</t>
+          <t>https://www.indeed.com/viewjob?jk=cccab38c68c6dc6f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Entertainment Partners</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, NoSQL, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, PySpark, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597ab0eb363227ed</t>
+          <t>https://www.indeed.com/viewjob?jk=4223c8030b51f20b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer- Hybrid</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936d9e38993af00c</t>
+          <t>https://www.indeed.com/viewjob?jk=3979f77f1eb1efbc</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Security Architect(AI)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Paylocity</t>
+          <t>Entertainment Partners</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, NoSQL, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b6040d8fca19b2e</t>
+          <t>https://www.indeed.com/viewjob?jk=597ab0eb363227ed</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
+          <t>Data Engineer- Hybrid</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6911722171aa1c</t>
+          <t>https://www.indeed.com/viewjob?jk=936d9e38993af00c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>RPA Engineer</t>
+          <t>Full Stack Developer III - Private Markets Applications</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+          <t>https://www.indeed.com/viewjob?jk=04f2e93224c9a790</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a2f1102b97c2bd1</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6911722171aa1c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - SRE</t>
+          <t>Senior .NET and SSRS Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f2cb5787bcd07a</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c8883b0dd19abf</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Product Engineer - Fusion GRC Platform</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Dental Care Alliance</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Scala, SQL Server, NoSQL, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef44df6379fa49ce</t>
+          <t>https://www.indeed.com/viewjob?jk=8f835ab35442d7c1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Architect of Data Architecture</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Empower</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,287 +3636,287 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a69b442d48a997e</t>
+          <t>https://www.indeed.com/viewjob?jk=032b8db4bfd5e6d8</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c629002dbb52205d</t>
+          <t>https://www.indeed.com/viewjob?jk=46f856d080d24d05</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer IV (Snowflake/Databricks) - REMOTE</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Velera</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd204a1167efc6a3</t>
+          <t>https://www.indeed.com/viewjob?jk=19153bb3202f8519</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2df343ab9d22ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=ee7a2d23cf0b0fbe</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SugarAI</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51c067e768a2b9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=00a3e62df8c707d8</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer Seniors III (Databricks)</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89625a5f68a2c750</t>
+          <t>https://www.indeed.com/viewjob?jk=779a1a0a5eccc32e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Safelite</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89f11f71a1c806a8</t>
+          <t>https://www.indeed.com/viewjob?jk=8993a2c0de0e70e1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>RPA Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aab6a4a6b438005</t>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,14 +3926,14 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073c59c0c666dd26</t>
+          <t>https://www.indeed.com/viewjob?jk=5a2f1102b97c2bd1</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Oracle)</t>
+          <t>Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3947,11 +3947,11 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7673be72cf2a7f02</t>
+          <t>https://www.indeed.com/viewjob?jk=91f2cb5787bcd07a</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise, Data &amp; AI</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Zoox</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, Terraform, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303390f40d7bb17a</t>
+          <t>https://www.indeed.com/viewjob?jk=c629002dbb52205d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>[REMOTE] Senior Platform Software Engineer- Oracle Clinical Digital Assistant</t>
+          <t>Data Engineer IV (Snowflake/Databricks) - REMOTE</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Velera</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f3fde4ed90357e</t>
+          <t>https://www.indeed.com/viewjob?jk=fd204a1167efc6a3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. Data Engineering Architect</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6af42e024fb5358</t>
+          <t>https://www.indeed.com/viewjob?jk=c2df343ab9d22ccf</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Cloud Architect @ Dallas, TX</t>
+          <t>Senior Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Logistic Solutions Inc</t>
+          <t>SugarAI</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ffb721ba3a7f68</t>
+          <t>https://www.indeed.com/viewjob?jk=51c067e768a2b9f2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer Seniors III (Databricks)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Verisure</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Uniontown, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, REST API integration, Power BI, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c374eb71cdd5829a</t>
+          <t>https://www.indeed.com/viewjob?jk=89625a5f68a2c750</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer - &amp; Modeler Informatica</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Safelite</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aebf504e442ce2f2</t>
+          <t>https://www.indeed.com/viewjob?jk=89f11f71a1c806a8</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Asurion</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, AWS CodePipeline, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a35189b0c83845</t>
+          <t>https://www.indeed.com/viewjob?jk=4aab6a4a6b438005</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Appian Dev-Reporting &amp; Analytics</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Department of Finance</t>
+          <t>Health Data Analytics Institute</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Dedham, MA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, ETL, Power BI, Tableau, AKS</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88aacc0c7f29344d</t>
+          <t>https://www.indeed.com/viewjob?jk=073c59c0c666dd26</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I- Data &amp; Insights Engineering</t>
+          <t>Senior Data Engineer (Oracle)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Aledade, Inc.</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,17 +4266,297 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7673be72cf2a7f02</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Solutions Engineer - Data Visualization</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SHI International</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7cfe4bd64f8f496f</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>[REMOTE] Senior Platform Software Engineer- Oracle Clinical Digital Assistant</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23f3fde4ed90357e</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer I- Data &amp; Insights Engineering</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Aledade, Inc.</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
           <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=15c358b482d33d6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineering Architect</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b6af42e024fb5358</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Cloud Architect @ Dallas, TX</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Logistic Solutions Inc</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1ffb721ba3a7f68</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Appian Dev-Reporting &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Department of Finance</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Manhattan, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, ETL, Power BI, Tableau, AKS</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88aacc0c7f29344d</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Verisure</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Uniontown, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, SQL Server, REST API integration, Power BI, CI/CD, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c374eb71cdd5829a</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Asurion</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Sterling, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, AWS CodePipeline, Docker</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4a35189b0c83845</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-14.xlsx
+++ b/results/job_matches_2026-07-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Junior Architect / Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Winfo Solutions</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1691b4d7b52de9</t>
+          <t>https://www.indeed.com/viewjob?jk=7e53a2ba6f9a4021</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Developer, Business Intelligence Analyst</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Winfo Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01d88d0c47a7625</t>
+          <t>https://www.indeed.com/viewjob?jk=0c1691b4d7b52de9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Azure Data Architect (remote US)</t>
+          <t>Software Developer, Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>News Corp</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d584a94be46cf8b0</t>
+          <t>https://www.indeed.com/viewjob?jk=c01d88d0c47a7625</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AWS Data Platform</t>
+          <t>Azure Data Architect (remote US)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>News Corp</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,52 +696,52 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfb146f53215cc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=d584a94be46cf8b0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Senior Data Engineer, AWS Data Platform</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9be95a71934961d</t>
+          <t>https://www.indeed.com/viewjob?jk=cfb146f53215cc2b</t>
         </is>
       </c>
     </row>
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf05ce3284e6a20</t>
+          <t>https://www.indeed.com/viewjob?jk=b9be95a71934961d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Itero Group</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e304be37d5897728</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf05ce3284e6a20</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9724f20b3e8cf9d3</t>
+          <t>https://www.indeed.com/viewjob?jk=e304be37d5897728</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Operations Engineer</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Abrigo</t>
+          <t>Itero Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7fae8116d2ca386</t>
+          <t>https://www.indeed.com/viewjob?jk=9724f20b3e8cf9d3</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e9a8697ac906001</t>
+          <t>https://www.indeed.com/viewjob?jk=d7fae8116d2ca386</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dae3ed04ad2bede</t>
+          <t>https://www.indeed.com/viewjob?jk=3e9a8697ac906001</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Management Professional - Data Engineering - Entities</t>
+          <t>Senior Cloud Database Operations Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Abrigo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a24491194c9938</t>
+          <t>https://www.indeed.com/viewjob?jk=0dae3ed04ad2bede</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1016,24 +1016,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d437f6ae16eb4d</t>
+          <t>https://www.indeed.com/viewjob?jk=00a24491194c9938</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Quality AI Intern (61_2026.3)</t>
+          <t>Senior Data Management Professional - Data Engineering - Entities</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Affinity Solutions</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1046,69 +1046,69 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc7c811d1c4b67c</t>
+          <t>https://www.indeed.com/viewjob?jk=44d437f6ae16eb4d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Junior Software Engineer- Cloud Cost Optimization</t>
+          <t>Data Quality AI Intern (61_2026.3)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Affinity Solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59be0306e4985a52</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc7c811d1c4b67c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Junior Software Engineer- Cloud Cost Optimization</t>
+          <t>Senior Cloud Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12264a4762b0f153</t>
+          <t>https://www.indeed.com/viewjob?jk=0426c9944a6312e8</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4741b2aaf2ec4639</t>
+          <t>https://www.indeed.com/viewjob?jk=59be0306e4985a52</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8379cf1d692d007</t>
+          <t>https://www.indeed.com/viewjob?jk=12264a4762b0f153</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9696f4f0c31fbf12</t>
+          <t>https://www.indeed.com/viewjob?jk=4741b2aaf2ec4639</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23fcdad233ea5e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=c8379cf1d692d007</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12bdc06f31387ddb</t>
+          <t>https://www.indeed.com/viewjob?jk=9696f4f0c31fbf12</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f457f2be81b9770</t>
+          <t>https://www.indeed.com/viewjob?jk=23fcdad233ea5e6d</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c8bee941837486</t>
+          <t>https://www.indeed.com/viewjob?jk=12bdc06f31387ddb</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bce80595c811362</t>
+          <t>https://www.indeed.com/viewjob?jk=7f457f2be81b9770</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0cf43be3ae79d3</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c8bee941837486</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade89b18f313e675</t>
+          <t>https://www.indeed.com/viewjob?jk=6bce80595c811362</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfddcbf296252d6b</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0cf43be3ae79d3</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0aae1d49cd9474ec</t>
+          <t>https://www.indeed.com/viewjob?jk=ade89b18f313e675</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2866e598e580305</t>
+          <t>https://www.indeed.com/viewjob?jk=cfddcbf296252d6b</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ffd4ec0a1a5c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=0aae1d49cd9474ec</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=534c078f01ee2602</t>
+          <t>https://www.indeed.com/viewjob?jk=e2866e598e580305</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d39a911901dc6d</t>
+          <t>https://www.indeed.com/viewjob?jk=c2ffd4ec0a1a5c3a</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a72c1fe63174bbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=534c078f01ee2602</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bdbc801745a49ec</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d39a911901dc6d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Platform Engineer</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Vertex AI, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40b7d898d0faad8</t>
+          <t>https://www.indeed.com/viewjob?jk=a72c1fe63174bbb8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Charter Manufacturing</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mequon, WI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=284985e81accb0a4</t>
+          <t>https://www.indeed.com/viewjob?jk=4bdbc801745a49ec</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Native Developer- Europe</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Charter Manufacturing</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mequon, WI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,14 +1896,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=444a0e6bd539f82b</t>
+          <t>https://www.indeed.com/viewjob?jk=284985e81accb0a4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Native Builder-Europe</t>
+          <t>AI Native Developer- Europe</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae934e8451ebc14c</t>
+          <t>https://www.indeed.com/viewjob?jk=444a0e6bd539f82b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>AI Native Builder-Europe</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Entertainment Partners</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42eebf957e43408</t>
+          <t>https://www.indeed.com/viewjob?jk=ae934e8451ebc14c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Native Builder_EU</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Entertainment Partners</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,24 +1991,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea4fc6a360496ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e42eebf957e43408</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer-Specialist</t>
+          <t>AI Native Builder_EU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2df1f2e18d690c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea4fc6a360496ad</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d896c15ac717e14c</t>
+          <t>https://www.indeed.com/viewjob?jk=2df1f2e18d690c4a</t>
         </is>
       </c>
     </row>
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4fe4e7c9a86b11</t>
+          <t>https://www.indeed.com/viewjob?jk=d896c15ac717e14c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Forward Deployed Engineer-Specialist</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6310ba46fd00a82c</t>
+          <t>https://www.indeed.com/viewjob?jk=db4fe4e7c9a86b11</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>C2FO</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Spark, Scala, Kafka, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a710f918b88f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=6310ba46fd00a82c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Application Engineer</t>
+          <t>Senior Data Engineer I</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>C2FO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Glue, Redshift, Spark, Scala, Kafka, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d521f5fad271b9</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a710f918b88f2b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Sales Engineer - US-East</t>
+          <t>Application Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Perforce Software</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc6cc2f265b558a0</t>
+          <t>https://www.indeed.com/viewjob?jk=53d521f5fad271b9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Sales Engineer - US-East</t>
+          <t>Senior Data Scientist - AI/ML</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Perforce Software</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e4b3c9272c2a259</t>
+          <t>https://www.indeed.com/viewjob?jk=aa005e3343082c96</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Sales Engineer - US-East</t>
+          <t>Artificial Intelligence (AI) Senior Data Scientist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Perforce Software</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,29 +2306,29 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4036bfdc733445b6</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9ea8d31a8815a9</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - AI/ML</t>
+          <t>DataHub Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2337,46 +2337,46 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, S3, IAM, RDS, Azure, Kafka, Kafka Connect, Oracle, MySQL, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa005e3343082c96</t>
+          <t>https://www.indeed.com/viewjob?jk=5423277344900438</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI) Senior Data Scientist</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9ea8d31a8815a9</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ec36958a4f20d5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DataHub Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Safelite</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Kafka, Kafka Connect, Oracle, MySQL, ETL</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5423277344900438</t>
+          <t>https://www.indeed.com/viewjob?jk=eab9b545c0f88523</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Quality Engineer - FY27</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Hadoop, Spark</t>
+          <t>AWS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, CodeBuild</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ec36958a4f20d5</t>
+          <t>https://www.indeed.com/viewjob?jk=754540310d15df69</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Safelite</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Talend</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab9b545c0f88523</t>
+          <t>https://www.indeed.com/viewjob?jk=2633a0f0dff514a6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer II (US)</t>
+          <t>Princ Engr-Ntwk Engring</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2633a0f0dff514a6</t>
+          <t>https://www.indeed.com/viewjob?jk=4e6dbfd3d963c65c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Princ Engr-Ntwk Engring</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,129 +2561,129 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e6dbfd3d963c65c</t>
+          <t>https://www.indeed.com/viewjob?jk=84ef94552c14d9bd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Financial Data &amp; Analytics Engineer</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Research Foundation for The State University of New York at Stony Brook</t>
+          <t>Escalent</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Stony Brook, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c72e69c8d1b5df</t>
+          <t>https://www.indeed.com/viewjob?jk=45d62ba2dc0bd875</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ef94552c14d9bd</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69cd7125f7a833</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=898a5660007f1525</t>
+          <t>https://www.indeed.com/viewjob?jk=c09787e1cb8cb395</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82d983a063892214</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4ad7ea1b58a31e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Escalent</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,42 +2726,42 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45d62ba2dc0bd875</t>
+          <t>https://www.indeed.com/viewjob?jk=1cc726639aa959a6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Spark Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe69cd7125f7a833</t>
+          <t>https://www.indeed.com/viewjob?jk=2cb65007f4e4e07a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Spark Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,67 +2806,67 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c09787e1cb8cb395</t>
+          <t>https://www.indeed.com/viewjob?jk=e7beab78b75a48b8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4ad7ea1b58a31e</t>
+          <t>https://www.indeed.com/viewjob?jk=33124af211245233</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>El Toro.com</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,59 +2876,59 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cc726639aa959a6</t>
+          <t>https://www.indeed.com/viewjob?jk=d42d84e2b583adb0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Specialist, Retirement Investment Analytics</t>
+          <t>Sr. Software Engineer, Quality Engineering, Energy</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Brookshire, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea8b523875ba47e1</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e988ed0beac81e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Spark Engineer</t>
+          <t>Sigma Report Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tachyon Technologies</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cb65007f4e4e07a</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8d0798b16bd29a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Spark Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,77 +2971,77 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7beab78b75a48b8</t>
+          <t>https://www.indeed.com/viewjob?jk=8102d30c9db848fa</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, PySpark, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33124af211245233</t>
+          <t>https://www.indeed.com/viewjob?jk=4223c8030b51f20b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,234 +3051,234 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d7f6a3d55e28770</t>
+          <t>https://www.indeed.com/viewjob?jk=3979f77f1eb1efbc</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Quality Engineering, Energy</t>
+          <t>Sr. Data Engineer - Cloud, AWS and Snowflake</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brookshire, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e988ed0beac81e</t>
+          <t>https://www.indeed.com/viewjob?jk=b4be1c8e67e2a1f2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AI) - Frisco, TX</t>
+          <t>2026-2027 Information Technology - Software Engineer - Full-Time</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Invovia</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8e491698172a68a</t>
+          <t>https://www.indeed.com/viewjob?jk=d6578ea1eb5e5142</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AI)</t>
+          <t>Full Stack Developer III - Private Markets Applications</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Invovia</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9389c7fce7ffb417</t>
+          <t>https://www.indeed.com/viewjob?jk=04f2e93224c9a790</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sigma Report Developer</t>
+          <t>Data Engineer- Hybrid</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tachyon Technologies</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8d0798b16bd29a</t>
+          <t>https://www.indeed.com/viewjob?jk=936d9e38993af00c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>2026-2027 Information Technology - Software Engineer - Intern</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8102d30c9db848fa</t>
+          <t>https://www.indeed.com/viewjob?jk=eab14599c79da82b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior .NET and SSRS Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc63eb13d50f0ab</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c8883b0dd19abf</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Cloud, AWS and Snowflake</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4be1c8e67e2a1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=032b8db4bfd5e6d8</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Data &amp; Integration</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cccab38c68c6dc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=46f856d080d24d05</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, PySpark, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4223c8030b51f20b</t>
+          <t>https://www.indeed.com/viewjob?jk=19153bb3202f8519</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3979f77f1eb1efbc</t>
+          <t>https://www.indeed.com/viewjob?jk=ee7a2d23cf0b0fbe</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Entertainment Partners</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, NoSQL, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597ab0eb363227ed</t>
+          <t>https://www.indeed.com/viewjob?jk=00a3e62df8c707d8</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer- Hybrid</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936d9e38993af00c</t>
+          <t>https://www.indeed.com/viewjob?jk=779a1a0a5eccc32e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full Stack Developer III - Private Markets Applications</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f2e93224c9a790</t>
+          <t>https://www.indeed.com/viewjob?jk=8993a2c0de0e70e1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
+          <t>RPA Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,77 +3531,77 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6911722171aa1c</t>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior .NET and SSRS Developer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c8883b0dd19abf</t>
+          <t>https://www.indeed.com/viewjob?jk=c2df343ab9d22ccf</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Dental Care Alliance</t>
+          <t>SugarAI</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, NoSQL, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,137 +3611,137 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f835ab35442d7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=51c067e768a2b9f2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Data Engineer Seniors III (Databricks)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032b8db4bfd5e6d8</t>
+          <t>https://www.indeed.com/viewjob?jk=89625a5f68a2c750</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f856d080d24d05</t>
+          <t>https://www.indeed.com/viewjob?jk=c629002dbb52205d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Safelite</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19153bb3202f8519</t>
+          <t>https://www.indeed.com/viewjob?jk=89f11f71a1c806a8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee7a2d23cf0b0fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=e7dbdf6ce237b13d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Solutions Engineer - Data Visualization</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,49 +3786,49 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a3e62df8c707d8</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfe4bd64f8f496f</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Senior Software Engineer I- Data &amp; Insights Engineering</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Aledade, Inc.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=779a1a0a5eccc32e</t>
+          <t>https://www.indeed.com/viewjob?jk=15c358b482d33d6d</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Sr. Data Engineering Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3838,147 +3838,147 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8993a2c0de0e70e1</t>
+          <t>https://www.indeed.com/viewjob?jk=b6af42e024fb5358</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>RPA Engineer</t>
+          <t>Cloud Architect @ Dallas, TX</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Logistic Solutions Inc</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ffb721ba3a7f68</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Appian Dev-Reporting &amp; Analytics</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Department of Finance</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, ETL, Power BI, Tableau, AKS</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a2f1102b97c2bd1</t>
+          <t>https://www.indeed.com/viewjob?jk=88aacc0c7f29344d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - SRE</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Verisure</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Uniontown, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, SQL Server, REST API integration, Power BI, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f2cb5787bcd07a</t>
+          <t>https://www.indeed.com/viewjob?jk=c374eb71cdd5829a</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>[REMOTE] Senior Platform Software Engineer- Oracle Clinical Digital Assistant</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c629002dbb52205d</t>
+          <t>https://www.indeed.com/viewjob?jk=23f3fde4ed90357e</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer IV (Snowflake/Databricks) - REMOTE</t>
+          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Velera</t>
+          <t>Asurion</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,540 +4021,15 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, AWS CodePipeline, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd204a1167efc6a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Pano AI</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2df343ab9d22ccf</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer - Databricks</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>SugarAI</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=51c067e768a2b9f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Data Engineer Seniors III (Databricks)</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>FIS</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=89625a5f68a2c750</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior Business Intelligence Engineer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Safelite</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=89f11f71a1c806a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Pano AI</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4aab6a4a6b438005</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Senior Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Health Data Analytics Institute</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Dedham, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=073c59c0c666dd26</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer (Oracle)</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Bitscopic</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7673be72cf2a7f02</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Solutions Engineer - Data Visualization</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>SHI International</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfe4bd64f8f496f</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>[REMOTE] Senior Platform Software Engineer- Oracle Clinical Digital Assistant</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23f3fde4ed90357e</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer I- Data &amp; Insights Engineering</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Aledade, Inc.</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15c358b482d33d6d</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Sr. Data Engineering Architect</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b6af42e024fb5358</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Cloud Architect @ Dallas, TX</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Logistic Solutions Inc</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ffb721ba3a7f68</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Appian Dev-Reporting &amp; Analytics</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Department of Finance</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Manhattan, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, ETL, Power BI, Tableau, AKS</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88aacc0c7f29344d</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Verisure</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Uniontown, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, SQL Server, REST API integration, Power BI, CI/CD, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c374eb71cdd5829a</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Asurion</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Sterling, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, AWS CodePipeline, Docker</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b4a35189b0c83845</t>
         </is>

--- a/results/job_matches_2026-07-14.xlsx
+++ b/results/job_matches_2026-07-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer II</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BankUnited</t>
+          <t>Omada Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Miami Lakes, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, Step Functions, RDS, Azure, Hadoop, Spark, PySpark</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, SQS, SNS, Databricks, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7dee1b85cc76fb8</t>
+          <t>https://www.indeed.com/viewjob?jk=0663114dfd06c9eb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Transformation Senior Consultant</t>
+          <t>Cloud Data Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>BankUnited</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami Lakes, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP</t>
+          <t>AWS, Glue, Redshift, Athena, Step Functions, RDS, Azure, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57362c44cdaea54f</t>
+          <t>https://www.indeed.com/viewjob?jk=c7dee1b85cc76fb8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Cloud Transformation Senior Consultant</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Azure, Databricks, Google Cloud Platform, GCP, Hive, HBase, Spark</t>
+          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e278e0dc4824974</t>
+          <t>https://www.indeed.com/viewjob?jk=57362c44cdaea54f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Junior Architect / Senior Data Engineer - Remote</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>AWS, Glue, EMR, Azure, Databricks, Google Cloud Platform, GCP, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e53a2ba6f9a4021</t>
+          <t>https://www.indeed.com/viewjob?jk=78eadef287e1b0ce</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Winfo Solutions</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>20.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1691b4d7b52de9</t>
+          <t>https://www.indeed.com/viewjob?jk=e085be8f0f2f681d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Developer, Business Intelligence Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>20.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01d88d0c47a7625</t>
+          <t>https://www.indeed.com/viewjob?jk=b192e5946ee2ce27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure Data Architect (remote US)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>News Corp</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>20.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,102 +706,102 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d584a94be46cf8b0</t>
+          <t>https://www.indeed.com/viewjob?jk=93c17e2e00004cf8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AWS Data Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>20.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfb146f53215cc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d9682d5f343e62</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>20.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Azure, Databricks, Google Cloud Platform, GCP, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9be95a71934961d</t>
+          <t>https://www.indeed.com/viewjob?jk=3e278e0dc4824974</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Junior Architect / Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>20.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf05ce3284e6a20</t>
+          <t>https://www.indeed.com/viewjob?jk=7e53a2ba6f9a4021</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Data AI Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Itero Group</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e304be37d5897728</t>
+          <t>https://www.indeed.com/viewjob?jk=9de5ac8d42dd8ec2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Itero Group</t>
+          <t>Winfo Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,102 +881,102 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9724f20b3e8cf9d3</t>
+          <t>https://www.indeed.com/viewjob?jk=0c1691b4d7b52de9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Operations Engineer</t>
+          <t>Software Developer, Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Abrigo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7fae8116d2ca386</t>
+          <t>https://www.indeed.com/viewjob?jk=c01d88d0c47a7625</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Operations Engineer</t>
+          <t>Senior Data Engineer, AWS Data Platform</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Abrigo</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e9a8697ac906001</t>
+          <t>https://www.indeed.com/viewjob?jk=cfb146f53215cc2b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Operations Engineer</t>
+          <t>Azure Data Architect (remote US)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Abrigo</t>
+          <t>News Corp</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dae3ed04ad2bede</t>
+          <t>https://www.indeed.com/viewjob?jk=d584a94be46cf8b0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Management Professional - Data Engineering - Entities</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,102 +1021,102 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a24491194c9938</t>
+          <t>https://www.indeed.com/viewjob?jk=b9be95a71934961d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Management Professional - Data Engineering - Entities</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d437f6ae16eb4d</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf05ce3284e6a20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Quality AI Intern (61_2026.3)</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Affinity Solutions</t>
+          <t>Itero Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc7c811d1c4b67c</t>
+          <t>https://www.indeed.com/viewjob?jk=e304be37d5897728</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Remote</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Itero Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,164 +1126,164 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0426c9944a6312e8</t>
+          <t>https://www.indeed.com/viewjob?jk=9724f20b3e8cf9d3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Junior Software Engineer- Cloud Cost Optimization</t>
+          <t>Senior Cloud Database Operations Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Abrigo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59be0306e4985a52</t>
+          <t>https://www.indeed.com/viewjob?jk=d7fae8116d2ca386</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Junior Software Engineer- Cloud Cost Optimization</t>
+          <t>Senior Cloud Database Operations Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Abrigo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12264a4762b0f153</t>
+          <t>https://www.indeed.com/viewjob?jk=3e9a8697ac906001</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Junior Software Engineer- Cloud Cost Optimization</t>
+          <t>Senior Cloud Database Operations Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Abrigo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4741b2aaf2ec4639</t>
+          <t>https://www.indeed.com/viewjob?jk=0dae3ed04ad2bede</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Junior Software Engineer- Cloud Cost Optimization</t>
+          <t>Senior Data Management Professional - Data Engineering - Entities</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8379cf1d692d007</t>
+          <t>https://www.indeed.com/viewjob?jk=00a24491194c9938</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Junior Software Engineer- Cloud Cost Optimization</t>
+          <t>Senior Cloud Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9696f4f0c31fbf12</t>
+          <t>https://www.indeed.com/viewjob?jk=0426c9944a6312e8</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23fcdad233ea5e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=59be0306e4985a52</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12bdc06f31387ddb</t>
+          <t>https://www.indeed.com/viewjob?jk=12264a4762b0f153</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f457f2be81b9770</t>
+          <t>https://www.indeed.com/viewjob?jk=4741b2aaf2ec4639</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c8bee941837486</t>
+          <t>https://www.indeed.com/viewjob?jk=c8379cf1d692d007</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bce80595c811362</t>
+          <t>https://www.indeed.com/viewjob?jk=9696f4f0c31fbf12</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0cf43be3ae79d3</t>
+          <t>https://www.indeed.com/viewjob?jk=23fcdad233ea5e6d</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade89b18f313e675</t>
+          <t>https://www.indeed.com/viewjob?jk=12bdc06f31387ddb</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfddcbf296252d6b</t>
+          <t>https://www.indeed.com/viewjob?jk=7f457f2be81b9770</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0aae1d49cd9474ec</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c8bee941837486</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2866e598e580305</t>
+          <t>https://www.indeed.com/viewjob?jk=6bce80595c811362</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ffd4ec0a1a5c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0cf43be3ae79d3</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=534c078f01ee2602</t>
+          <t>https://www.indeed.com/viewjob?jk=ade89b18f313e675</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d39a911901dc6d</t>
+          <t>https://www.indeed.com/viewjob?jk=cfddcbf296252d6b</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a72c1fe63174bbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=0aae1d49cd9474ec</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,19 +1826,19 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bdbc801745a49ec</t>
+          <t>https://www.indeed.com/viewjob?jk=e2866e598e580305</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c27f2a9eec45412</t>
+          <t>https://www.indeed.com/viewjob?jk=c2ffd4ec0a1a5c3a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Charter Manufacturing</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mequon, WI, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=284985e81accb0a4</t>
+          <t>https://www.indeed.com/viewjob?jk=534c078f01ee2602</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Native Developer- Europe</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=444a0e6bd539f82b</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d39a911901dc6d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Native Builder-Europe</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae934e8451ebc14c</t>
+          <t>https://www.indeed.com/viewjob?jk=a72c1fe63174bbb8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Entertainment Partners</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42eebf957e43408</t>
+          <t>https://www.indeed.com/viewjob?jk=4bdbc801745a49ec</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Native Builder_EU</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Charter Manufacturing</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mequon, WI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea4fc6a360496ad</t>
+          <t>https://www.indeed.com/viewjob?jk=284985e81accb0a4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer-Specialist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Arbitration Forums Inc.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,24 +2061,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2df1f2e18d690c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=0c27f2a9eec45412</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer-Specialist</t>
+          <t>AI Native Developer- Europe</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2101,19 +2101,19 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d896c15ac717e14c</t>
+          <t>https://www.indeed.com/viewjob?jk=444a0e6bd539f82b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer-Specialist</t>
+          <t>AI Native Builder-Europe</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2136,72 +2136,72 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4fe4e7c9a86b11</t>
+          <t>https://www.indeed.com/viewjob?jk=ae934e8451ebc14c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Entertainment Partners</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6310ba46fd00a82c</t>
+          <t>https://www.indeed.com/viewjob?jk=e42eebf957e43408</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I</t>
+          <t>AI Native Builder_EU</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>C2FO</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Spark, Scala, Kafka, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a710f918b88f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea4fc6a360496ad</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Application Engineer</t>
+          <t>Forward Deployed Engineer-Specialist</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d521f5fad271b9</t>
+          <t>https://www.indeed.com/viewjob?jk=2df1f2e18d690c4a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - AI/ML</t>
+          <t>Forward Deployed Engineer-Specialist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,19 +2281,19 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa005e3343082c96</t>
+          <t>https://www.indeed.com/viewjob?jk=d896c15ac717e14c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI) Senior Data Scientist</t>
+          <t>Forward Deployed Engineer-Specialist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2302,11 +2302,11 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9ea8d31a8815a9</t>
+          <t>https://www.indeed.com/viewjob?jk=db4fe4e7c9a86b11</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DataHub Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>GE Appliances</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Kafka, Kafka Connect, Oracle, MySQL, ETL</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, IAM, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5423277344900438</t>
+          <t>https://www.indeed.com/viewjob?jk=f488fb42bdd9a3e5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Data Scientist - AI/ML</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Hadoop, Spark</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ec36958a4f20d5</t>
+          <t>https://www.indeed.com/viewjob?jk=aa005e3343082c96</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Artificial Intelligence (AI) Senior Data Scientist</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Safelite</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Talend</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab9b545c0f88523</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9ea8d31a8815a9</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - FY27</t>
+          <t>AWS Full Stack Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, CodeBuild</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754540310d15df69</t>
+          <t>https://www.indeed.com/viewjob?jk=e643625eb77abd14</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer II (US)</t>
+          <t>DataHub Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
+          <t>AWS, S3, IAM, RDS, Azure, Kafka, Kafka Connect, Oracle, MySQL, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2633a0f0dff514a6</t>
+          <t>https://www.indeed.com/viewjob?jk=5423277344900438</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Princ Engr-Ntwk Engring</t>
+          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e6dbfd3d963c65c</t>
+          <t>https://www.indeed.com/viewjob?jk=4f9fcd187c753bef</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,102 +2561,102 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ef94552c14d9bd</t>
+          <t>https://www.indeed.com/viewjob?jk=751a33e38e145115</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Escalent</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45d62ba2dc0bd875</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ec36958a4f20d5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Safelite</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe69cd7125f7a833</t>
+          <t>https://www.indeed.com/viewjob?jk=eab9b545c0f88523</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Quality Engineer - FY27</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, CodeBuild</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,172 +2666,172 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c09787e1cb8cb395</t>
+          <t>https://www.indeed.com/viewjob?jk=754540310d15df69</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4ad7ea1b58a31e</t>
+          <t>https://www.indeed.com/viewjob?jk=2633a0f0dff514a6</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Princ Engr-Ntwk Engring</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cc726639aa959a6</t>
+          <t>https://www.indeed.com/viewjob?jk=4e6dbfd3d963c65c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Spark Engineer</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cb65007f4e4e07a</t>
+          <t>https://www.indeed.com/viewjob?jk=84ef94552c14d9bd</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Spark Engineer</t>
+          <t>DevOps Engineer III — Deployment, Release Safety &amp; Disaster Recovery</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Cloud Storage, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7beab78b75a48b8</t>
+          <t>https://www.indeed.com/viewjob?jk=406e283b35cafd12</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>DevOps Engineer III — Deployment, Release Safety &amp; Disaster Recovery</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Cloud Storage, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33124af211245233</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3692758f37822d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Cloud Ops Engineer I - SRE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>El Toro.com</t>
+          <t>CaseWorthy</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,67 +2876,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42d84e2b583adb0</t>
+          <t>https://www.indeed.com/viewjob?jk=9d69f297c014e4a1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Quality Engineering, Energy</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Escalent</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brookshire, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e988ed0beac81e</t>
+          <t>https://www.indeed.com/viewjob?jk=45d62ba2dc0bd875</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sigma Report Developer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tachyon Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Redshift, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8d0798b16bd29a</t>
+          <t>https://www.indeed.com/viewjob?jk=ff8b1cf198867c72</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>DevOps Engineer IV — CI/CD Pipeline &amp; Platform Engineering</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,137 +2981,137 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8102d30c9db848fa</t>
+          <t>https://www.indeed.com/viewjob?jk=e953e5a091cd9103</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer IV — CI/CD Pipeline &amp; Platform Engineering</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, PySpark, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4223c8030b51f20b</t>
+          <t>https://www.indeed.com/viewjob?jk=5eed877691f0ccfc</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Software Development Engineer I - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3979f77f1eb1efbc</t>
+          <t>https://www.indeed.com/viewjob?jk=0b08010c09c91435</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Cloud, AWS and Snowflake</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4be1c8e67e2a1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69cd7125f7a833</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-2027 Information Technology - Software Engineer - Full-Time</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6578ea1eb5e5142</t>
+          <t>https://www.indeed.com/viewjob?jk=c09787e1cb8cb395</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full Stack Developer III - Private Markets Applications</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,67 +3156,67 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f2e93224c9a790</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4ad7ea1b58a31e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer- Hybrid</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936d9e38993af00c</t>
+          <t>https://www.indeed.com/viewjob?jk=1cc726639aa959a6</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-2027 Information Technology - Software Engineer - Intern</t>
+          <t>Spark Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab14599c79da82b</t>
+          <t>https://www.indeed.com/viewjob?jk=2cb65007f4e4e07a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior .NET and SSRS Developer</t>
+          <t>Spark Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,67 +3261,67 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c8883b0dd19abf</t>
+          <t>https://www.indeed.com/viewjob?jk=e7beab78b75a48b8</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032b8db4bfd5e6d8</t>
+          <t>https://www.indeed.com/viewjob?jk=33124af211245233</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Sr Engineer, Data &amp; Analytics Platform (Snowflake/dbt)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f856d080d24d05</t>
+          <t>https://www.indeed.com/viewjob?jk=f401900b912197cd</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Senior Software Engineer - Machine Learning (Remote)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>API Gateway, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19153bb3202f8519</t>
+          <t>https://www.indeed.com/viewjob?jk=0ef4f0fa082366da</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>El Toro.com</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,89 +3401,89 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee7a2d23cf0b0fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=d42d84e2b583adb0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>DevOps Engineer IV — Operational Resilience, Observability &amp; SRE</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a3e62df8c707d8</t>
+          <t>https://www.indeed.com/viewjob?jk=761890a317dd4012</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>DevOps Engineer IV — Operational Resilience, Observability &amp; SRE</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=779a1a0a5eccc32e</t>
+          <t>https://www.indeed.com/viewjob?jk=c1c767b23cb64efd</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Advanced Software Engineer- Full Stack Cloud Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3492,11 +3492,11 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8993a2c0de0e70e1</t>
+          <t>https://www.indeed.com/viewjob?jk=78950b770ed7417f</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>RPA Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,207 +3541,207 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+          <t>https://www.indeed.com/viewjob?jk=ec87a9fb2bfdfaef</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2df343ab9d22ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=31b3b16aa81c41b5</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SugarAI</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51c067e768a2b9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8e782a934aa046</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer Seniors III (Databricks)</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89625a5f68a2c750</t>
+          <t>https://www.indeed.com/viewjob?jk=f0d1116e6c21d2df</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c629002dbb52205d</t>
+          <t>https://www.indeed.com/viewjob?jk=d3aa3e371f227965</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Safelite</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89f11f71a1c806a8</t>
+          <t>https://www.indeed.com/viewjob?jk=4ca117bf04d9ffe8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hope Hull, AL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7dbdf6ce237b13d</t>
+          <t>https://www.indeed.com/viewjob?jk=ace45fc5c61852f3</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Visualization</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,137 +3786,137 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfe4bd64f8f496f</t>
+          <t>https://www.indeed.com/viewjob?jk=11ae8229a3a496f6</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I- Data &amp; Insights Engineering</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Aledade, Inc.</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c358b482d33d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=e5568a11ce1b824f</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr. Data Engineering Architect</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6af42e024fb5358</t>
+          <t>https://www.indeed.com/viewjob?jk=858f2040e74be705</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Cloud Architect @ Dallas, TX</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Logistic Solutions Inc</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hot Springs Village, AR, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ffb721ba3a7f68</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f9c431318c2296</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Appian Dev-Reporting &amp; Analytics</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Department of Finance</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, ETL, Power BI, Tableau, AKS</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88aacc0c7f29344d</t>
+          <t>https://www.indeed.com/viewjob?jk=22400953b1097638</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Verisure</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Uniontown, OH, US USA</t>
+          <t>Long Key, FL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, REST API integration, Power BI, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,77 +3961,2667 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c374eb71cdd5829a</t>
+          <t>https://www.indeed.com/viewjob?jk=c250e961be308780</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>[REMOTE] Senior Platform Software Engineer- Oracle Clinical Digital Assistant</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f3fde4ed90357e</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c18f90256dfdcf</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>KY, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=991a6606bcf54e4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Augusta, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fa34df78a35e73c</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=717f4ba2563e9c72</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58eb1e048db63cbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Pierre, SD, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89167ab20868e733</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Pawtucket, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b176e971f59ee1d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Middletown, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e54aa8f1b4aaced8</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=613d4a5f22442bf1</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=535e05900f7981e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>MT, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e1cb34888680ccb</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Corrales, NM, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d83e6279e7d6910</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Kansas City, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=106cbae01f7f7d8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Fremont, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd04313bb2f7da9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7219daec87e613e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>New Franken, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f31bac0e875df9af</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2ca6c1debed50f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0cfe2200933398b</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=269b4317cd08c69a</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f743c2d0ca8e8782</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3899d26482c4683b</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66a2d72e8e7439f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Charleston, WV, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=317f859e3fbd6963</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e45db4fbb479caaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=192985db73897ccc</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Upper Darby, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4dcb51fe0ec32e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Okemos, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06c75a03e3040629</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1cc8989583f1dcf</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Columbia, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59a56d64f04cb490</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>UT, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb22fabc567b6b1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93fa20c57faaa79c</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Walnut Creek, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff7569c2f065a6e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fc5ffa459949a81</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=133d752eeb387774</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Charles Schwab</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Southlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8102d30c9db848fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Sigma Report Developer</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Tachyon Technologies</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac8d0798b16bd29a</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>DevOps Engineer III — Platform Maintenance &amp; Vulnerability Response</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Ad Hoc</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd03dd73fcf8e61c</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>DevOps Engineer III — Platform Maintenance &amp; Vulnerability Response</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Ad Hoc</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81aea0d34c5dcd96</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Forward Deployed Data Engineer</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>CoorsTek</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Golden, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b36c700922532ac2</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Azure Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Eli Lilly</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32d19f755ee8489a</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>CT, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, PySpark, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4223c8030b51f20b</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Cloud Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Nightwing</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Sterling, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3979f77f1eb1efbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer - Cloud, AWS and Snowflake</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Regions Financial</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4be1c8e67e2a1f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf57c7d8b4b2d9e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-2027 Information Technology - Software Engineer - Full-Time</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6578ea1eb5e5142</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>AWS connect developer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, Scala, DynamoDB, Terraform</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7fdc32dbba430d32</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Splunk, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d95f616f8a93e76b</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-2027 Information Technology - Software Engineer - Intern</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eab14599c79da82b</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Data Engineer- Hybrid</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Match Made Tech</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=936d9e38993af00c</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Full Stack Developer III - Private Markets Applications</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Neuberger Berman</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, ETL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04f2e93224c9a790</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 (Backend AI)</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Earth City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=032b8db4bfd5e6d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 (Backend AI)</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46f856d080d24d05</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 (Backend AI)</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19153bb3202f8519</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 (Backend AI)</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Brookfield, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee7a2d23cf0b0fbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 (Backend AI)</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Hopkins, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00a3e62df8c707d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 (Backend AI)</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=779a1a0a5eccc32e</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 (Backend AI)</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8993a2c0de0e70e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>RPA Engineer</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Senior .NET and SSRS Developer</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3c8883b0dd19abf</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Pano AI</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2df343ab9d22ccf</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Databricks</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>SugarAI</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51c067e768a2b9f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Data Engineer Seniors III (Databricks)</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>FIS</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89625a5f68a2c750</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Specialist - Data Engineering</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>LTM Limited</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c629002dbb52205d</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Senior Business Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Safelite</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89f11f71a1c806a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e7fd121bc0e2325</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f41d2b8270473c0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a6494cda8c81441</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Aivra Health</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7dbdf6ce237b13d</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Solutions Engineer - Data Visualization</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>SHI International</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7cfe4bd64f8f496f</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer I- Data &amp; Insights Engineering</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Aledade, Inc.</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15c358b482d33d6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineering Architect</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b6af42e024fb5358</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Cloud Architect @ Dallas, TX</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Logistic Solutions Inc</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1ffb721ba3a7f68</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Verisure</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Uniontown, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, SQL Server, REST API integration, Power BI, CI/CD, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c374eb71cdd5829a</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>[REMOTE] Senior Platform Software Engineer- Oracle Clinical Digital Assistant</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23f3fde4ed90357e</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
           <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B176" t="inlineStr">
         <is>
           <t>Asurion</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C176" t="inlineStr">
         <is>
           <t>Sterling, VA, US USA</t>
         </is>
       </c>
-      <c r="D103" t="n">
+      <c r="D176" t="n">
         <v>10.4</v>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E176" t="inlineStr">
         <is>
           <t>AWS, ECS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, AWS CodePipeline, Docker</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F176" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G176" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b4a35189b0c83845</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Appian Dev-Reporting &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Department of Finance</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Manhattan, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, ETL, Power BI, Tableau, AKS</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88aacc0c7f29344d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-14.xlsx
+++ b/results/job_matches_2026-07-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G177"/>
+  <dimension ref="A1:G174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Azure, Databricks, Google Cloud Platform, GCP, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e085be8f0f2f681d</t>
+          <t>https://www.indeed.com/viewjob?jk=3e278e0dc4824974</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b192e5946ee2ce27</t>
+          <t>https://www.indeed.com/viewjob?jk=e085be8f0f2f681d</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c17e2e00004cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=b192e5946ee2ce27</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d9682d5f343e62</t>
+          <t>https://www.indeed.com/viewjob?jk=93c17e2e00004cf8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,17 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Azure, Databricks, Google Cloud Platform, GCP, Hive, HBase, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e278e0dc4824974</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d9682d5f343e62</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AWS Data Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfb146f53215cc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=3720530c1ac33814</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Azure Data Architect (remote US)</t>
+          <t>Senior Data Engineer, AWS Data Platform</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>News Corp</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d584a94be46cf8b0</t>
+          <t>https://www.indeed.com/viewjob?jk=cfb146f53215cc2b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Azure Data Architect (remote US)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>News Corp</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9be95a71934961d</t>
+          <t>https://www.indeed.com/viewjob?jk=d584a94be46cf8b0</t>
         </is>
       </c>
     </row>
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf05ce3284e6a20</t>
+          <t>https://www.indeed.com/viewjob?jk=b9be95a71934961d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Itero Group</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e304be37d5897728</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf05ce3284e6a20</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9724f20b3e8cf9d3</t>
+          <t>https://www.indeed.com/viewjob?jk=e304be37d5897728</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Operations Engineer</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Abrigo</t>
+          <t>Itero Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7fae8116d2ca386</t>
+          <t>https://www.indeed.com/viewjob?jk=9724f20b3e8cf9d3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Operations Engineer</t>
+          <t>Senior Data Management Professional - Data Engineering - Entities</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Abrigo</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e9a8697ac906001</t>
+          <t>https://www.indeed.com/viewjob?jk=00a24491194c9938</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Operations Engineer</t>
+          <t>AI &amp; Financial Engineering Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Abrigo</t>
+          <t>Aktra Inc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dae3ed04ad2bede</t>
+          <t>https://www.indeed.com/viewjob?jk=241a34851225e025</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Management Professional - Data Engineering - Entities</t>
+          <t>Senior Cloud Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a24491194c9938</t>
+          <t>https://www.indeed.com/viewjob?jk=0426c9944a6312e8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Remote</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0426c9944a6312e8</t>
+          <t>https://www.indeed.com/viewjob?jk=59be0306e4985a52</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59be0306e4985a52</t>
+          <t>https://www.indeed.com/viewjob?jk=12264a4762b0f153</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12264a4762b0f153</t>
+          <t>https://www.indeed.com/viewjob?jk=4741b2aaf2ec4639</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4741b2aaf2ec4639</t>
+          <t>https://www.indeed.com/viewjob?jk=c8379cf1d692d007</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8379cf1d692d007</t>
+          <t>https://www.indeed.com/viewjob?jk=9696f4f0c31fbf12</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9696f4f0c31fbf12</t>
+          <t>https://www.indeed.com/viewjob?jk=23fcdad233ea5e6d</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23fcdad233ea5e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=12bdc06f31387ddb</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12bdc06f31387ddb</t>
+          <t>https://www.indeed.com/viewjob?jk=7f457f2be81b9770</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f457f2be81b9770</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c8bee941837486</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c8bee941837486</t>
+          <t>https://www.indeed.com/viewjob?jk=6bce80595c811362</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bce80595c811362</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0cf43be3ae79d3</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0cf43be3ae79d3</t>
+          <t>https://www.indeed.com/viewjob?jk=ade89b18f313e675</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade89b18f313e675</t>
+          <t>https://www.indeed.com/viewjob?jk=cfddcbf296252d6b</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfddcbf296252d6b</t>
+          <t>https://www.indeed.com/viewjob?jk=0aae1d49cd9474ec</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0aae1d49cd9474ec</t>
+          <t>https://www.indeed.com/viewjob?jk=e2866e598e580305</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2866e598e580305</t>
+          <t>https://www.indeed.com/viewjob?jk=c2ffd4ec0a1a5c3a</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ffd4ec0a1a5c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=534c078f01ee2602</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=534c078f01ee2602</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d39a911901dc6d</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d39a911901dc6d</t>
+          <t>https://www.indeed.com/viewjob?jk=a72c1fe63174bbb8</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a72c1fe63174bbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=4bdbc801745a49ec</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Junior Software Engineer- Cloud Cost Optimization</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Charter Manufacturing</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Mequon, WI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bdbc801745a49ec</t>
+          <t>https://www.indeed.com/viewjob?jk=284985e81accb0a4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AI Native Developer- Europe</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Charter Manufacturing</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mequon, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=284985e81accb0a4</t>
+          <t>https://www.indeed.com/viewjob?jk=444a0e6bd539f82b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Native Builder-Europe</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c27f2a9eec45412</t>
+          <t>https://www.indeed.com/viewjob?jk=ae934e8451ebc14c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI Native Developer- Europe</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Entertainment Partners</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=444a0e6bd539f82b</t>
+          <t>https://www.indeed.com/viewjob?jk=e42eebf957e43408</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI Native Builder-Europe</t>
+          <t>Senior Solutions Architect - Airflow (West Coast)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae934e8451ebc14c</t>
+          <t>https://www.indeed.com/viewjob?jk=563d41613641e2d6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Entertainment Partners</t>
+          <t>GE Appliances</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, IAM, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42eebf957e43408</t>
+          <t>https://www.indeed.com/viewjob?jk=f488fb42bdd9a3e5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Native Builder_EU</t>
+          <t>Senior Data Scientist - AI/ML</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,19 +2211,19 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea4fc6a360496ad</t>
+          <t>https://www.indeed.com/viewjob?jk=aa005e3343082c96</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer-Specialist</t>
+          <t>Artificial Intelligence (AI) Senior Data Scientist</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2232,11 +2232,11 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,137 +2246,137 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2df1f2e18d690c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9ea8d31a8815a9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer-Specialist</t>
+          <t>AWS Full Stack Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d896c15ac717e14c</t>
+          <t>https://www.indeed.com/viewjob?jk=e643625eb77abd14</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer-Specialist</t>
+          <t>DataHub Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Kafka, Kafka Connect, Oracle, MySQL, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4fe4e7c9a86b11</t>
+          <t>https://www.indeed.com/viewjob?jk=5423277344900438</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GE Appliances</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, IAM, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f488fb42bdd9a3e5</t>
+          <t>https://www.indeed.com/viewjob?jk=4f9fcd187c753bef</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - AI/ML</t>
+          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa005e3343082c96</t>
+          <t>https://www.indeed.com/viewjob?jk=751a33e38e145115</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI) Senior Data Scientist</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9ea8d31a8815a9</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ec36958a4f20d5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AWS Full Stack Engineer</t>
+          <t>Senior Quality Engineer - FY27</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, IAM, RDS, Scala</t>
+          <t>AWS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, CodeBuild</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e643625eb77abd14</t>
+          <t>https://www.indeed.com/viewjob?jk=754540310d15df69</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DataHub Developer</t>
+          <t>Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Kafka, Kafka Connect, Oracle, MySQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5423277344900438</t>
+          <t>https://www.indeed.com/viewjob?jk=2633a0f0dff514a6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
+          <t>Princ Engr-Ntwk Engring</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f9fcd187c753bef</t>
+          <t>https://www.indeed.com/viewjob?jk=4e6dbfd3d963c65c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=751a33e38e145115</t>
+          <t>https://www.indeed.com/viewjob?jk=84ef94552c14d9bd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>DevOps Engineer III — Deployment, Release Safety &amp; Disaster Recovery</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Hadoop, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Cloud Storage, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ec36958a4f20d5</t>
+          <t>https://www.indeed.com/viewjob?jk=406e283b35cafd12</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer III — Deployment, Release Safety &amp; Disaster Recovery</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Safelite</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Talend</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Cloud Storage, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab9b545c0f88523</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3692758f37822d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - FY27</t>
+          <t>Senior Cloud Ops Engineer I - SRE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>CaseWorthy</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, CodeBuild</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,102 +2666,102 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754540310d15df69</t>
+          <t>https://www.indeed.com/viewjob?jk=9d69f297c014e4a1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer II (US)</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Escalent</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2633a0f0dff514a6</t>
+          <t>https://www.indeed.com/viewjob?jk=45d62ba2dc0bd875</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Princ Engr-Ntwk Engring</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e6dbfd3d963c65c</t>
+          <t>https://www.indeed.com/viewjob?jk=ff8b1cf198867c72</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>DevOps Engineer IV — CI/CD Pipeline &amp; Platform Engineering</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,14 +2771,14 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ef94552c14d9bd</t>
+          <t>https://www.indeed.com/viewjob?jk=e953e5a091cd9103</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DevOps Engineer III — Deployment, Release Safety &amp; Disaster Recovery</t>
+          <t>DevOps Engineer IV — CI/CD Pipeline &amp; Platform Engineering</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2792,11 +2792,11 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Cloud Storage, Scala, CI/CD, Jenkins</t>
+          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,59 +2806,59 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=406e283b35cafd12</t>
+          <t>https://www.indeed.com/viewjob?jk=5eed877691f0ccfc</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DevOps Engineer III — Deployment, Release Safety &amp; Disaster Recovery</t>
+          <t>Systems Integration Senior Specialist</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Cloud Storage, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3692758f37822d</t>
+          <t>https://www.indeed.com/viewjob?jk=73592828eec12b39</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Cloud Ops Engineer I - SRE</t>
+          <t>Software Development Engineer I - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CaseWorthy</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d69f297c014e4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=0b08010c09c91435</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Escalent</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45d62ba2dc0bd875</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69cd7125f7a833</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff8b1cf198867c72</t>
+          <t>https://www.indeed.com/viewjob?jk=c09787e1cb8cb395</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DevOps Engineer IV — CI/CD Pipeline &amp; Platform Engineering</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e953e5a091cd9103</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4ad7ea1b58a31e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DevOps Engineer IV — CI/CD Pipeline &amp; Platform Engineering</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eed877691f0ccfc</t>
+          <t>https://www.indeed.com/viewjob?jk=1cc726639aa959a6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Development Engineer I - ArcGIS Enterprise</t>
+          <t>Software Engineer III - Full Stack</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b08010c09c91435</t>
+          <t>https://www.indeed.com/viewjob?jk=a457abd93bdf7c3a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Sr Engineer, Data &amp; Analytics Platform (Snowflake/dbt)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>RDS, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe69cd7125f7a833</t>
+          <t>https://www.indeed.com/viewjob?jk=f401900b912197cd</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Spark Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c09787e1cb8cb395</t>
+          <t>https://www.indeed.com/viewjob?jk=2cb65007f4e4e07a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Spark Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,54 +3156,54 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4ad7ea1b58a31e</t>
+          <t>https://www.indeed.com/viewjob?jk=e7beab78b75a48b8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cc726639aa959a6</t>
+          <t>https://www.indeed.com/viewjob?jk=33124af211245233</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Spark Engineer</t>
+          <t>Senior Software Engineer - Machine Learning (Remote)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>API Gateway, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cb65007f4e4e07a</t>
+          <t>https://www.indeed.com/viewjob?jk=0ef4f0fa082366da</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Spark Engineer</t>
+          <t>DevOps Engineer IV — Operational Resilience, Observability &amp; SRE</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, S3, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7beab78b75a48b8</t>
+          <t>https://www.indeed.com/viewjob?jk=761890a317dd4012</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>DevOps Engineer IV — Operational Resilience, Observability &amp; SRE</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33124af211245233</t>
+          <t>https://www.indeed.com/viewjob?jk=c1c767b23cb64efd</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data &amp; Analytics Platform (Snowflake/dbt)</t>
+          <t>Data Scientist, Analytics and Modelling</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, Power BI, Tableau, DataOps</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Spark, PySpark, Scala, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,19 +3331,19 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f401900b912197cd</t>
+          <t>https://www.indeed.com/viewjob?jk=9439d62d21cdb7b2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Machine Learning (Remote)</t>
+          <t>Advanced Software Engineer- Full Stack Cloud Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, MLOps</t>
+          <t>AWS, S3, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ef4f0fa082366da</t>
+          <t>https://www.indeed.com/viewjob?jk=78950b770ed7417f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>El Toro.com</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42d84e2b583adb0</t>
+          <t>https://www.indeed.com/viewjob?jk=ec87a9fb2bfdfaef</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DevOps Engineer IV — Operational Resilience, Observability &amp; SRE</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761890a317dd4012</t>
+          <t>https://www.indeed.com/viewjob?jk=31b3b16aa81c41b5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DevOps Engineer IV — Operational Resilience, Observability &amp; SRE</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1c767b23cb64efd</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8e782a934aa046</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Advanced Software Engineer- Full Stack Cloud Developer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78950b770ed7417f</t>
+          <t>https://www.indeed.com/viewjob?jk=f0d1116e6c21d2df</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec87a9fb2bfdfaef</t>
+          <t>https://www.indeed.com/viewjob?jk=d3aa3e371f227965</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b3b16aa81c41b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4ca117bf04d9ffe8</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Hope Hull, AL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8e782a934aa046</t>
+          <t>https://www.indeed.com/viewjob?jk=ace45fc5c61852f3</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0d1116e6c21d2df</t>
+          <t>https://www.indeed.com/viewjob?jk=11ae8229a3a496f6</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3aa3e371f227965</t>
+          <t>https://www.indeed.com/viewjob?jk=e5568a11ce1b824f</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca117bf04d9ffe8</t>
+          <t>https://www.indeed.com/viewjob?jk=858f2040e74be705</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hope Hull, AL, US USA</t>
+          <t>Hot Springs Village, AR, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace45fc5c61852f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f9c431318c2296</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11ae8229a3a496f6</t>
+          <t>https://www.indeed.com/viewjob?jk=22400953b1097638</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Long Key, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5568a11ce1b824f</t>
+          <t>https://www.indeed.com/viewjob?jk=c250e961be308780</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858f2040e74be705</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c18f90256dfdcf</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hot Springs Village, AR, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f9c431318c2296</t>
+          <t>https://www.indeed.com/viewjob?jk=991a6606bcf54e4c</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22400953b1097638</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa34df78a35e73c</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Long Key, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c250e961be308780</t>
+          <t>https://www.indeed.com/viewjob?jk=717f4ba2563e9c72</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c18f90256dfdcf</t>
+          <t>https://www.indeed.com/viewjob?jk=58eb1e048db63cbb</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991a6606bcf54e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=89167ab20868e733</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa34df78a35e73c</t>
+          <t>https://www.indeed.com/viewjob?jk=b176e971f59ee1d0</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Middletown, DE, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=717f4ba2563e9c72</t>
+          <t>https://www.indeed.com/viewjob?jk=e54aa8f1b4aaced8</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58eb1e048db63cbb</t>
+          <t>https://www.indeed.com/viewjob?jk=613d4a5f22442bf1</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89167ab20868e733</t>
+          <t>https://www.indeed.com/viewjob?jk=535e05900f7981e2</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b176e971f59ee1d0</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1cb34888680ccb</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Middletown, DE, US USA</t>
+          <t>Corrales, NM, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e54aa8f1b4aaced8</t>
+          <t>https://www.indeed.com/viewjob?jk=0d83e6279e7d6910</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613d4a5f22442bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=106cbae01f7f7d8b</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Fremont, NH, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=535e05900f7981e2</t>
+          <t>https://www.indeed.com/viewjob?jk=dd04313bb2f7da9d</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1cb34888680ccb</t>
+          <t>https://www.indeed.com/viewjob?jk=7219daec87e613e4</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Corrales, NM, US USA</t>
+          <t>New Franken, WI, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d83e6279e7d6910</t>
+          <t>https://www.indeed.com/viewjob?jk=f31bac0e875df9af</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106cbae01f7f7d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ca6c1debed50f1</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Fremont, NH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd04313bb2f7da9d</t>
+          <t>https://www.indeed.com/viewjob?jk=a0cfe2200933398b</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7219daec87e613e4</t>
+          <t>https://www.indeed.com/viewjob?jk=269b4317cd08c69a</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>New Franken, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31bac0e875df9af</t>
+          <t>https://www.indeed.com/viewjob?jk=f743c2d0ca8e8782</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ca6c1debed50f1</t>
+          <t>https://www.indeed.com/viewjob?jk=3899d26482c4683b</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0cfe2200933398b</t>
+          <t>https://www.indeed.com/viewjob?jk=66a2d72e8e7439f5</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=269b4317cd08c69a</t>
+          <t>https://www.indeed.com/viewjob?jk=317f859e3fbd6963</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f743c2d0ca8e8782</t>
+          <t>https://www.indeed.com/viewjob?jk=e45db4fbb479caaa</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3899d26482c4683b</t>
+          <t>https://www.indeed.com/viewjob?jk=192985db73897ccc</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Upper Darby, PA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66a2d72e8e7439f5</t>
+          <t>https://www.indeed.com/viewjob?jk=d4dcb51fe0ec32e8</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Okemos, MI, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=317f859e3fbd6963</t>
+          <t>https://www.indeed.com/viewjob?jk=06c75a03e3040629</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e45db4fbb479caaa</t>
+          <t>https://www.indeed.com/viewjob?jk=d1cc8989583f1dcf</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=192985db73897ccc</t>
+          <t>https://www.indeed.com/viewjob?jk=59a56d64f04cb490</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Upper Darby, PA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4dcb51fe0ec32e8</t>
+          <t>https://www.indeed.com/viewjob?jk=cb22fabc567b6b1f</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Okemos, MI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c75a03e3040629</t>
+          <t>https://www.indeed.com/viewjob?jk=93fa20c57faaa79c</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1cc8989583f1dcf</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7569c2f065a6e4</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59a56d64f04cb490</t>
+          <t>https://www.indeed.com/viewjob?jk=4fc5ffa459949a81</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb22fabc567b6b1f</t>
+          <t>https://www.indeed.com/viewjob?jk=133d752eeb387774</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>El Toro.com</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fa20c57faaa79c</t>
+          <t>https://www.indeed.com/viewjob?jk=d42d84e2b583adb0</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Sigma Report Developer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Tachyon Technologies</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7569c2f065a6e4</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8d0798b16bd29a</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fc5ffa459949a81</t>
+          <t>https://www.indeed.com/viewjob?jk=8102d30c9db848fa</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>DevOps Engineer III — Platform Maintenance &amp; Vulnerability Response</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=133d752eeb387774</t>
+          <t>https://www.indeed.com/viewjob?jk=cd03dd73fcf8e61c</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>DevOps Engineer III — Platform Maintenance &amp; Vulnerability Response</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,129 +5186,129 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8102d30c9db848fa</t>
+          <t>https://www.indeed.com/viewjob?jk=81aea0d34c5dcd96</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Sigma Report Developer</t>
+          <t>Sr. Data Engineer - Cloud, AWS and Snowflake</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Tachyon Technologies</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8d0798b16bd29a</t>
+          <t>https://www.indeed.com/viewjob?jk=b4be1c8e67e2a1f2</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DevOps Engineer III — Platform Maintenance &amp; Vulnerability Response</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd03dd73fcf8e61c</t>
+          <t>https://www.indeed.com/viewjob?jk=b36c700922532ac2</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>DevOps Engineer III — Platform Maintenance &amp; Vulnerability Response</t>
+          <t>Azure Platform Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81aea0d34c5dcd96</t>
+          <t>https://www.indeed.com/viewjob?jk=32d19f755ee8489a</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, PySpark, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36c700922532ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=4223c8030b51f20b</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
+          <t>AWS, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d19f755ee8489a</t>
+          <t>https://www.indeed.com/viewjob?jk=3979f77f1eb1efbc</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, PySpark, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4223c8030b51f20b</t>
+          <t>https://www.indeed.com/viewjob?jk=bf57c7d8b4b2d9e4</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>2026-2027 Information Technology - Software Engineer - Full-Time</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3979f77f1eb1efbc</t>
+          <t>https://www.indeed.com/viewjob?jk=d6578ea1eb5e5142</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Cloud, AWS and Snowflake</t>
+          <t>AWS connect developer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,24 +5456,24 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, Scala, DynamoDB, Terraform</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4be1c8e67e2a1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=7fdc32dbba430d32</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,14 +5501,14 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf57c7d8b4b2d9e4</t>
+          <t>https://www.indeed.com/viewjob?jk=d95f616f8a93e76b</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-2027 Information Technology - Software Engineer - Full-Time</t>
+          <t>2026-2027 Information Technology - Software Engineer - Intern</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6578ea1eb5e5142</t>
+          <t>https://www.indeed.com/viewjob?jk=eab14599c79da82b</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>AWS connect developer</t>
+          <t>Data Engineer- Hybrid</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, Scala, DynamoDB, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fdc32dbba430d32</t>
+          <t>https://www.indeed.com/viewjob?jk=936d9e38993af00c</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>Senior .NET and SSRS Developer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Splunk, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d95f616f8a93e76b</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c8883b0dd19abf</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-2027 Information Technology - Software Engineer - Intern</t>
+          <t>Full Stack Developer III - Private Markets Applications</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab14599c79da82b</t>
+          <t>https://www.indeed.com/viewjob?jk=04f2e93224c9a790</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Data Engineer- Hybrid</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936d9e38993af00c</t>
+          <t>https://www.indeed.com/viewjob?jk=032b8db4bfd5e6d8</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Full Stack Developer III - Private Markets Applications</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f2e93224c9a790</t>
+          <t>https://www.indeed.com/viewjob?jk=46f856d080d24d05</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032b8db4bfd5e6d8</t>
+          <t>https://www.indeed.com/viewjob?jk=19153bb3202f8519</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f856d080d24d05</t>
+          <t>https://www.indeed.com/viewjob?jk=ee7a2d23cf0b0fbe</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19153bb3202f8519</t>
+          <t>https://www.indeed.com/viewjob?jk=00a3e62df8c707d8</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee7a2d23cf0b0fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=779a1a0a5eccc32e</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a3e62df8c707d8</t>
+          <t>https://www.indeed.com/viewjob?jk=8993a2c0de0e70e1</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>RPA Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,129 +5921,129 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=779a1a0a5eccc32e</t>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8993a2c0de0e70e1</t>
+          <t>https://www.indeed.com/viewjob?jk=c629002dbb52205d</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>RPA Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+          <t>https://www.indeed.com/viewjob?jk=c2df343ab9d22ccf</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Senior .NET and SSRS Developer</t>
+          <t>Senior Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SugarAI</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c8883b0dd19abf</t>
+          <t>https://www.indeed.com/viewjob?jk=51c067e768a2b9f2</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineer Seniors III (Databricks)</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2df343ab9d22ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=89625a5f68a2c750</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>SugarAI</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,34 +6086,34 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51c067e768a2b9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=3e7fd121bc0e2325</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Data Engineer Seniors III (Databricks)</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,34 +6121,34 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89625a5f68a2c750</t>
+          <t>https://www.indeed.com/viewjob?jk=f41d2b8270473c0a</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,34 +6156,34 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c629002dbb52205d</t>
+          <t>https://www.indeed.com/viewjob?jk=8a6494cda8c81441</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Safelite</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,34 +6191,34 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89f11f71a1c806a8</t>
+          <t>https://www.indeed.com/viewjob?jk=e7dbdf6ce237b13d</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, MLOps, CI/CD, Docker, Kubernetes, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7fd121bc0e2325</t>
+          <t>https://www.indeed.com/viewjob?jk=020e432808447458</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>CCaaS GCP Product Owner</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Betsol</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Kafka, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f41d2b8270473c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=14af21d8d4a25c44</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Network/Systems Engineer/DBA</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CCSI</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, MySQL, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a6494cda8c81441</t>
+          <t>https://www.indeed.com/viewjob?jk=82f25ac0bbe1b8ca</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Solutions Engineer - Data Visualization</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,19 +6341,19 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7dbdf6ce237b13d</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfe4bd64f8f496f</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Visualization</t>
+          <t>Senior Software Engineer I- Data &amp; Insights Engineering</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Aledade, Inc.</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6366,34 +6366,34 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfe4bd64f8f496f</t>
+          <t>https://www.indeed.com/viewjob?jk=15c358b482d33d6d</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I- Data &amp; Insights Engineering</t>
+          <t>Appian Dev-Reporting &amp; Analytics</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Aledade, Inc.</t>
+          <t>Department of Finance</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,34 +6401,34 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, ETL, Power BI, Tableau, AKS</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c358b482d33d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=88aacc0c7f29344d</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Sr. Data Engineering Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Verisure</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Uniontown, OH, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,34 +6436,34 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
+          <t>AWS, Azure, Scala, SQL Server, REST API integration, Power BI, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6af42e024fb5358</t>
+          <t>https://www.indeed.com/viewjob?jk=c374eb71cdd5829a</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Cloud Architect @ Dallas, TX</t>
+          <t>[REMOTE] Senior Platform Software Engineer- Oracle Clinical Digital Assistant</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Logistic Solutions Inc</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,34 +6471,34 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ffb721ba3a7f68</t>
+          <t>https://www.indeed.com/viewjob?jk=23f3fde4ed90357e</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Verisure</t>
+          <t>Asurion</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Uniontown, OH, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,122 +6506,17 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, REST API integration, Power BI, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, AWS CodePipeline, Docker</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c374eb71cdd5829a</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>[REMOTE] Senior Platform Software Engineer- Oracle Clinical Digital Assistant</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23f3fde4ed90357e</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Asurion</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Sterling, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, AWS CodePipeline, Docker</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=b4a35189b0c83845</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Appian Dev-Reporting &amp; Analytics</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Department of Finance</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Manhattan, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, ETL, Power BI, Tableau, AKS</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88aacc0c7f29344d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-14.xlsx
+++ b/results/job_matches_2026-07-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G174"/>
+  <dimension ref="A1:G173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer II</t>
+          <t>Cloud Transformation Senior Consultant</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BankUnited</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Miami Lakes, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, Step Functions, RDS, Azure, Hadoop, Spark, PySpark</t>
+          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,42 +531,42 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7dee1b85cc76fb8</t>
+          <t>https://www.indeed.com/viewjob?jk=57362c44cdaea54f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Transformation Senior Consultant</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP</t>
+          <t>AWS, Glue, EMR, Azure, Databricks, Google Cloud Platform, GCP, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57362c44cdaea54f</t>
+          <t>https://www.indeed.com/viewjob?jk=78eadef287e1b0ce</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -596,29 +596,29 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78eadef287e1b0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=3e278e0dc4824974</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Azure, Databricks, Google Cloud Platform, GCP, Hive, HBase, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e278e0dc4824974</t>
+          <t>https://www.indeed.com/viewjob?jk=e085be8f0f2f681d</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e085be8f0f2f681d</t>
+          <t>https://www.indeed.com/viewjob?jk=b192e5946ee2ce27</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b192e5946ee2ce27</t>
+          <t>https://www.indeed.com/viewjob?jk=93c17e2e00004cf8</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c17e2e00004cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d9682d5f343e62</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d9682d5f343e62</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c9310d05771935</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Developer, Business Intelligence Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01d88d0c47a7625</t>
+          <t>https://www.indeed.com/viewjob?jk=3720530c1ac33814</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer, AWS Data Platform</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3720530c1ac33814</t>
+          <t>https://www.indeed.com/viewjob?jk=cfb146f53215cc2b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AWS Data Platform</t>
+          <t>Azure Data Architect (remote US)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>News Corp</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfb146f53215cc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=d584a94be46cf8b0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Azure Data Architect (remote US)</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>News Corp</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d584a94be46cf8b0</t>
+          <t>https://www.indeed.com/viewjob?jk=b9be95a71934961d</t>
         </is>
       </c>
     </row>
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9be95a71934961d</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf05ce3284e6a20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Itero Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>AWS, Glue, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf05ce3284e6a20</t>
+          <t>https://www.indeed.com/viewjob?jk=e304be37d5897728</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e304be37d5897728</t>
+          <t>https://www.indeed.com/viewjob?jk=9724f20b3e8cf9d3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Senior Data Management Professional - Data Engineering - Entities</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Itero Group</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9724f20b3e8cf9d3</t>
+          <t>https://www.indeed.com/viewjob?jk=00a24491194c9938</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Management Professional - Data Engineering - Entities</t>
+          <t>AI &amp; Financial Engineering Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Aktra Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a24491194c9938</t>
+          <t>https://www.indeed.com/viewjob?jk=241a34851225e025</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI &amp; Financial Engineering Developer</t>
+          <t>Senior Cloud Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Aktra Inc</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=241a34851225e025</t>
+          <t>https://www.indeed.com/viewjob?jk=0426c9944a6312e8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Remote</t>
+          <t>Junior Software Engineer- Cloud Cost Optimization</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0426c9944a6312e8</t>
+          <t>https://www.indeed.com/viewjob?jk=59be0306e4985a52</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59be0306e4985a52</t>
+          <t>https://www.indeed.com/viewjob?jk=12264a4762b0f153</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12264a4762b0f153</t>
+          <t>https://www.indeed.com/viewjob?jk=4741b2aaf2ec4639</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4741b2aaf2ec4639</t>
+          <t>https://www.indeed.com/viewjob?jk=c8379cf1d692d007</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8379cf1d692d007</t>
+          <t>https://www.indeed.com/viewjob?jk=9696f4f0c31fbf12</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9696f4f0c31fbf12</t>
+          <t>https://www.indeed.com/viewjob?jk=23fcdad233ea5e6d</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23fcdad233ea5e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=12bdc06f31387ddb</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12bdc06f31387ddb</t>
+          <t>https://www.indeed.com/viewjob?jk=7f457f2be81b9770</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f457f2be81b9770</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c8bee941837486</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c8bee941837486</t>
+          <t>https://www.indeed.com/viewjob?jk=6bce80595c811362</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bce80595c811362</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0cf43be3ae79d3</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0cf43be3ae79d3</t>
+          <t>https://www.indeed.com/viewjob?jk=ade89b18f313e675</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade89b18f313e675</t>
+          <t>https://www.indeed.com/viewjob?jk=cfddcbf296252d6b</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfddcbf296252d6b</t>
+          <t>https://www.indeed.com/viewjob?jk=0aae1d49cd9474ec</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0aae1d49cd9474ec</t>
+          <t>https://www.indeed.com/viewjob?jk=e2866e598e580305</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2866e598e580305</t>
+          <t>https://www.indeed.com/viewjob?jk=c2ffd4ec0a1a5c3a</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ffd4ec0a1a5c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=534c078f01ee2602</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=534c078f01ee2602</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d39a911901dc6d</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d39a911901dc6d</t>
+          <t>https://www.indeed.com/viewjob?jk=a72c1fe63174bbb8</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a72c1fe63174bbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=4bdbc801745a49ec</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Junior Software Engineer- Cloud Cost Optimization</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Charter Manufacturing</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Mequon, WI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bdbc801745a49ec</t>
+          <t>https://www.indeed.com/viewjob?jk=284985e81accb0a4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AI Native Developer- Europe</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Charter Manufacturing</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mequon, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,14 +2001,14 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=284985e81accb0a4</t>
+          <t>https://www.indeed.com/viewjob?jk=444a0e6bd539f82b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Native Developer- Europe</t>
+          <t>AI Native Builder-Europe</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=444a0e6bd539f82b</t>
+          <t>https://www.indeed.com/viewjob?jk=ae934e8451ebc14c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Native Builder-Europe</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Entertainment Partners</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae934e8451ebc14c</t>
+          <t>https://www.indeed.com/viewjob?jk=e42eebf957e43408</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Senior Solutions Architect - Airflow (West Coast)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Entertainment Partners</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42eebf957e43408</t>
+          <t>https://www.indeed.com/viewjob?jk=563d41613641e2d6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (West Coast)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>GE Appliances</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, IAM, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563d41613641e2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=f488fb42bdd9a3e5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Data Scientist - AI/ML</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GE Appliances</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, IAM, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f488fb42bdd9a3e5</t>
+          <t>https://www.indeed.com/viewjob?jk=aa005e3343082c96</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - AI/ML</t>
+          <t>Artificial Intelligence (AI) Senior Data Scientist</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,59 +2211,59 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa005e3343082c96</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9ea8d31a8815a9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI) Senior Data Scientist</t>
+          <t>AWS Full Stack Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9ea8d31a8815a9</t>
+          <t>https://www.indeed.com/viewjob?jk=e643625eb77abd14</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AWS Full Stack Engineer</t>
+          <t>DataHub Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, IAM, RDS, Scala</t>
+          <t>AWS, S3, IAM, RDS, Azure, Kafka, Kafka Connect, Oracle, MySQL, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e643625eb77abd14</t>
+          <t>https://www.indeed.com/viewjob?jk=5423277344900438</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DataHub Developer</t>
+          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Kafka, Kafka Connect, Oracle, MySQL, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5423277344900438</t>
+          <t>https://www.indeed.com/viewjob?jk=4f9fcd187c753bef</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f9fcd187c753bef</t>
+          <t>https://www.indeed.com/viewjob?jk=751a33e38e145115</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=751a33e38e145115</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ec36958a4f20d5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Hadoop, Spark</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ec36958a4f20d5</t>
+          <t>https://www.indeed.com/viewjob?jk=84ef94552c14d9bd</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - FY27</t>
+          <t>DevOps Engineer III — Deployment, Release Safety &amp; Disaster Recovery</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, CodeBuild</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Cloud Storage, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754540310d15df69</t>
+          <t>https://www.indeed.com/viewjob?jk=406e283b35cafd12</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer II (US)</t>
+          <t>DevOps Engineer III — Deployment, Release Safety &amp; Disaster Recovery</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Cloud Storage, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,164 +2491,164 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2633a0f0dff514a6</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3692758f37822d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Princ Engr-Ntwk Engring</t>
+          <t>Senior Cloud Ops Engineer I - SRE</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>CaseWorthy</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e6dbfd3d963c65c</t>
+          <t>https://www.indeed.com/viewjob?jk=9d69f297c014e4a1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Escalent</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ef94552c14d9bd</t>
+          <t>https://www.indeed.com/viewjob?jk=45d62ba2dc0bd875</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DevOps Engineer III — Deployment, Release Safety &amp; Disaster Recovery</t>
+          <t>Systems Integration Senior Specialist</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Cloud Storage, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=406e283b35cafd12</t>
+          <t>https://www.indeed.com/viewjob?jk=73592828eec12b39</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DevOps Engineer III — Deployment, Release Safety &amp; Disaster Recovery</t>
+          <t>Software Development Engineer I - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Cloud Storage, Scala, CI/CD, Jenkins</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3692758f37822d</t>
+          <t>https://www.indeed.com/viewjob?jk=0b08010c09c91435</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Cloud Ops Engineer I - SRE</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CaseWorthy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
+          <t>AWS, Redshift, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,19 +2666,19 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d69f297c014e4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=ff8b1cf198867c72</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>DevOps Engineer IV — CI/CD Pipeline &amp; Platform Engineering</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Escalent</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45d62ba2dc0bd875</t>
+          <t>https://www.indeed.com/viewjob?jk=e953e5a091cd9103</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>DevOps Engineer IV — CI/CD Pipeline &amp; Platform Engineering</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff8b1cf198867c72</t>
+          <t>https://www.indeed.com/viewjob?jk=5eed877691f0ccfc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DevOps Engineer IV — CI/CD Pipeline &amp; Platform Engineering</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e953e5a091cd9103</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69cd7125f7a833</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DevOps Engineer IV — CI/CD Pipeline &amp; Platform Engineering</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eed877691f0ccfc</t>
+          <t>https://www.indeed.com/viewjob?jk=c09787e1cb8cb395</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Systems Integration Senior Specialist</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73592828eec12b39</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4ad7ea1b58a31e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Development Engineer I - ArcGIS Enterprise</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b08010c09c91435</t>
+          <t>https://www.indeed.com/viewjob?jk=1cc726639aa959a6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Sr Engineer, Data &amp; Analytics Platform (Snowflake/dbt)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>RDS, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe69cd7125f7a833</t>
+          <t>https://www.indeed.com/viewjob?jk=f401900b912197cd</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Spark Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c09787e1cb8cb395</t>
+          <t>https://www.indeed.com/viewjob?jk=2cb65007f4e4e07a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Spark Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,67 +2981,67 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4ad7ea1b58a31e</t>
+          <t>https://www.indeed.com/viewjob?jk=e7beab78b75a48b8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cc726639aa959a6</t>
+          <t>https://www.indeed.com/viewjob?jk=33124af211245233</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Blob Storage, YARN, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a457abd93bdf7c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=52c472962c791de2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data &amp; Analytics Platform (Snowflake/dbt)</t>
+          <t>Data Scientist, Analytics and Modelling</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, Power BI, Tableau, DataOps</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Spark, PySpark, Scala, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f401900b912197cd</t>
+          <t>https://www.indeed.com/viewjob?jk=9439d62d21cdb7b2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Spark Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cb65007f4e4e07a</t>
+          <t>https://www.indeed.com/viewjob?jk=ec87a9fb2bfdfaef</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Spark Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7beab78b75a48b8</t>
+          <t>https://www.indeed.com/viewjob?jk=31b3b16aa81c41b5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33124af211245233</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8e782a934aa046</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Machine Learning (Remote)</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, MLOps</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ef4f0fa082366da</t>
+          <t>https://www.indeed.com/viewjob?jk=f0d1116e6c21d2df</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DevOps Engineer IV — Operational Resilience, Observability &amp; SRE</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761890a317dd4012</t>
+          <t>https://www.indeed.com/viewjob?jk=d3aa3e371f227965</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DevOps Engineer IV — Operational Resilience, Observability &amp; SRE</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1c767b23cb64efd</t>
+          <t>https://www.indeed.com/viewjob?jk=4ca117bf04d9ffe8</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Scientist, Analytics and Modelling</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hope Hull, AL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Spark, PySpark, Scala, Git</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9439d62d21cdb7b2</t>
+          <t>https://www.indeed.com/viewjob?jk=ace45fc5c61852f3</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Advanced Software Engineer- Full Stack Cloud Developer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78950b770ed7417f</t>
+          <t>https://www.indeed.com/viewjob?jk=11ae8229a3a496f6</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec87a9fb2bfdfaef</t>
+          <t>https://www.indeed.com/viewjob?jk=e5568a11ce1b824f</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b3b16aa81c41b5</t>
+          <t>https://www.indeed.com/viewjob?jk=858f2040e74be705</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Hot Springs Village, AR, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8e782a934aa046</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f9c431318c2296</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0d1116e6c21d2df</t>
+          <t>https://www.indeed.com/viewjob?jk=22400953b1097638</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Long Key, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3aa3e371f227965</t>
+          <t>https://www.indeed.com/viewjob?jk=c250e961be308780</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca117bf04d9ffe8</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c18f90256dfdcf</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hope Hull, AL, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace45fc5c61852f3</t>
+          <t>https://www.indeed.com/viewjob?jk=991a6606bcf54e4c</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11ae8229a3a496f6</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa34df78a35e73c</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5568a11ce1b824f</t>
+          <t>https://www.indeed.com/viewjob?jk=717f4ba2563e9c72</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858f2040e74be705</t>
+          <t>https://www.indeed.com/viewjob?jk=58eb1e048db63cbb</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hot Springs Village, AR, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f9c431318c2296</t>
+          <t>https://www.indeed.com/viewjob?jk=89167ab20868e733</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22400953b1097638</t>
+          <t>https://www.indeed.com/viewjob?jk=b176e971f59ee1d0</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Long Key, FL, US USA</t>
+          <t>Middletown, DE, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c250e961be308780</t>
+          <t>https://www.indeed.com/viewjob?jk=e54aa8f1b4aaced8</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c18f90256dfdcf</t>
+          <t>https://www.indeed.com/viewjob?jk=613d4a5f22442bf1</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991a6606bcf54e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=535e05900f7981e2</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa34df78a35e73c</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1cb34888680ccb</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Corrales, NM, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=717f4ba2563e9c72</t>
+          <t>https://www.indeed.com/viewjob?jk=0d83e6279e7d6910</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58eb1e048db63cbb</t>
+          <t>https://www.indeed.com/viewjob?jk=106cbae01f7f7d8b</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Fremont, NH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89167ab20868e733</t>
+          <t>https://www.indeed.com/viewjob?jk=dd04313bb2f7da9d</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b176e971f59ee1d0</t>
+          <t>https://www.indeed.com/viewjob?jk=7219daec87e613e4</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Middletown, DE, US USA</t>
+          <t>New Franken, WI, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e54aa8f1b4aaced8</t>
+          <t>https://www.indeed.com/viewjob?jk=f31bac0e875df9af</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613d4a5f22442bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ca6c1debed50f1</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=535e05900f7981e2</t>
+          <t>https://www.indeed.com/viewjob?jk=a0cfe2200933398b</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1cb34888680ccb</t>
+          <t>https://www.indeed.com/viewjob?jk=269b4317cd08c69a</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Corrales, NM, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d83e6279e7d6910</t>
+          <t>https://www.indeed.com/viewjob?jk=f743c2d0ca8e8782</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106cbae01f7f7d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=3899d26482c4683b</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Fremont, NH, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd04313bb2f7da9d</t>
+          <t>https://www.indeed.com/viewjob?jk=66a2d72e8e7439f5</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7219daec87e613e4</t>
+          <t>https://www.indeed.com/viewjob?jk=317f859e3fbd6963</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>New Franken, WI, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31bac0e875df9af</t>
+          <t>https://www.indeed.com/viewjob?jk=e45db4fbb479caaa</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ca6c1debed50f1</t>
+          <t>https://www.indeed.com/viewjob?jk=192985db73897ccc</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Upper Darby, PA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0cfe2200933398b</t>
+          <t>https://www.indeed.com/viewjob?jk=d4dcb51fe0ec32e8</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Okemos, MI, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=269b4317cd08c69a</t>
+          <t>https://www.indeed.com/viewjob?jk=06c75a03e3040629</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f743c2d0ca8e8782</t>
+          <t>https://www.indeed.com/viewjob?jk=d1cc8989583f1dcf</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3899d26482c4683b</t>
+          <t>https://www.indeed.com/viewjob?jk=59a56d64f04cb490</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66a2d72e8e7439f5</t>
+          <t>https://www.indeed.com/viewjob?jk=cb22fabc567b6b1f</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=317f859e3fbd6963</t>
+          <t>https://www.indeed.com/viewjob?jk=93fa20c57faaa79c</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e45db4fbb479caaa</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7569c2f065a6e4</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=192985db73897ccc</t>
+          <t>https://www.indeed.com/viewjob?jk=4fc5ffa459949a81</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Upper Darby, PA, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4dcb51fe0ec32e8</t>
+          <t>https://www.indeed.com/viewjob?jk=133d752eeb387774</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>El Toro.com</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Okemos, MI, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c75a03e3040629</t>
+          <t>https://www.indeed.com/viewjob?jk=d42d84e2b583adb0</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Senior Software Engineer - Machine Learning (Remote)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>API Gateway, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1cc8989583f1dcf</t>
+          <t>https://www.indeed.com/viewjob?jk=0ef4f0fa082366da</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>DevOps Engineer IV — Operational Resilience, Observability &amp; SRE</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, S3, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59a56d64f04cb490</t>
+          <t>https://www.indeed.com/viewjob?jk=761890a317dd4012</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>DevOps Engineer IV — Operational Resilience, Observability &amp; SRE</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, S3, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb22fabc567b6b1f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1c767b23cb64efd</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Consultant, Data Analytics</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Beghou Consulting</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fa20c57faaa79c</t>
+          <t>https://www.indeed.com/viewjob?jk=6c4d9af5a8a63484</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Advanced Software Engineer- Full Stack Cloud Developer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7569c2f065a6e4</t>
+          <t>https://www.indeed.com/viewjob?jk=78950b770ed7417f</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fc5ffa459949a81</t>
+          <t>https://www.indeed.com/viewjob?jk=8102d30c9db848fa</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Sigma Report Developer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Tachyon Technologies</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=133d752eeb387774</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8d0798b16bd29a</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>DevOps Engineer III — Platform Maintenance &amp; Vulnerability Response</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>El Toro.com</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42d84e2b583adb0</t>
+          <t>https://www.indeed.com/viewjob?jk=cd03dd73fcf8e61c</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sigma Report Developer</t>
+          <t>DevOps Engineer III — Platform Maintenance &amp; Vulnerability Response</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Tachyon Technologies</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,77 +5071,77 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8d0798b16bd29a</t>
+          <t>https://www.indeed.com/viewjob?jk=81aea0d34c5dcd96</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Quality and Data Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Mercedes-Benz Group</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Vance, AL, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8102d30c9db848fa</t>
+          <t>https://www.indeed.com/viewjob?jk=3a36a0ff08797a70</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>DevOps Engineer III — Platform Maintenance &amp; Vulnerability Response</t>
+          <t>Sr. Data Engineer - Cloud, AWS and Snowflake</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,59 +5151,59 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd03dd73fcf8e61c</t>
+          <t>https://www.indeed.com/viewjob?jk=b4be1c8e67e2a1f2</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>DevOps Engineer III — Platform Maintenance &amp; Vulnerability Response</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81aea0d34c5dcd96</t>
+          <t>https://www.indeed.com/viewjob?jk=b36c700922532ac2</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Cloud, AWS and Snowflake</t>
+          <t>Azure Platform Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4be1c8e67e2a1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=32d19f755ee8489a</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, PySpark, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36c700922532ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=4223c8030b51f20b</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
+          <t>AWS, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d19f755ee8489a</t>
+          <t>https://www.indeed.com/viewjob?jk=3979f77f1eb1efbc</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS connect developer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, PySpark, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, Scala, DynamoDB, Terraform</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4223c8030b51f20b</t>
+          <t>https://www.indeed.com/viewjob?jk=7fdc32dbba430d32</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,17 +5351,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3979f77f1eb1efbc</t>
+          <t>https://www.indeed.com/viewjob?jk=d95f616f8a93e76b</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-2027 Information Technology - Software Engineer - Full-Time</t>
+          <t>2026-2027 Information Technology - Software Engineer - Intern</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6578ea1eb5e5142</t>
+          <t>https://www.indeed.com/viewjob?jk=eab14599c79da82b</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>AWS connect developer</t>
+          <t>2026-2027 Information Technology - Software Engineer - Full-Time</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, Scala, DynamoDB, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fdc32dbba430d32</t>
+          <t>https://www.indeed.com/viewjob?jk=d6578ea1eb5e5142</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>Data Engineer- Hybrid</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d95f616f8a93e76b</t>
+          <t>https://www.indeed.com/viewjob?jk=936d9e38993af00c</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-2027 Information Technology - Software Engineer - Intern</t>
+          <t>Full Stack Developer III - Private Markets Applications</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab14599c79da82b</t>
+          <t>https://www.indeed.com/viewjob?jk=04f2e93224c9a790</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Data Engineer- Hybrid</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936d9e38993af00c</t>
+          <t>https://www.indeed.com/viewjob?jk=032b8db4bfd5e6d8</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior .NET and SSRS Developer</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c8883b0dd19abf</t>
+          <t>https://www.indeed.com/viewjob?jk=46f856d080d24d05</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Full Stack Developer III - Private Markets Applications</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f2e93224c9a790</t>
+          <t>https://www.indeed.com/viewjob?jk=19153bb3202f8519</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032b8db4bfd5e6d8</t>
+          <t>https://www.indeed.com/viewjob?jk=ee7a2d23cf0b0fbe</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f856d080d24d05</t>
+          <t>https://www.indeed.com/viewjob?jk=00a3e62df8c707d8</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19153bb3202f8519</t>
+          <t>https://www.indeed.com/viewjob?jk=779a1a0a5eccc32e</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee7a2d23cf0b0fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=8993a2c0de0e70e1</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>RPA Engineer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a3e62df8c707d8</t>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Senior .NET and SSRS Developer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,32 +5851,32 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=779a1a0a5eccc32e</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c8883b0dd19abf</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Senior Software Engineer – Product</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Re:Build Manufacturing</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,32 +5886,32 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8993a2c0de0e70e1</t>
+          <t>https://www.indeed.com/viewjob?jk=61d08f5c56b39289</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>RPA Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, DataOps</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+          <t>https://www.indeed.com/viewjob?jk=0ebbf24573d559b5</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c629002dbb52205d</t>
+          <t>https://www.indeed.com/viewjob?jk=c2df343ab9d22ccf</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>SugarAI</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2df343ab9d22ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=51c067e768a2b9f2</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SugarAI</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,34 +6016,34 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, SQL Server, PostgreSQL, ETL, ELT</t>
+          <t>AWS, RDS, Scala, MLOps, CI/CD, Docker, Kubernetes, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51c067e768a2b9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=020e432808447458</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Data Engineer Seniors III (Databricks)</t>
+          <t>CCaaS GCP Product Owner</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Betsol</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,17 +6051,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Data Modeling, ETL, ELT</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Kafka, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89625a5f68a2c750</t>
+          <t>https://www.indeed.com/viewjob?jk=14af21d8d4a25c44</t>
         </is>
       </c>
     </row>
@@ -6173,17 +6173,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Development Operations Engineer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,24 +6201,24 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7dbdf6ce237b13d</t>
+          <t>https://www.indeed.com/viewjob?jk=730302ab09184768</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Network/Systems Engineer/DBA</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>CCSI</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MLOps, CI/CD, Docker, Kubernetes, Git, Python, SQL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, MySQL, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=020e432808447458</t>
+          <t>https://www.indeed.com/viewjob?jk=82f25ac0bbe1b8ca</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CCaaS GCP Product Owner</t>
+          <t>Solutions Engineer - Data Visualization</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Betsol</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Kafka, Power BI, Tableau</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14af21d8d4a25c44</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfe4bd64f8f496f</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Network/Systems Engineer/DBA</t>
+          <t>Senior Software Engineer I- Data &amp; Insights Engineering</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>CCSI</t>
+          <t>Aledade, Inc.</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,34 +6296,34 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, MySQL, Splunk, Terraform, Kubernetes</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82f25ac0bbe1b8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=15c358b482d33d6d</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Visualization</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfe4bd64f8f496f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7dbdf6ce237b13d</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I- Data &amp; Insights Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Aledade, Inc.</t>
+          <t>Verisure</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Uniontown, OH, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,34 +6366,34 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, SQL Server, REST API integration, Power BI, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c358b482d33d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=c374eb71cdd5829a</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Appian Dev-Reporting &amp; Analytics</t>
+          <t>[REMOTE] Senior Platform Software Engineer- Oracle Clinical Digital Assistant</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Department of Finance</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,34 +6401,34 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, ETL, Power BI, Tableau, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88aacc0c7f29344d</t>
+          <t>https://www.indeed.com/viewjob?jk=23f3fde4ed90357e</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Verisure</t>
+          <t>Asurion</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Uniontown, OH, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,34 +6436,34 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, REST API integration, Power BI, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, AWS CodePipeline, Docker</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c374eb71cdd5829a</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a35189b0c83845</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>[REMOTE] Senior Platform Software Engineer- Oracle Clinical Digital Assistant</t>
+          <t>Appian Dev-Reporting &amp; Analytics</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Department of Finance</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,52 +6471,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, ETL, Power BI, Tableau, AKS</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f3fde4ed90357e</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Asurion</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Sterling, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, AWS CodePipeline, Docker</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a35189b0c83845</t>
+          <t>https://www.indeed.com/viewjob?jk=88aacc0c7f29344d</t>
         </is>
       </c>
     </row>
